--- a/docs/dataset/RADAR_Test_CAMRI_ARG.xlsx
+++ b/docs/dataset/RADAR_Test_CAMRI_ARG.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ARG Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARG Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,16 +416,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
       <c r="G1" t="inlineStr">
         <is>
           <t>copies/mL</t>
@@ -462,6 +456,16 @@
         </is>
       </c>
       <c r="N1" t="inlineStr">
+        <is>
+          <t>copies/mL</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>copies/mL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>copies/mL</t>
         </is>
@@ -500,42 +504,52 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>blaKPC</t>
+          <t>AY456_qepA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>blaCTX_M</t>
+          <t>AY461_qnrS2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>vanA</t>
+          <t>AY466_MCR-1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>blaNDM</t>
+          <t>AY134_blaCTX-M_5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blaSHV</t>
+          <t>AY152_blaNDM</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>tetO</t>
+          <t>AY104_blaSHV_1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>tetM</t>
+          <t>AY601_blaOXA48</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>qnrA</t>
+          <t>AY153_blaKPC_2</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>AY8_AAC6-Ib_1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>AY32_floR_1</t>
         </is>
       </c>
     </row>
@@ -569,28 +583,34 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>969</v>
+        <v>403978.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4631.83</v>
+        <v>826665.4</v>
       </c>
       <c r="I3" t="n">
-        <v>424.35</v>
+        <v>620730.6</v>
       </c>
       <c r="J3" t="n">
-        <v>49.89</v>
+        <v>981591.3</v>
       </c>
       <c r="K3" t="n">
-        <v>971.28</v>
+        <v>243888</v>
       </c>
       <c r="L3" t="n">
-        <v>641.24</v>
+        <v>780608.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1002.6</v>
+        <v>52699.9</v>
       </c>
       <c r="N3" t="n">
-        <v>46.91</v>
+        <v>617087.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>132704.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>890275.9</v>
       </c>
     </row>
     <row r="4">
@@ -623,28 +643,34 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>378.97</v>
+        <v>200075.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4926.54</v>
+        <v>936948</v>
       </c>
       <c r="I4" t="n">
-        <v>132.6</v>
+        <v>760538.6</v>
       </c>
       <c r="J4" t="n">
-        <v>235.22</v>
+        <v>129646.3</v>
       </c>
       <c r="K4" t="n">
-        <v>910.02</v>
+        <v>17391.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1269.02</v>
+        <v>348996.2</v>
       </c>
       <c r="M4" t="n">
-        <v>2393.29</v>
+        <v>369997.1</v>
       </c>
       <c r="N4" t="n">
-        <v>796.34</v>
+        <v>499124.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>65837.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>882497.6</v>
       </c>
     </row>
     <row r="5">
@@ -677,28 +703,34 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>555.77</v>
+        <v>178802.3</v>
       </c>
       <c r="H5" t="n">
-        <v>3592.04</v>
+        <v>479173.5</v>
       </c>
       <c r="I5" t="n">
-        <v>77.40000000000001</v>
+        <v>70458.60000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>89.01000000000001</v>
+        <v>970075</v>
       </c>
       <c r="K5" t="n">
-        <v>1937.42</v>
+        <v>451861.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1737.54</v>
+        <v>851687</v>
       </c>
       <c r="M5" t="n">
-        <v>1355.49</v>
+        <v>645731.5</v>
       </c>
       <c r="N5" t="n">
-        <v>598.38</v>
+        <v>558256.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>669758.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>956080.2</v>
       </c>
     </row>
     <row r="6">
@@ -731,28 +763,34 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>57.17</v>
+        <v>248431.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2920.89</v>
+        <v>892929.4</v>
       </c>
       <c r="I6" t="n">
-        <v>251.43</v>
+        <v>742.7</v>
       </c>
       <c r="J6" t="n">
-        <v>255.82</v>
+        <v>661488.4</v>
       </c>
       <c r="K6" t="n">
-        <v>314.87</v>
+        <v>167424.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2882.34</v>
+        <v>956694.1</v>
       </c>
       <c r="M6" t="n">
-        <v>200.28</v>
+        <v>127948.4</v>
       </c>
       <c r="N6" t="n">
-        <v>148.66</v>
+        <v>104746.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>140883.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>926365.5</v>
       </c>
     </row>
     <row r="7">
@@ -785,28 +823,34 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>595.04</v>
+        <v>759877.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3376.06</v>
+        <v>889266.1</v>
       </c>
       <c r="I7" t="n">
-        <v>117.6</v>
+        <v>113963.8</v>
       </c>
       <c r="J7" t="n">
-        <v>35.97</v>
+        <v>767727.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1780.57</v>
+        <v>955055.5</v>
       </c>
       <c r="L7" t="n">
-        <v>738.65</v>
+        <v>343371.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1486.3</v>
+        <v>11009.4</v>
       </c>
       <c r="N7" t="n">
-        <v>495.51</v>
+        <v>354676.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>701835</v>
+      </c>
+      <c r="P7" t="n">
+        <v>864944.3</v>
       </c>
     </row>
     <row r="8">
@@ -839,28 +883,34 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>419.22</v>
+        <v>251151</v>
       </c>
       <c r="H8" t="n">
-        <v>2918.36</v>
+        <v>476353.4</v>
       </c>
       <c r="I8" t="n">
-        <v>261.39</v>
+        <v>435847.4</v>
       </c>
       <c r="J8" t="n">
-        <v>280.41</v>
+        <v>945468.4</v>
       </c>
       <c r="K8" t="n">
-        <v>408.52</v>
+        <v>822021.9</v>
       </c>
       <c r="L8" t="n">
-        <v>2148.58</v>
+        <v>673405.5</v>
       </c>
       <c r="M8" t="n">
-        <v>596.71</v>
+        <v>794110.9</v>
       </c>
       <c r="N8" t="n">
-        <v>316.63</v>
+        <v>184677.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>611971.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>712342.2</v>
       </c>
     </row>
     <row r="9">
@@ -893,28 +943,34 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>671.6900000000001</v>
+        <v>383067.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1499.99</v>
+        <v>169481.7</v>
       </c>
       <c r="I9" t="n">
-        <v>158.09</v>
+        <v>691875.2</v>
       </c>
       <c r="J9" t="n">
-        <v>225.56</v>
+        <v>548111.8</v>
       </c>
       <c r="K9" t="n">
-        <v>145.09</v>
+        <v>935990.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1374.86</v>
+        <v>209740.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2496.14</v>
+        <v>132740.3</v>
       </c>
       <c r="N9" t="n">
-        <v>796.88</v>
+        <v>937649</v>
+      </c>
+      <c r="O9" t="n">
+        <v>757976.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>948900.4</v>
       </c>
     </row>
     <row r="10">
@@ -947,28 +1003,34 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>73.26000000000001</v>
+        <v>684308.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1065.77</v>
+        <v>74745.39999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>132.6</v>
+        <v>972659.1</v>
       </c>
       <c r="J10" t="n">
-        <v>279.98</v>
+        <v>535043.7</v>
       </c>
       <c r="K10" t="n">
-        <v>1761.73</v>
+        <v>213499</v>
       </c>
       <c r="L10" t="n">
-        <v>2637.81</v>
+        <v>278195.2</v>
       </c>
       <c r="M10" t="n">
-        <v>923.8200000000001</v>
+        <v>512820.5</v>
       </c>
       <c r="N10" t="n">
-        <v>126.2</v>
+        <v>465952.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>344148.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>194329.9</v>
       </c>
     </row>
     <row r="11">
@@ -1001,28 +1063,34 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>833.74</v>
+        <v>538629.1</v>
       </c>
       <c r="H11" t="n">
-        <v>3517.7</v>
+        <v>239573</v>
       </c>
       <c r="I11" t="n">
-        <v>305.84</v>
+        <v>369765.5</v>
       </c>
       <c r="J11" t="n">
-        <v>296.17</v>
+        <v>142416</v>
       </c>
       <c r="K11" t="n">
-        <v>1307.95</v>
+        <v>874838.2</v>
       </c>
       <c r="L11" t="n">
-        <v>23.47</v>
+        <v>222024.7</v>
       </c>
       <c r="M11" t="n">
-        <v>2042.76</v>
+        <v>341867.6</v>
       </c>
       <c r="N11" t="n">
-        <v>239.5</v>
+        <v>65762.39999999999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>927176.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>145305.7</v>
       </c>
     </row>
     <row r="12">
@@ -1055,28 +1123,34 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>663.39</v>
+        <v>938376.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4694.65</v>
+        <v>459872.1</v>
       </c>
       <c r="I12" t="n">
-        <v>67.15000000000001</v>
+        <v>423749.4</v>
       </c>
       <c r="J12" t="n">
-        <v>34.63</v>
+        <v>411303.1</v>
       </c>
       <c r="K12" t="n">
-        <v>214.07</v>
+        <v>914116.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1659.67</v>
+        <v>507135.2</v>
       </c>
       <c r="M12" t="n">
-        <v>680.87</v>
+        <v>435003.3</v>
       </c>
       <c r="N12" t="n">
-        <v>483.86</v>
+        <v>185232.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>60646.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>828058.9</v>
       </c>
     </row>
     <row r="13">
@@ -1109,28 +1183,34 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>717.61</v>
+        <v>489275</v>
       </c>
       <c r="H13" t="n">
-        <v>1017.99</v>
+        <v>15413</v>
       </c>
       <c r="I13" t="n">
-        <v>317.12</v>
+        <v>876080.6</v>
       </c>
       <c r="J13" t="n">
-        <v>79.2</v>
+        <v>552407.1</v>
       </c>
       <c r="K13" t="n">
-        <v>977.0599999999999</v>
+        <v>282363.7</v>
       </c>
       <c r="L13" t="n">
-        <v>2716.01</v>
+        <v>101620</v>
       </c>
       <c r="M13" t="n">
-        <v>2115.26</v>
+        <v>844330.8</v>
       </c>
       <c r="N13" t="n">
-        <v>73.84</v>
+        <v>472660.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>76307.10000000001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>948059.3</v>
       </c>
     </row>
     <row r="14">
@@ -1163,28 +1243,34 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>423.58</v>
+        <v>421639.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1383.4</v>
+        <v>329746.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.77</v>
+        <v>767674.3</v>
       </c>
       <c r="J14" t="n">
-        <v>231.34</v>
+        <v>265116.9</v>
       </c>
       <c r="K14" t="n">
-        <v>1274.23</v>
+        <v>814946.9</v>
       </c>
       <c r="L14" t="n">
-        <v>785.87</v>
+        <v>806458.9</v>
       </c>
       <c r="M14" t="n">
-        <v>1853.08</v>
+        <v>780949.6</v>
       </c>
       <c r="N14" t="n">
-        <v>441.34</v>
+        <v>320727.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>517564.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>536115.1</v>
       </c>
     </row>
     <row r="15">
@@ -1217,28 +1303,34 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>427.69</v>
+        <v>613216.1</v>
       </c>
       <c r="H15" t="n">
-        <v>48.35</v>
+        <v>494123.9</v>
       </c>
       <c r="I15" t="n">
-        <v>37.62</v>
+        <v>904308.1</v>
       </c>
       <c r="J15" t="n">
-        <v>264.93</v>
+        <v>434212.6</v>
       </c>
       <c r="K15" t="n">
-        <v>1807.86</v>
+        <v>368793.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1636.77</v>
+        <v>698233</v>
       </c>
       <c r="M15" t="n">
-        <v>2086.49</v>
+        <v>719031.7</v>
       </c>
       <c r="N15" t="n">
-        <v>466.01</v>
+        <v>609474.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>239869.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>547737.4</v>
       </c>
     </row>
     <row r="16">
@@ -1271,28 +1363,34 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>148.09</v>
+        <v>216692.3</v>
       </c>
       <c r="H16" t="n">
-        <v>637.23</v>
+        <v>335750.9</v>
       </c>
       <c r="I16" t="n">
-        <v>154.13</v>
+        <v>262823.5</v>
       </c>
       <c r="J16" t="n">
-        <v>269.69</v>
+        <v>383897</v>
       </c>
       <c r="K16" t="n">
-        <v>1592.24</v>
+        <v>186186.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2582.11</v>
+        <v>125162.4</v>
       </c>
       <c r="M16" t="n">
-        <v>2247.31</v>
+        <v>844586</v>
       </c>
       <c r="N16" t="n">
-        <v>168.06</v>
+        <v>928777.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>41426.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>622469.1</v>
       </c>
     </row>
     <row r="17">
@@ -1325,28 +1423,34 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>249.53</v>
+        <v>901999.3</v>
       </c>
       <c r="H17" t="n">
-        <v>513.97</v>
+        <v>733727.6</v>
       </c>
       <c r="I17" t="n">
-        <v>390.06</v>
+        <v>712075.2</v>
       </c>
       <c r="J17" t="n">
-        <v>265.24</v>
+        <v>837630.7</v>
       </c>
       <c r="K17" t="n">
-        <v>812.75</v>
+        <v>676494.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1861.98</v>
+        <v>278221.3</v>
       </c>
       <c r="M17" t="n">
-        <v>386.38</v>
+        <v>870054</v>
       </c>
       <c r="N17" t="n">
-        <v>743.9</v>
+        <v>436541.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>480451.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>690120.9</v>
       </c>
     </row>
     <row r="18">
@@ -1379,28 +1483,34 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>864.61</v>
+        <v>373979.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4881.03</v>
+        <v>569617.9</v>
       </c>
       <c r="I18" t="n">
-        <v>405.39</v>
+        <v>808399.6</v>
       </c>
       <c r="J18" t="n">
-        <v>264.42</v>
+        <v>345621.8</v>
       </c>
       <c r="K18" t="n">
-        <v>49.57</v>
+        <v>334280.7</v>
       </c>
       <c r="L18" t="n">
-        <v>2209.69</v>
+        <v>257132.7</v>
       </c>
       <c r="M18" t="n">
-        <v>830.46</v>
+        <v>767710</v>
       </c>
       <c r="N18" t="n">
-        <v>744.65</v>
+        <v>587162.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>889752.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>450740.7</v>
       </c>
     </row>
     <row r="19">
@@ -1433,28 +1543,34 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>802.24</v>
+        <v>388111.9</v>
       </c>
       <c r="H19" t="n">
-        <v>4320.32</v>
+        <v>533012</v>
       </c>
       <c r="I19" t="n">
-        <v>405.37</v>
+        <v>273271.1</v>
       </c>
       <c r="J19" t="n">
-        <v>80.04000000000001</v>
+        <v>896246.3</v>
       </c>
       <c r="K19" t="n">
-        <v>1574.75</v>
+        <v>301599.8</v>
       </c>
       <c r="L19" t="n">
-        <v>324.29</v>
+        <v>944063.4</v>
       </c>
       <c r="M19" t="n">
-        <v>2180.42</v>
+        <v>67239.89999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>686.87</v>
+        <v>260667.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>411455</v>
+      </c>
+      <c r="P19" t="n">
+        <v>117103.8</v>
       </c>
     </row>
     <row r="20">
@@ -1487,28 +1603,34 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>222.43</v>
+        <v>682368.8</v>
       </c>
       <c r="H20" t="n">
-        <v>4082.93</v>
+        <v>633507.5</v>
       </c>
       <c r="I20" t="n">
-        <v>230.15</v>
+        <v>243475</v>
       </c>
       <c r="J20" t="n">
-        <v>91.56</v>
+        <v>228472.2</v>
       </c>
       <c r="K20" t="n">
-        <v>1590.69</v>
+        <v>644575.2</v>
       </c>
       <c r="L20" t="n">
-        <v>682.79</v>
+        <v>899791.9</v>
       </c>
       <c r="M20" t="n">
-        <v>59.16</v>
+        <v>577721.2</v>
       </c>
       <c r="N20" t="n">
-        <v>154.5</v>
+        <v>858771.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>423108.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>173073.1</v>
       </c>
     </row>
     <row r="21">
@@ -1541,28 +1663,34 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>328.26</v>
+        <v>152276.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4321.76</v>
+        <v>582944.4</v>
       </c>
       <c r="I21" t="n">
-        <v>483.44</v>
+        <v>930321.3</v>
       </c>
       <c r="J21" t="n">
-        <v>83.73999999999999</v>
+        <v>651229.7</v>
       </c>
       <c r="K21" t="n">
-        <v>1282.96</v>
+        <v>648331.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1199.04</v>
+        <v>215047.2</v>
       </c>
       <c r="M21" t="n">
-        <v>2452.87</v>
+        <v>164111.1</v>
       </c>
       <c r="N21" t="n">
-        <v>428.97</v>
+        <v>583605.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>809024</v>
+      </c>
+      <c r="P21" t="n">
+        <v>443819</v>
       </c>
     </row>
     <row r="22">
@@ -1595,28 +1723,34 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>939.24</v>
+        <v>660567.9</v>
       </c>
       <c r="H22" t="n">
-        <v>576.71</v>
+        <v>413938.9</v>
       </c>
       <c r="I22" t="n">
-        <v>485.2</v>
+        <v>219706.2</v>
       </c>
       <c r="J22" t="n">
-        <v>53.57</v>
+        <v>499787.5</v>
       </c>
       <c r="K22" t="n">
-        <v>1925.07</v>
+        <v>14565.8</v>
       </c>
       <c r="L22" t="n">
-        <v>796.4</v>
+        <v>622440.5</v>
       </c>
       <c r="M22" t="n">
-        <v>271.01</v>
+        <v>901497.8</v>
       </c>
       <c r="N22" t="n">
-        <v>347.65</v>
+        <v>989017.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>863654.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>107294.1</v>
       </c>
     </row>
     <row r="23">
@@ -1649,28 +1783,34 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>728.55</v>
+        <v>849967.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1568.39</v>
+        <v>165984.2</v>
       </c>
       <c r="I23" t="n">
-        <v>303.1</v>
+        <v>326062.7</v>
       </c>
       <c r="J23" t="n">
-        <v>153.43</v>
+        <v>301521.2</v>
       </c>
       <c r="K23" t="n">
-        <v>770.39</v>
+        <v>28681.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1729.76</v>
+        <v>751459.5</v>
       </c>
       <c r="M23" t="n">
-        <v>636.8099999999999</v>
+        <v>762343.2</v>
       </c>
       <c r="N23" t="n">
-        <v>567.03</v>
+        <v>493097.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>190855</v>
+      </c>
+      <c r="P23" t="n">
+        <v>60994.8</v>
       </c>
     </row>
     <row r="24">
@@ -1703,28 +1843,34 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.69</v>
+        <v>338806.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4627.88</v>
+        <v>588142.9</v>
       </c>
       <c r="I24" t="n">
-        <v>269.23</v>
+        <v>102468.6</v>
       </c>
       <c r="J24" t="n">
-        <v>215.83</v>
+        <v>779493.1</v>
       </c>
       <c r="K24" t="n">
-        <v>1483.9</v>
+        <v>535942.7</v>
       </c>
       <c r="L24" t="n">
-        <v>2011.89</v>
+        <v>521772.7</v>
       </c>
       <c r="M24" t="n">
-        <v>910.55</v>
+        <v>809488.5</v>
       </c>
       <c r="N24" t="n">
-        <v>55.98</v>
+        <v>917351.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>698942.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>600131</v>
       </c>
     </row>
     <row r="25">
@@ -1757,28 +1903,34 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>664.24</v>
+        <v>946859.1</v>
       </c>
       <c r="H25" t="n">
-        <v>1651</v>
+        <v>47488.4</v>
       </c>
       <c r="I25" t="n">
-        <v>156.96</v>
+        <v>876301.8</v>
       </c>
       <c r="J25" t="n">
-        <v>254.4</v>
+        <v>988827.5</v>
       </c>
       <c r="K25" t="n">
-        <v>1439.51</v>
+        <v>90180.8</v>
       </c>
       <c r="L25" t="n">
-        <v>900.97</v>
+        <v>280407.8</v>
       </c>
       <c r="M25" t="n">
-        <v>773.21</v>
+        <v>545562.8</v>
       </c>
       <c r="N25" t="n">
-        <v>326.71</v>
+        <v>169289.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>661165.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>945429.5</v>
       </c>
     </row>
     <row r="26">
@@ -1811,28 +1963,34 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>402.4</v>
+        <v>528716.2</v>
       </c>
       <c r="H26" t="n">
-        <v>1478.28</v>
+        <v>36141.6</v>
       </c>
       <c r="I26" t="n">
-        <v>63.64</v>
+        <v>621347.9</v>
       </c>
       <c r="J26" t="n">
-        <v>126.13</v>
+        <v>126865.3</v>
       </c>
       <c r="K26" t="n">
-        <v>1880.73</v>
+        <v>108088</v>
       </c>
       <c r="L26" t="n">
-        <v>2031.95</v>
+        <v>850156.8</v>
       </c>
       <c r="M26" t="n">
-        <v>2257.01</v>
+        <v>400944.6</v>
       </c>
       <c r="N26" t="n">
-        <v>492.41</v>
+        <v>898508.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>289043.7</v>
+      </c>
+      <c r="P26" t="n">
+        <v>406154.9</v>
       </c>
     </row>
     <row r="27">
@@ -1865,28 +2023,34 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>300.95</v>
+        <v>774473.6</v>
       </c>
       <c r="H27" t="n">
-        <v>2739.69</v>
+        <v>342389.7</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>243104.1</v>
       </c>
       <c r="J27" t="n">
-        <v>86.06999999999999</v>
+        <v>811215.1</v>
       </c>
       <c r="K27" t="n">
-        <v>859.78</v>
+        <v>934508.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1739.95</v>
+        <v>14260.2</v>
       </c>
       <c r="M27" t="n">
-        <v>1636.76</v>
+        <v>326990.8</v>
       </c>
       <c r="N27" t="n">
-        <v>371.99</v>
+        <v>537712.7</v>
+      </c>
+      <c r="O27" t="n">
+        <v>73847.7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>793728.8</v>
       </c>
     </row>
     <row r="28">
@@ -1919,28 +2083,34 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>442.16</v>
+        <v>469039</v>
       </c>
       <c r="H28" t="n">
-        <v>1068.51</v>
+        <v>229955.9</v>
       </c>
       <c r="I28" t="n">
-        <v>236.59</v>
+        <v>442264.9</v>
       </c>
       <c r="J28" t="n">
-        <v>270.35</v>
+        <v>69888.3</v>
       </c>
       <c r="K28" t="n">
-        <v>1592.05</v>
+        <v>952021</v>
       </c>
       <c r="L28" t="n">
-        <v>509.07</v>
+        <v>936648.6</v>
       </c>
       <c r="M28" t="n">
-        <v>211.99</v>
+        <v>936845.3</v>
       </c>
       <c r="N28" t="n">
-        <v>412.36</v>
+        <v>117289.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>809378.3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>552174.7</v>
       </c>
     </row>
     <row r="29">
@@ -1973,28 +2143,34 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>632.9400000000001</v>
+        <v>402622.7</v>
       </c>
       <c r="H29" t="n">
-        <v>1675.94</v>
+        <v>755519</v>
       </c>
       <c r="I29" t="n">
-        <v>409.21</v>
+        <v>444703.9</v>
       </c>
       <c r="J29" t="n">
-        <v>225.34</v>
+        <v>355050.4</v>
       </c>
       <c r="K29" t="n">
-        <v>1345.59</v>
+        <v>711734.2</v>
       </c>
       <c r="L29" t="n">
-        <v>673.92</v>
+        <v>753333.9</v>
       </c>
       <c r="M29" t="n">
-        <v>497.82</v>
+        <v>887244.6</v>
       </c>
       <c r="N29" t="n">
-        <v>19.54</v>
+        <v>596619.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>213042</v>
+      </c>
+      <c r="P29" t="n">
+        <v>437514.3</v>
       </c>
     </row>
     <row r="30">
@@ -2027,28 +2203,34 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>244.84</v>
+        <v>269399.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2375.68</v>
+        <v>158516.7</v>
       </c>
       <c r="I30" t="n">
-        <v>424.87</v>
+        <v>16857.5</v>
       </c>
       <c r="J30" t="n">
-        <v>21.85</v>
+        <v>956954.8</v>
       </c>
       <c r="K30" t="n">
-        <v>828.88</v>
+        <v>923655.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1889.3</v>
+        <v>621820.5</v>
       </c>
       <c r="M30" t="n">
-        <v>486.09</v>
+        <v>148215.5</v>
       </c>
       <c r="N30" t="n">
-        <v>557.08</v>
+        <v>309189</v>
+      </c>
+      <c r="O30" t="n">
+        <v>444021.1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>574153.8</v>
       </c>
     </row>
     <row r="31">
@@ -2081,28 +2263,34 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>494.38</v>
+        <v>7619.8</v>
       </c>
       <c r="H31" t="n">
-        <v>1219.92</v>
+        <v>439081.1</v>
       </c>
       <c r="I31" t="n">
-        <v>328.03</v>
+        <v>743704.6</v>
       </c>
       <c r="J31" t="n">
-        <v>1.66</v>
+        <v>965133.3</v>
       </c>
       <c r="K31" t="n">
-        <v>1501.93</v>
+        <v>689999.5</v>
       </c>
       <c r="L31" t="n">
-        <v>2310.14</v>
+        <v>272168.9</v>
       </c>
       <c r="M31" t="n">
-        <v>266.47</v>
+        <v>77897</v>
       </c>
       <c r="N31" t="n">
-        <v>340.12</v>
+        <v>124.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>446320.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>997793.5</v>
       </c>
     </row>
     <row r="32">
@@ -2135,28 +2323,34 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>175.89</v>
+        <v>203764.4</v>
       </c>
       <c r="H32" t="n">
-        <v>4789.83</v>
+        <v>695537.3</v>
       </c>
       <c r="I32" t="n">
-        <v>258.98</v>
+        <v>77636.39999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>15.07</v>
+        <v>926992.3</v>
       </c>
       <c r="K32" t="n">
-        <v>498.4</v>
+        <v>926331.3</v>
       </c>
       <c r="L32" t="n">
-        <v>2545.01</v>
+        <v>90134</v>
       </c>
       <c r="M32" t="n">
-        <v>1141.15</v>
+        <v>656489.4</v>
       </c>
       <c r="N32" t="n">
-        <v>641.13</v>
+        <v>67349.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>729417.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>118873.5</v>
       </c>
     </row>
     <row r="33">
@@ -2189,28 +2383,34 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>667.58</v>
+        <v>989570</v>
       </c>
       <c r="H33" t="n">
-        <v>4939.46</v>
+        <v>417717.2</v>
       </c>
       <c r="I33" t="n">
-        <v>297.73</v>
+        <v>383423.5</v>
       </c>
       <c r="J33" t="n">
-        <v>285.01</v>
+        <v>355278.3</v>
       </c>
       <c r="K33" t="n">
-        <v>1782.85</v>
+        <v>3532.9</v>
       </c>
       <c r="L33" t="n">
-        <v>1837.96</v>
+        <v>389127.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1798.18</v>
+        <v>286434</v>
       </c>
       <c r="N33" t="n">
-        <v>403.82</v>
+        <v>6650.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>574771.8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>565338.5</v>
       </c>
     </row>
     <row r="34">
@@ -2243,28 +2443,34 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>830.5700000000001</v>
+        <v>534310</v>
       </c>
       <c r="H34" t="n">
-        <v>2739.36</v>
+        <v>805354.3</v>
       </c>
       <c r="I34" t="n">
-        <v>448.6</v>
+        <v>737707.5</v>
       </c>
       <c r="J34" t="n">
-        <v>223.1</v>
+        <v>740339.8</v>
       </c>
       <c r="K34" t="n">
-        <v>949.35</v>
+        <v>372670.8</v>
       </c>
       <c r="L34" t="n">
-        <v>777.5700000000001</v>
+        <v>513116.9</v>
       </c>
       <c r="M34" t="n">
-        <v>618.1</v>
+        <v>531961.3</v>
       </c>
       <c r="N34" t="n">
-        <v>510.13</v>
+        <v>425351.8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>730302</v>
+      </c>
+      <c r="P34" t="n">
+        <v>271193.7</v>
       </c>
     </row>
     <row r="35">
@@ -2297,28 +2503,34 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>765.8099999999999</v>
+        <v>462086.7</v>
       </c>
       <c r="H35" t="n">
-        <v>2606.5</v>
+        <v>117167.3</v>
       </c>
       <c r="I35" t="n">
-        <v>313.37</v>
+        <v>282298.5</v>
       </c>
       <c r="J35" t="n">
-        <v>82.38</v>
+        <v>977158.2</v>
       </c>
       <c r="K35" t="n">
-        <v>154.97</v>
+        <v>365383.6</v>
       </c>
       <c r="L35" t="n">
-        <v>857.1799999999999</v>
+        <v>572977.5</v>
       </c>
       <c r="M35" t="n">
-        <v>679.29</v>
+        <v>614566.9</v>
       </c>
       <c r="N35" t="n">
-        <v>255.77</v>
+        <v>826795.9</v>
+      </c>
+      <c r="O35" t="n">
+        <v>957401.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>592815.2</v>
       </c>
     </row>
     <row r="36">
@@ -2351,28 +2563,34 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>540.15</v>
+        <v>900242.3</v>
       </c>
       <c r="H36" t="n">
-        <v>691.87</v>
+        <v>171836.9</v>
       </c>
       <c r="I36" t="n">
-        <v>115.63</v>
+        <v>764567.2</v>
       </c>
       <c r="J36" t="n">
-        <v>208.18</v>
+        <v>64630.1</v>
       </c>
       <c r="K36" t="n">
-        <v>1412.84</v>
+        <v>339090.6</v>
       </c>
       <c r="L36" t="n">
-        <v>192.69</v>
+        <v>181688.2</v>
       </c>
       <c r="M36" t="n">
-        <v>1019</v>
+        <v>437022.2</v>
       </c>
       <c r="N36" t="n">
-        <v>434.09</v>
+        <v>595830.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>651569.3</v>
+      </c>
+      <c r="P36" t="n">
+        <v>755887.3</v>
       </c>
     </row>
     <row r="37">
@@ -2405,28 +2623,34 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>415.77</v>
+        <v>605509.1</v>
       </c>
       <c r="H37" t="n">
-        <v>1034.17</v>
+        <v>275490.9</v>
       </c>
       <c r="I37" t="n">
-        <v>210.07</v>
+        <v>902098.5</v>
       </c>
       <c r="J37" t="n">
-        <v>271.45</v>
+        <v>828210.7</v>
       </c>
       <c r="K37" t="n">
-        <v>1168.16</v>
+        <v>269584.2</v>
       </c>
       <c r="L37" t="n">
-        <v>2086.57</v>
+        <v>372020.9</v>
       </c>
       <c r="M37" t="n">
-        <v>2141.83</v>
+        <v>105617.5</v>
       </c>
       <c r="N37" t="n">
-        <v>612.48</v>
+        <v>658171.4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16665.7</v>
+      </c>
+      <c r="P37" t="n">
+        <v>326679.8</v>
       </c>
     </row>
     <row r="38">
@@ -2459,28 +2683,34 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>380.38</v>
+        <v>976711.9</v>
       </c>
       <c r="H38" t="n">
-        <v>29.48</v>
+        <v>365168.7</v>
       </c>
       <c r="I38" t="n">
-        <v>175.88</v>
+        <v>703947.9</v>
       </c>
       <c r="J38" t="n">
-        <v>226.04</v>
+        <v>724313.8</v>
       </c>
       <c r="K38" t="n">
-        <v>1706.9</v>
+        <v>319905.9</v>
       </c>
       <c r="L38" t="n">
-        <v>2860.29</v>
+        <v>156076.6</v>
       </c>
       <c r="M38" t="n">
-        <v>1047.55</v>
+        <v>504701.3</v>
       </c>
       <c r="N38" t="n">
-        <v>598.01</v>
+        <v>123495.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>984205.6</v>
+      </c>
+      <c r="P38" t="n">
+        <v>253864.9</v>
       </c>
     </row>
     <row r="39">
@@ -2513,28 +2743,34 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>546.13</v>
+        <v>357524.9</v>
       </c>
       <c r="H39" t="n">
-        <v>3016.26</v>
+        <v>559701</v>
       </c>
       <c r="I39" t="n">
-        <v>110.27</v>
+        <v>425819.1</v>
       </c>
       <c r="J39" t="n">
-        <v>65.83</v>
+        <v>932157.9</v>
       </c>
       <c r="K39" t="n">
-        <v>871.67</v>
+        <v>743708.7</v>
       </c>
       <c r="L39" t="n">
-        <v>87.06999999999999</v>
+        <v>24268</v>
       </c>
       <c r="M39" t="n">
-        <v>840.3200000000001</v>
+        <v>903431.6</v>
       </c>
       <c r="N39" t="n">
-        <v>543.3099999999999</v>
+        <v>632622.6</v>
+      </c>
+      <c r="O39" t="n">
+        <v>385429.9</v>
+      </c>
+      <c r="P39" t="n">
+        <v>347800.3</v>
       </c>
     </row>
     <row r="40">
@@ -2567,28 +2803,34 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>404.32</v>
+        <v>215823.3</v>
       </c>
       <c r="H40" t="n">
-        <v>825.22</v>
+        <v>198239.9</v>
       </c>
       <c r="I40" t="n">
-        <v>233.7</v>
+        <v>929481.3</v>
       </c>
       <c r="J40" t="n">
-        <v>38.29</v>
+        <v>451037.4</v>
       </c>
       <c r="K40" t="n">
-        <v>1244.51</v>
+        <v>949362.8</v>
       </c>
       <c r="L40" t="n">
-        <v>80.90000000000001</v>
+        <v>511809.6</v>
       </c>
       <c r="M40" t="n">
-        <v>985.05</v>
+        <v>462389.7</v>
       </c>
       <c r="N40" t="n">
-        <v>451.51</v>
+        <v>439686.9</v>
+      </c>
+      <c r="O40" t="n">
+        <v>388598.7</v>
+      </c>
+      <c r="P40" t="n">
+        <v>22536.2</v>
       </c>
     </row>
     <row r="41">
@@ -2621,28 +2863,34 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>27.1</v>
+        <v>920764.2</v>
       </c>
       <c r="H41" t="n">
-        <v>3213.75</v>
+        <v>559000.4</v>
       </c>
       <c r="I41" t="n">
-        <v>67.84999999999999</v>
+        <v>320899</v>
       </c>
       <c r="J41" t="n">
-        <v>138.51</v>
+        <v>643226.8</v>
       </c>
       <c r="K41" t="n">
-        <v>100.57</v>
+        <v>922066.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1137.31</v>
+        <v>481849.2</v>
       </c>
       <c r="M41" t="n">
-        <v>529.15</v>
+        <v>155010.3</v>
       </c>
       <c r="N41" t="n">
-        <v>261.48</v>
+        <v>124774</v>
+      </c>
+      <c r="O41" t="n">
+        <v>302389.4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>651712.5</v>
       </c>
     </row>
     <row r="42">
@@ -2675,28 +2923,34 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>761.23</v>
+        <v>160812</v>
       </c>
       <c r="H42" t="n">
-        <v>1895.63</v>
+        <v>701819.5</v>
       </c>
       <c r="I42" t="n">
-        <v>376</v>
+        <v>996372.3</v>
       </c>
       <c r="J42" t="n">
-        <v>249.58</v>
+        <v>762007.4</v>
       </c>
       <c r="K42" t="n">
-        <v>504.54</v>
+        <v>390111.6</v>
       </c>
       <c r="L42" t="n">
-        <v>245.72</v>
+        <v>606044.4</v>
       </c>
       <c r="M42" t="n">
-        <v>48.46</v>
+        <v>135963.5</v>
       </c>
       <c r="N42" t="n">
-        <v>431.54</v>
+        <v>452281.7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>851905.8</v>
+      </c>
+      <c r="P42" t="n">
+        <v>211265.2</v>
       </c>
     </row>
     <row r="43">
@@ -2729,28 +2983,34 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>999.91</v>
+        <v>791839.1</v>
       </c>
       <c r="H43" t="n">
-        <v>1749.8</v>
+        <v>652598.6</v>
       </c>
       <c r="I43" t="n">
-        <v>325.07</v>
+        <v>604972.7</v>
       </c>
       <c r="J43" t="n">
-        <v>234.37</v>
+        <v>496616.4</v>
       </c>
       <c r="K43" t="n">
-        <v>1303.51</v>
+        <v>603046.7</v>
       </c>
       <c r="L43" t="n">
-        <v>2262.7</v>
+        <v>433879.6</v>
       </c>
       <c r="M43" t="n">
-        <v>2374.03</v>
+        <v>965089.3</v>
       </c>
       <c r="N43" t="n">
-        <v>159.49</v>
+        <v>836272.6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>373915.9</v>
+      </c>
+      <c r="P43" t="n">
+        <v>145089.9</v>
       </c>
     </row>
     <row r="44">
@@ -2783,28 +3043,34 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>20.38</v>
+        <v>595417.5</v>
       </c>
       <c r="H44" t="n">
-        <v>761.91</v>
+        <v>815202.4</v>
       </c>
       <c r="I44" t="n">
-        <v>63.11</v>
+        <v>534585.2</v>
       </c>
       <c r="J44" t="n">
-        <v>200.84</v>
+        <v>718233.5</v>
       </c>
       <c r="K44" t="n">
-        <v>1127.94</v>
+        <v>230779.9</v>
       </c>
       <c r="L44" t="n">
-        <v>653.89</v>
+        <v>664912.5</v>
       </c>
       <c r="M44" t="n">
-        <v>1748.66</v>
+        <v>686931.8</v>
       </c>
       <c r="N44" t="n">
-        <v>613.52</v>
+        <v>670160.1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>42342.7</v>
+      </c>
+      <c r="P44" t="n">
+        <v>246193.9</v>
       </c>
     </row>
     <row r="45">
@@ -2837,28 +3103,34 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>167.79</v>
+        <v>982888.1</v>
       </c>
       <c r="H45" t="n">
-        <v>3036.24</v>
+        <v>81463</v>
       </c>
       <c r="I45" t="n">
-        <v>373.96</v>
+        <v>871527.3</v>
       </c>
       <c r="J45" t="n">
-        <v>34.36</v>
+        <v>216626.1</v>
       </c>
       <c r="K45" t="n">
-        <v>1638.6</v>
+        <v>308715.8</v>
       </c>
       <c r="L45" t="n">
-        <v>2894.16</v>
+        <v>942896.5</v>
       </c>
       <c r="M45" t="n">
-        <v>270.25</v>
+        <v>325807.7</v>
       </c>
       <c r="N45" t="n">
-        <v>20.54</v>
+        <v>787895.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>429353.8</v>
+      </c>
+      <c r="P45" t="n">
+        <v>578028</v>
       </c>
     </row>
     <row r="46">
@@ -2891,28 +3163,34 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>311.96</v>
+        <v>943910.6</v>
       </c>
       <c r="H46" t="n">
-        <v>3386.74</v>
+        <v>677874.2</v>
       </c>
       <c r="I46" t="n">
-        <v>479.09</v>
+        <v>105840.8</v>
       </c>
       <c r="J46" t="n">
-        <v>119</v>
+        <v>44667.6</v>
       </c>
       <c r="K46" t="n">
-        <v>1430.03</v>
+        <v>911514.4</v>
       </c>
       <c r="L46" t="n">
-        <v>227.99</v>
+        <v>398946.7</v>
       </c>
       <c r="M46" t="n">
-        <v>1726.54</v>
+        <v>509348.4</v>
       </c>
       <c r="N46" t="n">
-        <v>501.79</v>
+        <v>791.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>209810.6</v>
+      </c>
+      <c r="P46" t="n">
+        <v>885293.7</v>
       </c>
     </row>
     <row r="47">
@@ -2945,28 +3223,34 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>101.9</v>
+        <v>660299.7</v>
       </c>
       <c r="H47" t="n">
-        <v>3862.4</v>
+        <v>724747.9</v>
       </c>
       <c r="I47" t="n">
-        <v>425.15</v>
+        <v>286535.1</v>
       </c>
       <c r="J47" t="n">
-        <v>180.12</v>
+        <v>220169.3</v>
       </c>
       <c r="K47" t="n">
-        <v>242.11</v>
+        <v>538520.2</v>
       </c>
       <c r="L47" t="n">
-        <v>2951.53</v>
+        <v>584208.7</v>
       </c>
       <c r="M47" t="n">
-        <v>1956.59</v>
+        <v>883752.9</v>
       </c>
       <c r="N47" t="n">
-        <v>277.76</v>
+        <v>260327.1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>420729</v>
+      </c>
+      <c r="P47" t="n">
+        <v>877965.4</v>
       </c>
     </row>
     <row r="48">
@@ -2999,28 +3283,34 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>428.38</v>
+        <v>37062.2</v>
       </c>
       <c r="H48" t="n">
-        <v>1852.85</v>
+        <v>825072.8</v>
       </c>
       <c r="I48" t="n">
-        <v>252.98</v>
+        <v>775142.8</v>
       </c>
       <c r="J48" t="n">
-        <v>102.37</v>
+        <v>985279.2</v>
       </c>
       <c r="K48" t="n">
-        <v>1699.15</v>
+        <v>87795.8</v>
       </c>
       <c r="L48" t="n">
-        <v>2466.99</v>
+        <v>519688.6</v>
       </c>
       <c r="M48" t="n">
-        <v>263.85</v>
+        <v>429889</v>
       </c>
       <c r="N48" t="n">
-        <v>768.63</v>
+        <v>998753.8</v>
+      </c>
+      <c r="O48" t="n">
+        <v>14681.7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>346989</v>
       </c>
     </row>
     <row r="49">
@@ -3053,28 +3343,34 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>635.59</v>
+        <v>23303.8</v>
       </c>
       <c r="H49" t="n">
-        <v>4143.54</v>
+        <v>150197.6</v>
       </c>
       <c r="I49" t="n">
-        <v>353.65</v>
+        <v>68121.3</v>
       </c>
       <c r="J49" t="n">
-        <v>130.65</v>
+        <v>431420.5</v>
       </c>
       <c r="K49" t="n">
-        <v>1467.59</v>
+        <v>481799.8</v>
       </c>
       <c r="L49" t="n">
-        <v>2896.42</v>
+        <v>486343.2</v>
       </c>
       <c r="M49" t="n">
-        <v>675.21</v>
+        <v>213152.6</v>
       </c>
       <c r="N49" t="n">
-        <v>646.5599999999999</v>
+        <v>48634</v>
+      </c>
+      <c r="O49" t="n">
+        <v>802611.9</v>
+      </c>
+      <c r="P49" t="n">
+        <v>319729.9</v>
       </c>
     </row>
     <row r="50">
@@ -3107,28 +3403,34 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>538.17</v>
+        <v>473726.9</v>
       </c>
       <c r="H50" t="n">
-        <v>2417.49</v>
+        <v>86508.5</v>
       </c>
       <c r="I50" t="n">
-        <v>217.79</v>
+        <v>925282.2</v>
       </c>
       <c r="J50" t="n">
-        <v>219.31</v>
+        <v>888150.9</v>
       </c>
       <c r="K50" t="n">
-        <v>536.79</v>
+        <v>789008</v>
       </c>
       <c r="L50" t="n">
-        <v>2555.14</v>
+        <v>2947.2</v>
       </c>
       <c r="M50" t="n">
-        <v>2076.83</v>
+        <v>832966.5</v>
       </c>
       <c r="N50" t="n">
-        <v>69.33</v>
+        <v>174853.3</v>
+      </c>
+      <c r="O50" t="n">
+        <v>901428.1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>957327.4</v>
       </c>
     </row>
     <row r="51">
@@ -3161,28 +3463,34 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>881.63</v>
+        <v>819668.1</v>
       </c>
       <c r="H51" t="n">
-        <v>1219.32</v>
+        <v>759183.6</v>
       </c>
       <c r="I51" t="n">
-        <v>232.35</v>
+        <v>453770.9</v>
       </c>
       <c r="J51" t="n">
-        <v>183.1</v>
+        <v>970309.2</v>
       </c>
       <c r="K51" t="n">
-        <v>757.98</v>
+        <v>680852.9</v>
       </c>
       <c r="L51" t="n">
-        <v>86.09999999999999</v>
+        <v>83835.10000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>2127.38</v>
+        <v>589133.9</v>
       </c>
       <c r="N51" t="n">
-        <v>145.47</v>
+        <v>398767.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>619741</v>
+      </c>
+      <c r="P51" t="n">
+        <v>887521.5</v>
       </c>
     </row>
     <row r="52">
@@ -3215,28 +3523,34 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>212.12</v>
+        <v>81160.10000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>3989.16</v>
+        <v>646612.2</v>
       </c>
       <c r="I52" t="n">
-        <v>170.17</v>
+        <v>490083.7</v>
       </c>
       <c r="J52" t="n">
-        <v>264.1</v>
+        <v>916763.6</v>
       </c>
       <c r="K52" t="n">
-        <v>1402.37</v>
+        <v>111455</v>
       </c>
       <c r="L52" t="n">
-        <v>828.8099999999999</v>
+        <v>578352.7</v>
       </c>
       <c r="M52" t="n">
-        <v>25.38</v>
+        <v>490665</v>
       </c>
       <c r="N52" t="n">
-        <v>758.45</v>
+        <v>65668.2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>400014.8</v>
+      </c>
+      <c r="P52" t="n">
+        <v>186938.8</v>
       </c>
     </row>
     <row r="53">
@@ -3269,28 +3583,34 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>85.61</v>
+        <v>425420.2</v>
       </c>
       <c r="H53" t="n">
-        <v>3600.37</v>
+        <v>166563.9</v>
       </c>
       <c r="I53" t="n">
-        <v>244.29</v>
+        <v>996118.1</v>
       </c>
       <c r="J53" t="n">
-        <v>227.45</v>
+        <v>549314.9</v>
       </c>
       <c r="K53" t="n">
-        <v>1381.22</v>
+        <v>388763.5</v>
       </c>
       <c r="L53" t="n">
-        <v>1937.71</v>
+        <v>587809.5</v>
       </c>
       <c r="M53" t="n">
-        <v>1227.05</v>
+        <v>186970.7</v>
       </c>
       <c r="N53" t="n">
-        <v>634.35</v>
+        <v>218653</v>
+      </c>
+      <c r="O53" t="n">
+        <v>135313.1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>124558.3</v>
       </c>
     </row>
     <row r="54">
@@ -3323,28 +3643,34 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>93.05</v>
+        <v>86018.89999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>1107.98</v>
+        <v>870872.2</v>
       </c>
       <c r="I54" t="n">
-        <v>345.89</v>
+        <v>85120.3</v>
       </c>
       <c r="J54" t="n">
-        <v>91.86</v>
+        <v>288513.3</v>
       </c>
       <c r="K54" t="n">
-        <v>1163.11</v>
+        <v>320858.9</v>
       </c>
       <c r="L54" t="n">
-        <v>1419.78</v>
+        <v>368694.3</v>
       </c>
       <c r="M54" t="n">
-        <v>1327.3</v>
+        <v>642377.4</v>
       </c>
       <c r="N54" t="n">
-        <v>340.4</v>
+        <v>899512.9</v>
+      </c>
+      <c r="O54" t="n">
+        <v>198594.7</v>
+      </c>
+      <c r="P54" t="n">
+        <v>410899.2</v>
       </c>
     </row>
     <row r="55">
@@ -3377,28 +3703,34 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>745.9400000000001</v>
+        <v>309806.9</v>
       </c>
       <c r="H55" t="n">
-        <v>1653.96</v>
+        <v>716942.1</v>
       </c>
       <c r="I55" t="n">
-        <v>351.43</v>
+        <v>19837.5</v>
       </c>
       <c r="J55" t="n">
-        <v>81.27</v>
+        <v>608800.1</v>
       </c>
       <c r="K55" t="n">
-        <v>502.81</v>
+        <v>220869</v>
       </c>
       <c r="L55" t="n">
-        <v>361.97</v>
+        <v>344751.9</v>
       </c>
       <c r="M55" t="n">
-        <v>481.46</v>
+        <v>542285.8</v>
       </c>
       <c r="N55" t="n">
-        <v>95.64</v>
+        <v>641407.4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>632183.3</v>
+      </c>
+      <c r="P55" t="n">
+        <v>792515</v>
       </c>
     </row>
     <row r="56">
@@ -3431,28 +3763,34 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>535.86</v>
+        <v>5667.9</v>
       </c>
       <c r="H56" t="n">
-        <v>3810.95</v>
+        <v>614984</v>
       </c>
       <c r="I56" t="n">
-        <v>92.56999999999999</v>
+        <v>563103.7</v>
       </c>
       <c r="J56" t="n">
-        <v>64.92</v>
+        <v>770190.9</v>
       </c>
       <c r="K56" t="n">
-        <v>968.4</v>
+        <v>245596.3</v>
       </c>
       <c r="L56" t="n">
-        <v>2173.76</v>
+        <v>102807.5</v>
       </c>
       <c r="M56" t="n">
-        <v>2441.52</v>
+        <v>269397.3</v>
       </c>
       <c r="N56" t="n">
-        <v>419.71</v>
+        <v>661915.3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>63778.8</v>
+      </c>
+      <c r="P56" t="n">
+        <v>405804.2</v>
       </c>
     </row>
     <row r="57">
@@ -3485,28 +3823,34 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>283</v>
+        <v>329697.7</v>
       </c>
       <c r="H57" t="n">
-        <v>502.63</v>
+        <v>760553.9</v>
       </c>
       <c r="I57" t="n">
-        <v>97.06</v>
+        <v>634241.9</v>
       </c>
       <c r="J57" t="n">
-        <v>68.23999999999999</v>
+        <v>722321.9</v>
       </c>
       <c r="K57" t="n">
-        <v>358.88</v>
+        <v>837746.5</v>
       </c>
       <c r="L57" t="n">
-        <v>42.45</v>
+        <v>677427.9</v>
       </c>
       <c r="M57" t="n">
-        <v>1335.34</v>
+        <v>999405.3</v>
       </c>
       <c r="N57" t="n">
-        <v>219.45</v>
+        <v>747644.3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>435221.1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>286868.1</v>
       </c>
     </row>
     <row r="58">
@@ -3539,28 +3883,34 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>974.29</v>
+        <v>523402.1</v>
       </c>
       <c r="H58" t="n">
-        <v>2766.79</v>
+        <v>611087</v>
       </c>
       <c r="I58" t="n">
-        <v>348.71</v>
+        <v>862451</v>
       </c>
       <c r="J58" t="n">
-        <v>37.88</v>
+        <v>32621.2</v>
       </c>
       <c r="K58" t="n">
-        <v>1736.92</v>
+        <v>553312</v>
       </c>
       <c r="L58" t="n">
-        <v>1472.64</v>
+        <v>643222.2</v>
       </c>
       <c r="M58" t="n">
-        <v>2181.8</v>
+        <v>485092.7</v>
       </c>
       <c r="N58" t="n">
-        <v>459.25</v>
+        <v>872223.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>894073.2</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1694.1</v>
       </c>
     </row>
     <row r="59">
@@ -3593,28 +3943,34 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>469.4</v>
+        <v>200794.4</v>
       </c>
       <c r="H59" t="n">
-        <v>2202.34</v>
+        <v>340091.9</v>
       </c>
       <c r="I59" t="n">
-        <v>92.18000000000001</v>
+        <v>192372.6</v>
       </c>
       <c r="J59" t="n">
-        <v>15.41</v>
+        <v>56537</v>
       </c>
       <c r="K59" t="n">
-        <v>1882.13</v>
+        <v>803000.9</v>
       </c>
       <c r="L59" t="n">
-        <v>1433.19</v>
+        <v>119347.9</v>
       </c>
       <c r="M59" t="n">
-        <v>2055.29</v>
+        <v>629376.9</v>
       </c>
       <c r="N59" t="n">
-        <v>320.57</v>
+        <v>120799.9</v>
+      </c>
+      <c r="O59" t="n">
+        <v>984304.9</v>
+      </c>
+      <c r="P59" t="n">
+        <v>330864.5</v>
       </c>
     </row>
     <row r="60">
@@ -3647,28 +4003,34 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>74.08</v>
+        <v>787215.9</v>
       </c>
       <c r="H60" t="n">
-        <v>3147.23</v>
+        <v>52811.5</v>
       </c>
       <c r="I60" t="n">
-        <v>26.8</v>
+        <v>883192.1</v>
       </c>
       <c r="J60" t="n">
-        <v>44.76</v>
+        <v>32580.4</v>
       </c>
       <c r="K60" t="n">
-        <v>1125.68</v>
+        <v>396604.9</v>
       </c>
       <c r="L60" t="n">
-        <v>911.51</v>
+        <v>161300.2</v>
       </c>
       <c r="M60" t="n">
-        <v>2484.8</v>
+        <v>601190.5</v>
       </c>
       <c r="N60" t="n">
-        <v>94.76000000000001</v>
+        <v>255527.4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>832490.7</v>
+      </c>
+      <c r="P60" t="n">
+        <v>60809.8</v>
       </c>
     </row>
     <row r="61">
@@ -3701,28 +4063,34 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>764.4400000000001</v>
+        <v>55399.9</v>
       </c>
       <c r="H61" t="n">
-        <v>3031.59</v>
+        <v>342402.2</v>
       </c>
       <c r="I61" t="n">
-        <v>395.37</v>
+        <v>657678.2</v>
       </c>
       <c r="J61" t="n">
-        <v>67.70999999999999</v>
+        <v>249166.6</v>
       </c>
       <c r="K61" t="n">
-        <v>1045.15</v>
+        <v>842053.3</v>
       </c>
       <c r="L61" t="n">
-        <v>1351.54</v>
+        <v>244029.8</v>
       </c>
       <c r="M61" t="n">
-        <v>1106.8</v>
+        <v>161551.5</v>
       </c>
       <c r="N61" t="n">
-        <v>688.13</v>
+        <v>16890.8</v>
+      </c>
+      <c r="O61" t="n">
+        <v>538341.8</v>
+      </c>
+      <c r="P61" t="n">
+        <v>314533</v>
       </c>
     </row>
     <row r="62">
@@ -3755,28 +4123,34 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>990.03</v>
+        <v>211435.2</v>
       </c>
       <c r="H62" t="n">
-        <v>1526.9</v>
+        <v>625062.1</v>
       </c>
       <c r="I62" t="n">
-        <v>310.51</v>
+        <v>578734.2</v>
       </c>
       <c r="J62" t="n">
-        <v>182.89</v>
+        <v>393453.4</v>
       </c>
       <c r="K62" t="n">
-        <v>1480.18</v>
+        <v>7236.9</v>
       </c>
       <c r="L62" t="n">
-        <v>2842.77</v>
+        <v>284440.5</v>
       </c>
       <c r="M62" t="n">
-        <v>519.47</v>
+        <v>39786.8</v>
       </c>
       <c r="N62" t="n">
-        <v>168.82</v>
+        <v>335842.3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>347616</v>
+      </c>
+      <c r="P62" t="n">
+        <v>18668.9</v>
       </c>
     </row>
     <row r="63">
@@ -3809,28 +4183,34 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>660.4299999999999</v>
+        <v>257576.6</v>
       </c>
       <c r="H63" t="n">
-        <v>785.29</v>
+        <v>187990.2</v>
       </c>
       <c r="I63" t="n">
-        <v>86.91</v>
+        <v>19591.4</v>
       </c>
       <c r="J63" t="n">
-        <v>22.52</v>
+        <v>371414.6</v>
       </c>
       <c r="K63" t="n">
-        <v>5.35</v>
+        <v>341159.7</v>
       </c>
       <c r="L63" t="n">
-        <v>1351.51</v>
+        <v>562764.4</v>
       </c>
       <c r="M63" t="n">
-        <v>1484.53</v>
+        <v>876073.9</v>
       </c>
       <c r="N63" t="n">
-        <v>233.01</v>
+        <v>669724.6</v>
+      </c>
+      <c r="O63" t="n">
+        <v>469387.8</v>
+      </c>
+      <c r="P63" t="n">
+        <v>177464.1</v>
       </c>
     </row>
     <row r="64">
@@ -3863,28 +4243,34 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>231.48</v>
+        <v>404067.7</v>
       </c>
       <c r="H64" t="n">
-        <v>3534.78</v>
+        <v>179575.4</v>
       </c>
       <c r="I64" t="n">
-        <v>351.49</v>
+        <v>799342.4</v>
       </c>
       <c r="J64" t="n">
-        <v>136.21</v>
+        <v>759725.9</v>
       </c>
       <c r="K64" t="n">
-        <v>1374.77</v>
+        <v>190668</v>
       </c>
       <c r="L64" t="n">
-        <v>2771.73</v>
+        <v>797273.6</v>
       </c>
       <c r="M64" t="n">
-        <v>1969.57</v>
+        <v>344379.3</v>
       </c>
       <c r="N64" t="n">
-        <v>500.05</v>
+        <v>358384.4</v>
+      </c>
+      <c r="O64" t="n">
+        <v>721343.4</v>
+      </c>
+      <c r="P64" t="n">
+        <v>495670.9</v>
       </c>
     </row>
     <row r="65">
@@ -3917,28 +4303,34 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>661.1799999999999</v>
+        <v>763794.9</v>
       </c>
       <c r="H65" t="n">
-        <v>4668.34</v>
+        <v>111135.8</v>
       </c>
       <c r="I65" t="n">
-        <v>212.57</v>
+        <v>218067.8</v>
       </c>
       <c r="J65" t="n">
-        <v>163.37</v>
+        <v>764283.1</v>
       </c>
       <c r="K65" t="n">
-        <v>1295.27</v>
+        <v>268570.7</v>
       </c>
       <c r="L65" t="n">
-        <v>2725.23</v>
+        <v>566218.2</v>
       </c>
       <c r="M65" t="n">
-        <v>2066.58</v>
+        <v>447602.2</v>
       </c>
       <c r="N65" t="n">
-        <v>57.13</v>
+        <v>605240.8</v>
+      </c>
+      <c r="O65" t="n">
+        <v>148488.4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>369345.5</v>
       </c>
     </row>
     <row r="66">
@@ -3971,28 +4363,34 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>165.92</v>
+        <v>353808.5</v>
       </c>
       <c r="H66" t="n">
-        <v>1538.06</v>
+        <v>496557.4</v>
       </c>
       <c r="I66" t="n">
-        <v>374.48</v>
+        <v>667766.7</v>
       </c>
       <c r="J66" t="n">
-        <v>170.76</v>
+        <v>284234.6</v>
       </c>
       <c r="K66" t="n">
-        <v>577.22</v>
+        <v>735173.6</v>
       </c>
       <c r="L66" t="n">
-        <v>373.06</v>
+        <v>789588.7</v>
       </c>
       <c r="M66" t="n">
-        <v>1721.69</v>
+        <v>216970.6</v>
       </c>
       <c r="N66" t="n">
-        <v>559.79</v>
+        <v>997840.9</v>
+      </c>
+      <c r="O66" t="n">
+        <v>920202.3</v>
+      </c>
+      <c r="P66" t="n">
+        <v>900843.5</v>
       </c>
     </row>
     <row r="67">
@@ -4025,28 +4423,34 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>942.6799999999999</v>
+        <v>694998.9</v>
       </c>
       <c r="H67" t="n">
-        <v>2502.36</v>
+        <v>966640.7</v>
       </c>
       <c r="I67" t="n">
-        <v>246.9</v>
+        <v>993305.5</v>
       </c>
       <c r="J67" t="n">
-        <v>24.13</v>
+        <v>348618</v>
       </c>
       <c r="K67" t="n">
-        <v>79.72</v>
+        <v>178790.2</v>
       </c>
       <c r="L67" t="n">
-        <v>1296.09</v>
+        <v>309008.7</v>
       </c>
       <c r="M67" t="n">
-        <v>805.8</v>
+        <v>589774.7</v>
       </c>
       <c r="N67" t="n">
-        <v>200.29</v>
+        <v>446822.1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>746701.4</v>
+      </c>
+      <c r="P67" t="n">
+        <v>498505.8</v>
       </c>
     </row>
     <row r="68">
@@ -4079,28 +4483,34 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>91.33</v>
+        <v>922199.4</v>
       </c>
       <c r="H68" t="n">
-        <v>4809.56</v>
+        <v>730691.9</v>
       </c>
       <c r="I68" t="n">
-        <v>417.98</v>
+        <v>12720.1</v>
       </c>
       <c r="J68" t="n">
-        <v>172.56</v>
+        <v>890901.7</v>
       </c>
       <c r="K68" t="n">
-        <v>1901.57</v>
+        <v>877943.8</v>
       </c>
       <c r="L68" t="n">
-        <v>2998.72</v>
+        <v>382793</v>
       </c>
       <c r="M68" t="n">
-        <v>1680.7</v>
+        <v>745348.8</v>
       </c>
       <c r="N68" t="n">
-        <v>215.61</v>
+        <v>587465.6</v>
+      </c>
+      <c r="O68" t="n">
+        <v>324211.3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>182823.1</v>
       </c>
     </row>
     <row r="69">
@@ -4133,28 +4543,34 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>40.23</v>
+        <v>130926.9</v>
       </c>
       <c r="H69" t="n">
-        <v>3781.34</v>
+        <v>12537.5</v>
       </c>
       <c r="I69" t="n">
-        <v>235.25</v>
+        <v>429715.2</v>
       </c>
       <c r="J69" t="n">
-        <v>195.45</v>
+        <v>691384.8</v>
       </c>
       <c r="K69" t="n">
-        <v>1832.15</v>
+        <v>579238.8</v>
       </c>
       <c r="L69" t="n">
-        <v>544.47</v>
+        <v>669077.9</v>
       </c>
       <c r="M69" t="n">
-        <v>1463.32</v>
+        <v>383664.9</v>
       </c>
       <c r="N69" t="n">
-        <v>507.83</v>
+        <v>546497.3</v>
+      </c>
+      <c r="O69" t="n">
+        <v>858915.2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>181985.8</v>
       </c>
     </row>
     <row r="70">
@@ -4187,28 +4603,34 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>491.73</v>
+        <v>863929.4</v>
       </c>
       <c r="H70" t="n">
-        <v>456.21</v>
+        <v>376836.9</v>
       </c>
       <c r="I70" t="n">
-        <v>173.98</v>
+        <v>938570.5</v>
       </c>
       <c r="J70" t="n">
-        <v>99.98999999999999</v>
+        <v>31907.2</v>
       </c>
       <c r="K70" t="n">
-        <v>1340.27</v>
+        <v>875666.4</v>
       </c>
       <c r="L70" t="n">
-        <v>2573.2</v>
+        <v>838853.6</v>
       </c>
       <c r="M70" t="n">
-        <v>824.51</v>
+        <v>445663.1</v>
       </c>
       <c r="N70" t="n">
-        <v>554.9400000000001</v>
+        <v>456461.7</v>
+      </c>
+      <c r="O70" t="n">
+        <v>239265.2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>386559.8</v>
       </c>
     </row>
     <row r="71">
@@ -4241,28 +4663,34 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>288.22</v>
+        <v>599668</v>
       </c>
       <c r="H71" t="n">
-        <v>4725.97</v>
+        <v>682121.9</v>
       </c>
       <c r="I71" t="n">
-        <v>406.78</v>
+        <v>286880.7</v>
       </c>
       <c r="J71" t="n">
-        <v>165.03</v>
+        <v>329670.3</v>
       </c>
       <c r="K71" t="n">
-        <v>909.65</v>
+        <v>22899.3</v>
       </c>
       <c r="L71" t="n">
-        <v>943.55</v>
+        <v>914309.4</v>
       </c>
       <c r="M71" t="n">
-        <v>808.1799999999999</v>
+        <v>197689.9</v>
       </c>
       <c r="N71" t="n">
-        <v>776.15</v>
+        <v>111694.7</v>
+      </c>
+      <c r="O71" t="n">
+        <v>110404.9</v>
+      </c>
+      <c r="P71" t="n">
+        <v>816368.5</v>
       </c>
     </row>
     <row r="72">
@@ -4295,28 +4723,34 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>404.18</v>
+        <v>747221.3</v>
       </c>
       <c r="H72" t="n">
-        <v>2572.98</v>
+        <v>96966.3</v>
       </c>
       <c r="I72" t="n">
-        <v>494.06</v>
+        <v>837905.5</v>
       </c>
       <c r="J72" t="n">
-        <v>197.3</v>
+        <v>823451.2</v>
       </c>
       <c r="K72" t="n">
-        <v>1085.19</v>
+        <v>61798.3</v>
       </c>
       <c r="L72" t="n">
-        <v>1239.74</v>
+        <v>720400.3</v>
       </c>
       <c r="M72" t="n">
-        <v>468.96</v>
+        <v>604076.8</v>
       </c>
       <c r="N72" t="n">
-        <v>289.42</v>
+        <v>392520</v>
+      </c>
+      <c r="O72" t="n">
+        <v>312211.1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>182067.5</v>
       </c>
     </row>
     <row r="73">
@@ -4349,28 +4783,34 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>756.4400000000001</v>
+        <v>608034.6</v>
       </c>
       <c r="H73" t="n">
-        <v>3127.04</v>
+        <v>794855.9</v>
       </c>
       <c r="I73" t="n">
-        <v>380</v>
+        <v>818952.9</v>
       </c>
       <c r="J73" t="n">
-        <v>61.07</v>
+        <v>536270.9</v>
       </c>
       <c r="K73" t="n">
-        <v>1098.44</v>
+        <v>32941.4</v>
       </c>
       <c r="L73" t="n">
-        <v>2783.02</v>
+        <v>176463.5</v>
       </c>
       <c r="M73" t="n">
-        <v>1095.29</v>
+        <v>308611.1</v>
       </c>
       <c r="N73" t="n">
-        <v>558.6</v>
+        <v>805033.4</v>
+      </c>
+      <c r="O73" t="n">
+        <v>351643.6</v>
+      </c>
+      <c r="P73" t="n">
+        <v>933804.5</v>
       </c>
     </row>
     <row r="74">
@@ -4403,28 +4843,34 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>121.43</v>
+        <v>408299.5</v>
       </c>
       <c r="H74" t="n">
-        <v>4865.73</v>
+        <v>235354.1</v>
       </c>
       <c r="I74" t="n">
-        <v>304.44</v>
+        <v>690717.9</v>
       </c>
       <c r="J74" t="n">
-        <v>71.79000000000001</v>
+        <v>200891.9</v>
       </c>
       <c r="K74" t="n">
-        <v>316.76</v>
+        <v>987064.7</v>
       </c>
       <c r="L74" t="n">
-        <v>1652.52</v>
+        <v>589751.7</v>
       </c>
       <c r="M74" t="n">
-        <v>1380.63</v>
+        <v>788325</v>
       </c>
       <c r="N74" t="n">
-        <v>74.56999999999999</v>
+        <v>745436.2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>66621.2</v>
+      </c>
+      <c r="P74" t="n">
+        <v>494539.4</v>
       </c>
     </row>
     <row r="75">
@@ -4457,28 +4903,34 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>992.26</v>
+        <v>96483.2</v>
       </c>
       <c r="H75" t="n">
-        <v>4564.65</v>
+        <v>443849</v>
       </c>
       <c r="I75" t="n">
-        <v>230.72</v>
+        <v>998315.2</v>
       </c>
       <c r="J75" t="n">
-        <v>35.24</v>
+        <v>414902.3</v>
       </c>
       <c r="K75" t="n">
-        <v>1664.29</v>
+        <v>469309.8</v>
       </c>
       <c r="L75" t="n">
-        <v>1495.13</v>
+        <v>83597.10000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>1791.51</v>
+        <v>867256.3</v>
       </c>
       <c r="N75" t="n">
-        <v>407.1</v>
+        <v>877323.5</v>
+      </c>
+      <c r="O75" t="n">
+        <v>839216.9</v>
+      </c>
+      <c r="P75" t="n">
+        <v>148302.2</v>
       </c>
     </row>
     <row r="76">
@@ -4511,28 +4963,34 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>273.42</v>
+        <v>143662.4</v>
       </c>
       <c r="H76" t="n">
-        <v>4173.62</v>
+        <v>792935.5</v>
       </c>
       <c r="I76" t="n">
-        <v>490.12</v>
+        <v>705663.5</v>
       </c>
       <c r="J76" t="n">
-        <v>73.12</v>
+        <v>676652.3</v>
       </c>
       <c r="K76" t="n">
-        <v>1102.53</v>
+        <v>59725.1</v>
       </c>
       <c r="L76" t="n">
-        <v>1150.76</v>
+        <v>184136.6</v>
       </c>
       <c r="M76" t="n">
-        <v>2304.67</v>
+        <v>867</v>
       </c>
       <c r="N76" t="n">
-        <v>406.59</v>
+        <v>897130</v>
+      </c>
+      <c r="O76" t="n">
+        <v>894264.8</v>
+      </c>
+      <c r="P76" t="n">
+        <v>520786.2</v>
       </c>
     </row>
     <row r="77">
@@ -4565,28 +5023,34 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>879.33</v>
+        <v>174135.1</v>
       </c>
       <c r="H77" t="n">
-        <v>4320.13</v>
+        <v>874196.2</v>
       </c>
       <c r="I77" t="n">
-        <v>138.12</v>
+        <v>104683.4</v>
       </c>
       <c r="J77" t="n">
-        <v>237</v>
+        <v>177554.1</v>
       </c>
       <c r="K77" t="n">
-        <v>829.88</v>
+        <v>287608.4</v>
       </c>
       <c r="L77" t="n">
-        <v>2802.75</v>
+        <v>436951.5</v>
       </c>
       <c r="M77" t="n">
-        <v>1269.34</v>
+        <v>588902.1</v>
       </c>
       <c r="N77" t="n">
-        <v>656.4400000000001</v>
+        <v>850164.9</v>
+      </c>
+      <c r="O77" t="n">
+        <v>999091.5</v>
+      </c>
+      <c r="P77" t="n">
+        <v>263540.5</v>
       </c>
     </row>
     <row r="78">
@@ -4619,28 +5083,34 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>282.84</v>
+        <v>177645.5</v>
       </c>
       <c r="H78" t="n">
-        <v>1492.78</v>
+        <v>80178.8</v>
       </c>
       <c r="I78" t="n">
-        <v>293.47</v>
+        <v>841903.2</v>
       </c>
       <c r="J78" t="n">
-        <v>299.67</v>
+        <v>254061.2</v>
       </c>
       <c r="K78" t="n">
-        <v>979.28</v>
+        <v>353938.8</v>
       </c>
       <c r="L78" t="n">
-        <v>445.79</v>
+        <v>623548.2</v>
       </c>
       <c r="M78" t="n">
-        <v>1346.45</v>
+        <v>339270.4</v>
       </c>
       <c r="N78" t="n">
-        <v>276.1</v>
+        <v>391726.7</v>
+      </c>
+      <c r="O78" t="n">
+        <v>268425.4</v>
+      </c>
+      <c r="P78" t="n">
+        <v>960896.7</v>
       </c>
     </row>
     <row r="79">
@@ -4673,28 +5143,34 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>551.92</v>
+        <v>145511.4</v>
       </c>
       <c r="H79" t="n">
-        <v>2717.15</v>
+        <v>817265.8</v>
       </c>
       <c r="I79" t="n">
-        <v>227.67</v>
+        <v>751757</v>
       </c>
       <c r="J79" t="n">
-        <v>96.53</v>
+        <v>840834.2</v>
       </c>
       <c r="K79" t="n">
-        <v>377.3</v>
+        <v>258878.1</v>
       </c>
       <c r="L79" t="n">
-        <v>2092.5</v>
+        <v>209292.5</v>
       </c>
       <c r="M79" t="n">
-        <v>1429.49</v>
+        <v>253579.6</v>
       </c>
       <c r="N79" t="n">
-        <v>186.85</v>
+        <v>984533.1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>624377</v>
+      </c>
+      <c r="P79" t="n">
+        <v>282669.3</v>
       </c>
     </row>
     <row r="80">
@@ -4727,28 +5203,34 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>775.54</v>
+        <v>207579.3</v>
       </c>
       <c r="H80" t="n">
-        <v>218.24</v>
+        <v>875432.9</v>
       </c>
       <c r="I80" t="n">
-        <v>372.35</v>
+        <v>386152.9</v>
       </c>
       <c r="J80" t="n">
-        <v>211.57</v>
+        <v>389158.9</v>
       </c>
       <c r="K80" t="n">
-        <v>1622.82</v>
+        <v>315019.8</v>
       </c>
       <c r="L80" t="n">
-        <v>1158.24</v>
+        <v>427459.5</v>
       </c>
       <c r="M80" t="n">
-        <v>1659.22</v>
+        <v>240105.2</v>
       </c>
       <c r="N80" t="n">
-        <v>656.6</v>
+        <v>349599.9</v>
+      </c>
+      <c r="O80" t="n">
+        <v>454594</v>
+      </c>
+      <c r="P80" t="n">
+        <v>868847.5</v>
       </c>
     </row>
     <row r="81">
@@ -4781,28 +5263,34 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>980.8200000000001</v>
+        <v>560965.7</v>
       </c>
       <c r="H81" t="n">
-        <v>2476.64</v>
+        <v>838576.9</v>
       </c>
       <c r="I81" t="n">
-        <v>18.51</v>
+        <v>96287.89999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>150.69</v>
+        <v>412458.1</v>
       </c>
       <c r="K81" t="n">
-        <v>1180.36</v>
+        <v>239133.4</v>
       </c>
       <c r="L81" t="n">
-        <v>2609.1</v>
+        <v>298267</v>
       </c>
       <c r="M81" t="n">
-        <v>2185.48</v>
+        <v>304323.4</v>
       </c>
       <c r="N81" t="n">
-        <v>352.24</v>
+        <v>326050.6</v>
+      </c>
+      <c r="O81" t="n">
+        <v>448041.6</v>
+      </c>
+      <c r="P81" t="n">
+        <v>532069.4</v>
       </c>
     </row>
     <row r="82">
@@ -4835,28 +5323,34 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>525.95</v>
+        <v>770567.2</v>
       </c>
       <c r="H82" t="n">
-        <v>2284.64</v>
+        <v>774045.1</v>
       </c>
       <c r="I82" t="n">
-        <v>361.22</v>
+        <v>268979.9</v>
       </c>
       <c r="J82" t="n">
-        <v>122.99</v>
+        <v>989616.2</v>
       </c>
       <c r="K82" t="n">
-        <v>1309.56</v>
+        <v>248382.2</v>
       </c>
       <c r="L82" t="n">
-        <v>463.08</v>
+        <v>106338.6</v>
       </c>
       <c r="M82" t="n">
-        <v>1173.73</v>
+        <v>90617.8</v>
       </c>
       <c r="N82" t="n">
-        <v>775.36</v>
+        <v>168764.1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>610862.5</v>
+      </c>
+      <c r="P82" t="n">
+        <v>822443.1</v>
       </c>
     </row>
     <row r="83">
@@ -4889,28 +5383,34 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>338.56</v>
+        <v>797965.6</v>
       </c>
       <c r="H83" t="n">
-        <v>3463.52</v>
+        <v>373116</v>
       </c>
       <c r="I83" t="n">
-        <v>324.92</v>
+        <v>526386.8</v>
       </c>
       <c r="J83" t="n">
-        <v>255.53</v>
+        <v>958026.1</v>
       </c>
       <c r="K83" t="n">
-        <v>1704.68</v>
+        <v>431595.5</v>
       </c>
       <c r="L83" t="n">
-        <v>2578.03</v>
+        <v>890132</v>
       </c>
       <c r="M83" t="n">
-        <v>950.02</v>
+        <v>128945.7</v>
       </c>
       <c r="N83" t="n">
-        <v>253.33</v>
+        <v>248314.6</v>
+      </c>
+      <c r="O83" t="n">
+        <v>770891.3</v>
+      </c>
+      <c r="P83" t="n">
+        <v>963691.7</v>
       </c>
     </row>
     <row r="84">
@@ -4943,28 +5443,34 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>718.72</v>
+        <v>846125.4</v>
       </c>
       <c r="H84" t="n">
-        <v>3797.01</v>
+        <v>313396.4</v>
       </c>
       <c r="I84" t="n">
-        <v>436.19</v>
+        <v>250190.9</v>
       </c>
       <c r="J84" t="n">
-        <v>10.77</v>
+        <v>303321.5</v>
       </c>
       <c r="K84" t="n">
-        <v>136.84</v>
+        <v>113003.4</v>
       </c>
       <c r="L84" t="n">
-        <v>1893.48</v>
+        <v>828242.7</v>
       </c>
       <c r="M84" t="n">
-        <v>2302.32</v>
+        <v>51590.8</v>
       </c>
       <c r="N84" t="n">
-        <v>797.9400000000001</v>
+        <v>695444.5</v>
+      </c>
+      <c r="O84" t="n">
+        <v>212563.3</v>
+      </c>
+      <c r="P84" t="n">
+        <v>434863.6</v>
       </c>
     </row>
     <row r="85">
@@ -4997,28 +5503,34 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>746.77</v>
+        <v>117213.3</v>
       </c>
       <c r="H85" t="n">
-        <v>2169.86</v>
+        <v>45600.6</v>
       </c>
       <c r="I85" t="n">
-        <v>49.22</v>
+        <v>986692.4</v>
       </c>
       <c r="J85" t="n">
-        <v>190.12</v>
+        <v>111</v>
       </c>
       <c r="K85" t="n">
-        <v>1745.16</v>
+        <v>598254.5</v>
       </c>
       <c r="L85" t="n">
-        <v>1331.04</v>
+        <v>784869.7</v>
       </c>
       <c r="M85" t="n">
-        <v>1735</v>
+        <v>326634.9</v>
       </c>
       <c r="N85" t="n">
-        <v>722.74</v>
+        <v>781486.1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>542531</v>
+      </c>
+      <c r="P85" t="n">
+        <v>940467.2</v>
       </c>
     </row>
     <row r="86">
@@ -5051,28 +5563,34 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>45.99</v>
+        <v>822348.5</v>
       </c>
       <c r="H86" t="n">
-        <v>3980.72</v>
+        <v>396526.5</v>
       </c>
       <c r="I86" t="n">
-        <v>146.68</v>
+        <v>158306.7</v>
       </c>
       <c r="J86" t="n">
-        <v>112.45</v>
+        <v>171909</v>
       </c>
       <c r="K86" t="n">
-        <v>291.14</v>
+        <v>807217.4</v>
       </c>
       <c r="L86" t="n">
-        <v>1593.5</v>
+        <v>144243.7</v>
       </c>
       <c r="M86" t="n">
-        <v>1414.82</v>
+        <v>925497.3</v>
       </c>
       <c r="N86" t="n">
-        <v>634.02</v>
+        <v>57193.4</v>
+      </c>
+      <c r="O86" t="n">
+        <v>873090.5</v>
+      </c>
+      <c r="P86" t="n">
+        <v>200082.1</v>
       </c>
     </row>
     <row r="87">
@@ -5105,28 +5623,34 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>169.98</v>
+        <v>185951.9</v>
       </c>
       <c r="H87" t="n">
-        <v>394.84</v>
+        <v>300637.6</v>
       </c>
       <c r="I87" t="n">
-        <v>435.42</v>
+        <v>274126.6</v>
       </c>
       <c r="J87" t="n">
-        <v>185.91</v>
+        <v>975500</v>
       </c>
       <c r="K87" t="n">
-        <v>481.66</v>
+        <v>175968.8</v>
       </c>
       <c r="L87" t="n">
-        <v>2738.49</v>
+        <v>827231</v>
       </c>
       <c r="M87" t="n">
-        <v>357.79</v>
+        <v>339293.1</v>
       </c>
       <c r="N87" t="n">
-        <v>368.92</v>
+        <v>792303.2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>698955.8</v>
+      </c>
+      <c r="P87" t="n">
+        <v>145984.6</v>
       </c>
     </row>
     <row r="88">
@@ -5159,28 +5683,34 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>253.98</v>
+        <v>72389.39999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>1276.63</v>
+        <v>158828</v>
       </c>
       <c r="I88" t="n">
-        <v>4.7</v>
+        <v>123640.7</v>
       </c>
       <c r="J88" t="n">
-        <v>241.39</v>
+        <v>702359.8</v>
       </c>
       <c r="K88" t="n">
-        <v>1802.42</v>
+        <v>637094.3</v>
       </c>
       <c r="L88" t="n">
-        <v>2032.83</v>
+        <v>928635.1</v>
       </c>
       <c r="M88" t="n">
-        <v>394.94</v>
+        <v>845131.3</v>
       </c>
       <c r="N88" t="n">
-        <v>353.38</v>
+        <v>929490.9</v>
+      </c>
+      <c r="O88" t="n">
+        <v>949698.5</v>
+      </c>
+      <c r="P88" t="n">
+        <v>753235.2</v>
       </c>
     </row>
     <row r="89">
@@ -5213,28 +5743,34 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>345.57</v>
+        <v>287714.3</v>
       </c>
       <c r="H89" t="n">
-        <v>2937.86</v>
+        <v>943643.5</v>
       </c>
       <c r="I89" t="n">
-        <v>319.47</v>
+        <v>748561.9</v>
       </c>
       <c r="J89" t="n">
-        <v>127.29</v>
+        <v>231790.1</v>
       </c>
       <c r="K89" t="n">
-        <v>500.2</v>
+        <v>685829</v>
       </c>
       <c r="L89" t="n">
-        <v>2535.91</v>
+        <v>69044.2</v>
       </c>
       <c r="M89" t="n">
-        <v>498.04</v>
+        <v>181631.9</v>
       </c>
       <c r="N89" t="n">
-        <v>307.75</v>
+        <v>552536.6</v>
+      </c>
+      <c r="O89" t="n">
+        <v>49557.2</v>
+      </c>
+      <c r="P89" t="n">
+        <v>567824.7</v>
       </c>
     </row>
     <row r="90">
@@ -5267,28 +5803,34 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>483.21</v>
+        <v>585692.5</v>
       </c>
       <c r="H90" t="n">
-        <v>1186.03</v>
+        <v>880956</v>
       </c>
       <c r="I90" t="n">
-        <v>285.96</v>
+        <v>828404.7</v>
       </c>
       <c r="J90" t="n">
-        <v>172.44</v>
+        <v>904267.4</v>
       </c>
       <c r="K90" t="n">
-        <v>1985.38</v>
+        <v>316721</v>
       </c>
       <c r="L90" t="n">
-        <v>885.6900000000001</v>
+        <v>246981.5</v>
       </c>
       <c r="M90" t="n">
-        <v>2444.86</v>
+        <v>712715.8</v>
       </c>
       <c r="N90" t="n">
-        <v>526.58</v>
+        <v>114899</v>
+      </c>
+      <c r="O90" t="n">
+        <v>346465.3</v>
+      </c>
+      <c r="P90" t="n">
+        <v>113019.3</v>
       </c>
     </row>
     <row r="91">
@@ -5321,28 +5863,34 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>274.48</v>
+        <v>47677.6</v>
       </c>
       <c r="H91" t="n">
-        <v>2829.65</v>
+        <v>809683.1</v>
       </c>
       <c r="I91" t="n">
-        <v>342.9</v>
+        <v>250812.6</v>
       </c>
       <c r="J91" t="n">
-        <v>223.4</v>
+        <v>877071.3</v>
       </c>
       <c r="K91" t="n">
-        <v>98.09</v>
+        <v>384467.7</v>
       </c>
       <c r="L91" t="n">
-        <v>1819.22</v>
+        <v>292353.8</v>
       </c>
       <c r="M91" t="n">
-        <v>1241.82</v>
+        <v>953393.6</v>
       </c>
       <c r="N91" t="n">
-        <v>723.3200000000001</v>
+        <v>529921.1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>163699.7</v>
+      </c>
+      <c r="P91" t="n">
+        <v>510820.6</v>
       </c>
     </row>
     <row r="92">
@@ -5375,28 +5923,34 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>286.19</v>
+        <v>216322.2</v>
       </c>
       <c r="H92" t="n">
-        <v>3994.3</v>
+        <v>295731.9</v>
       </c>
       <c r="I92" t="n">
-        <v>303.53</v>
+        <v>391157.1</v>
       </c>
       <c r="J92" t="n">
-        <v>105.7</v>
+        <v>712153.5</v>
       </c>
       <c r="K92" t="n">
-        <v>1273.24</v>
+        <v>139732.9</v>
       </c>
       <c r="L92" t="n">
-        <v>1862.67</v>
+        <v>199211</v>
       </c>
       <c r="M92" t="n">
-        <v>1694.41</v>
+        <v>209712.8</v>
       </c>
       <c r="N92" t="n">
-        <v>576.74</v>
+        <v>314304.3</v>
+      </c>
+      <c r="O92" t="n">
+        <v>249593.2</v>
+      </c>
+      <c r="P92" t="n">
+        <v>234076.8</v>
       </c>
     </row>
     <row r="93">
@@ -5429,28 +5983,34 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>659.1799999999999</v>
+        <v>399100.8</v>
       </c>
       <c r="H93" t="n">
-        <v>4191.69</v>
+        <v>123604.9</v>
       </c>
       <c r="I93" t="n">
-        <v>314.12</v>
+        <v>888424</v>
       </c>
       <c r="J93" t="n">
-        <v>271.02</v>
+        <v>17787.6</v>
       </c>
       <c r="K93" t="n">
-        <v>1292.68</v>
+        <v>616037.6</v>
       </c>
       <c r="L93" t="n">
-        <v>926.8</v>
+        <v>560090.3</v>
       </c>
       <c r="M93" t="n">
-        <v>1102.06</v>
+        <v>584281.1</v>
       </c>
       <c r="N93" t="n">
-        <v>463.66</v>
+        <v>597189.1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>480953</v>
+      </c>
+      <c r="P93" t="n">
+        <v>297999.6</v>
       </c>
     </row>
     <row r="94">
@@ -5483,28 +6043,34 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>732.36</v>
+        <v>822367.1</v>
       </c>
       <c r="H94" t="n">
-        <v>450.67</v>
+        <v>427496.4</v>
       </c>
       <c r="I94" t="n">
-        <v>147.56</v>
+        <v>597733.9</v>
       </c>
       <c r="J94" t="n">
-        <v>224.24</v>
+        <v>528567.4</v>
       </c>
       <c r="K94" t="n">
-        <v>351.28</v>
+        <v>978230.2</v>
       </c>
       <c r="L94" t="n">
-        <v>396.48</v>
+        <v>731602.1</v>
       </c>
       <c r="M94" t="n">
-        <v>1348.52</v>
+        <v>725998.7</v>
       </c>
       <c r="N94" t="n">
-        <v>777.1900000000001</v>
+        <v>10038.6</v>
+      </c>
+      <c r="O94" t="n">
+        <v>516864.9</v>
+      </c>
+      <c r="P94" t="n">
+        <v>953352.7</v>
       </c>
     </row>
     <row r="95">
@@ -5537,28 +6103,34 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>530.85</v>
+        <v>399410.1</v>
       </c>
       <c r="H95" t="n">
-        <v>4567.43</v>
+        <v>72300.7</v>
       </c>
       <c r="I95" t="n">
-        <v>415.24</v>
+        <v>217506.3</v>
       </c>
       <c r="J95" t="n">
-        <v>77.09</v>
+        <v>222387.5</v>
       </c>
       <c r="K95" t="n">
-        <v>1649.38</v>
+        <v>776642.6</v>
       </c>
       <c r="L95" t="n">
-        <v>1445.54</v>
+        <v>586666.9</v>
       </c>
       <c r="M95" t="n">
-        <v>2016.22</v>
+        <v>3181.6</v>
       </c>
       <c r="N95" t="n">
-        <v>597.25</v>
+        <v>40611.4</v>
+      </c>
+      <c r="O95" t="n">
+        <v>588858.3</v>
+      </c>
+      <c r="P95" t="n">
+        <v>971764.6</v>
       </c>
     </row>
     <row r="96">
@@ -5591,28 +6163,34 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>338.72</v>
+        <v>414065.2</v>
       </c>
       <c r="H96" t="n">
-        <v>575.85</v>
+        <v>353742</v>
       </c>
       <c r="I96" t="n">
-        <v>481.45</v>
+        <v>996809.4</v>
       </c>
       <c r="J96" t="n">
-        <v>42.23</v>
+        <v>255806</v>
       </c>
       <c r="K96" t="n">
-        <v>1933</v>
+        <v>214672.4</v>
       </c>
       <c r="L96" t="n">
-        <v>2580.42</v>
+        <v>897199</v>
       </c>
       <c r="M96" t="n">
-        <v>1810.54</v>
+        <v>30126.5</v>
       </c>
       <c r="N96" t="n">
-        <v>783.95</v>
+        <v>374735.5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>960598.8</v>
+      </c>
+      <c r="P96" t="n">
+        <v>719475.4</v>
       </c>
     </row>
     <row r="97">
@@ -5645,28 +6223,34 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>967.27</v>
+        <v>370976.6</v>
       </c>
       <c r="H97" t="n">
-        <v>4022.94</v>
+        <v>606479.7</v>
       </c>
       <c r="I97" t="n">
-        <v>182.89</v>
+        <v>769617.3</v>
       </c>
       <c r="J97" t="n">
-        <v>237.2</v>
+        <v>393417.7</v>
       </c>
       <c r="K97" t="n">
-        <v>27.84</v>
+        <v>428113.3</v>
       </c>
       <c r="L97" t="n">
-        <v>1609.72</v>
+        <v>604088.3</v>
       </c>
       <c r="M97" t="n">
-        <v>1136.97</v>
+        <v>431016.5</v>
       </c>
       <c r="N97" t="n">
-        <v>538.26</v>
+        <v>286003</v>
+      </c>
+      <c r="O97" t="n">
+        <v>642366.6</v>
+      </c>
+      <c r="P97" t="n">
+        <v>171597</v>
       </c>
     </row>
     <row r="98">
@@ -5699,28 +6283,34 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>672.34</v>
+        <v>92664.3</v>
       </c>
       <c r="H98" t="n">
-        <v>2922.8</v>
+        <v>317325.9</v>
       </c>
       <c r="I98" t="n">
-        <v>411.21</v>
+        <v>306631.9</v>
       </c>
       <c r="J98" t="n">
-        <v>282.09</v>
+        <v>401097.7</v>
       </c>
       <c r="K98" t="n">
-        <v>216.69</v>
+        <v>509590</v>
       </c>
       <c r="L98" t="n">
-        <v>701.47</v>
+        <v>732328.9</v>
       </c>
       <c r="M98" t="n">
-        <v>62.56</v>
+        <v>258760.2</v>
       </c>
       <c r="N98" t="n">
-        <v>707.39</v>
+        <v>765317.4</v>
+      </c>
+      <c r="O98" t="n">
+        <v>547355.9</v>
+      </c>
+      <c r="P98" t="n">
+        <v>233070.6</v>
       </c>
     </row>
     <row r="99">
@@ -5753,28 +6343,34 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>561.41</v>
+        <v>879568.4</v>
       </c>
       <c r="H99" t="n">
-        <v>4576.28</v>
+        <v>334534.4</v>
       </c>
       <c r="I99" t="n">
-        <v>110.68</v>
+        <v>447876.8</v>
       </c>
       <c r="J99" t="n">
-        <v>18.97</v>
+        <v>884223.3</v>
       </c>
       <c r="K99" t="n">
-        <v>1647.71</v>
+        <v>280787.8</v>
       </c>
       <c r="L99" t="n">
-        <v>2728.16</v>
+        <v>448594.7</v>
       </c>
       <c r="M99" t="n">
-        <v>755.48</v>
+        <v>371067.4</v>
       </c>
       <c r="N99" t="n">
-        <v>326.64</v>
+        <v>70632.7</v>
+      </c>
+      <c r="O99" t="n">
+        <v>52707.8</v>
+      </c>
+      <c r="P99" t="n">
+        <v>750894.4</v>
       </c>
     </row>
     <row r="100">
@@ -5807,28 +6403,34 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>139.78</v>
+        <v>923036.2</v>
       </c>
       <c r="H100" t="n">
-        <v>4731.31</v>
+        <v>326954.9</v>
       </c>
       <c r="I100" t="n">
-        <v>152.18</v>
+        <v>500104.6</v>
       </c>
       <c r="J100" t="n">
-        <v>147.79</v>
+        <v>374539.4</v>
       </c>
       <c r="K100" t="n">
-        <v>194.38</v>
+        <v>963246.6</v>
       </c>
       <c r="L100" t="n">
-        <v>2661.78</v>
+        <v>743294.5</v>
       </c>
       <c r="M100" t="n">
-        <v>339.16</v>
+        <v>536404.4</v>
       </c>
       <c r="N100" t="n">
-        <v>362.92</v>
+        <v>135532.8</v>
+      </c>
+      <c r="O100" t="n">
+        <v>881133.5</v>
+      </c>
+      <c r="P100" t="n">
+        <v>527822.7</v>
       </c>
     </row>
     <row r="101">
@@ -5861,28 +6463,34 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>670.49</v>
+        <v>721660</v>
       </c>
       <c r="H101" t="n">
-        <v>3715.7</v>
+        <v>829046.4</v>
       </c>
       <c r="I101" t="n">
-        <v>472.99</v>
+        <v>634518.4</v>
       </c>
       <c r="J101" t="n">
-        <v>125.74</v>
+        <v>165916.6</v>
       </c>
       <c r="K101" t="n">
-        <v>1484.54</v>
+        <v>878145.3</v>
       </c>
       <c r="L101" t="n">
-        <v>463.57</v>
+        <v>141742.8</v>
       </c>
       <c r="M101" t="n">
-        <v>1037.21</v>
+        <v>778101.9</v>
       </c>
       <c r="N101" t="n">
-        <v>79.22</v>
+        <v>656865.8</v>
+      </c>
+      <c r="O101" t="n">
+        <v>315015.8</v>
+      </c>
+      <c r="P101" t="n">
+        <v>467335.7</v>
       </c>
     </row>
     <row r="102">
@@ -5915,28 +6523,34 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>489.35</v>
+        <v>398579.9</v>
       </c>
       <c r="H102" t="n">
-        <v>2040.58</v>
+        <v>34566.8</v>
       </c>
       <c r="I102" t="n">
-        <v>475.76</v>
+        <v>459447.1</v>
       </c>
       <c r="J102" t="n">
-        <v>9.81</v>
+        <v>155761.2</v>
       </c>
       <c r="K102" t="n">
-        <v>741.0599999999999</v>
+        <v>446316</v>
       </c>
       <c r="L102" t="n">
-        <v>1330.15</v>
+        <v>464159.8</v>
       </c>
       <c r="M102" t="n">
-        <v>2376.39</v>
+        <v>247908.5</v>
       </c>
       <c r="N102" t="n">
-        <v>684.36</v>
+        <v>706512.3</v>
+      </c>
+      <c r="O102" t="n">
+        <v>556416</v>
+      </c>
+      <c r="P102" t="n">
+        <v>318754.6</v>
       </c>
     </row>
     <row r="103">
@@ -5969,28 +6583,34 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>99.34999999999999</v>
+        <v>443973.8</v>
       </c>
       <c r="H103" t="n">
-        <v>3428.4</v>
+        <v>813889.2</v>
       </c>
       <c r="I103" t="n">
-        <v>272.23</v>
+        <v>149016.9</v>
       </c>
       <c r="J103" t="n">
-        <v>293.35</v>
+        <v>463659</v>
       </c>
       <c r="K103" t="n">
-        <v>717.35</v>
+        <v>226718.1</v>
       </c>
       <c r="L103" t="n">
-        <v>1194.42</v>
+        <v>252633.1</v>
       </c>
       <c r="M103" t="n">
-        <v>474.52</v>
+        <v>840866.4</v>
       </c>
       <c r="N103" t="n">
-        <v>97.73</v>
+        <v>947265</v>
+      </c>
+      <c r="O103" t="n">
+        <v>168527.5</v>
+      </c>
+      <c r="P103" t="n">
+        <v>938334.9</v>
       </c>
     </row>
     <row r="104">
@@ -6023,28 +6643,34 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>848.03</v>
+        <v>311418.8</v>
       </c>
       <c r="H104" t="n">
-        <v>2273.59</v>
+        <v>610272.6</v>
       </c>
       <c r="I104" t="n">
-        <v>331.38</v>
+        <v>329118.5</v>
       </c>
       <c r="J104" t="n">
-        <v>192.51</v>
+        <v>277626.3</v>
       </c>
       <c r="K104" t="n">
-        <v>1194.29</v>
+        <v>752665</v>
       </c>
       <c r="L104" t="n">
-        <v>64.06999999999999</v>
+        <v>373775.3</v>
       </c>
       <c r="M104" t="n">
-        <v>1966.99</v>
+        <v>273902.3</v>
       </c>
       <c r="N104" t="n">
-        <v>194.86</v>
+        <v>682703.6</v>
+      </c>
+      <c r="O104" t="n">
+        <v>710295.5</v>
+      </c>
+      <c r="P104" t="n">
+        <v>248726.2</v>
       </c>
     </row>
     <row r="105">
@@ -6077,28 +6703,34 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>125.92</v>
+        <v>654334.1</v>
       </c>
       <c r="H105" t="n">
-        <v>2822.89</v>
+        <v>547976.4</v>
       </c>
       <c r="I105" t="n">
-        <v>34.31</v>
+        <v>128751.5</v>
       </c>
       <c r="J105" t="n">
-        <v>229.55</v>
+        <v>839363.3</v>
       </c>
       <c r="K105" t="n">
-        <v>414.31</v>
+        <v>518580.9</v>
       </c>
       <c r="L105" t="n">
-        <v>647.85</v>
+        <v>379575.7</v>
       </c>
       <c r="M105" t="n">
-        <v>2174.24</v>
+        <v>667320.6</v>
       </c>
       <c r="N105" t="n">
-        <v>262.85</v>
+        <v>197785.6</v>
+      </c>
+      <c r="O105" t="n">
+        <v>217356.7</v>
+      </c>
+      <c r="P105" t="n">
+        <v>402312.9</v>
       </c>
     </row>
     <row r="106">
@@ -6131,28 +6763,34 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>147.55</v>
+        <v>653363.7</v>
       </c>
       <c r="H106" t="n">
-        <v>4502.66</v>
+        <v>693631.4</v>
       </c>
       <c r="I106" t="n">
-        <v>1.42</v>
+        <v>502491.7</v>
       </c>
       <c r="J106" t="n">
-        <v>257.52</v>
+        <v>629839.1</v>
       </c>
       <c r="K106" t="n">
-        <v>289.38</v>
+        <v>714879.7</v>
       </c>
       <c r="L106" t="n">
-        <v>389.98</v>
+        <v>75402.89999999999</v>
       </c>
       <c r="M106" t="n">
-        <v>626.64</v>
+        <v>889363</v>
       </c>
       <c r="N106" t="n">
-        <v>139.6</v>
+        <v>279583.5</v>
+      </c>
+      <c r="O106" t="n">
+        <v>688686.4</v>
+      </c>
+      <c r="P106" t="n">
+        <v>105204.5</v>
       </c>
     </row>
     <row r="107">
@@ -6185,28 +6823,34 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>661.0599999999999</v>
+        <v>310656.4</v>
       </c>
       <c r="H107" t="n">
-        <v>128.9</v>
+        <v>18541.4</v>
       </c>
       <c r="I107" t="n">
-        <v>7.43</v>
+        <v>613652.9</v>
       </c>
       <c r="J107" t="n">
-        <v>237</v>
+        <v>731517.4</v>
       </c>
       <c r="K107" t="n">
-        <v>475.86</v>
+        <v>874613</v>
       </c>
       <c r="L107" t="n">
-        <v>971.3099999999999</v>
+        <v>514835.2</v>
       </c>
       <c r="M107" t="n">
-        <v>435.62</v>
+        <v>107047.9</v>
       </c>
       <c r="N107" t="n">
-        <v>41.92</v>
+        <v>742508.2</v>
+      </c>
+      <c r="O107" t="n">
+        <v>783565.3</v>
+      </c>
+      <c r="P107" t="n">
+        <v>911970.2</v>
       </c>
     </row>
     <row r="108">
@@ -6239,28 +6883,34 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>741.72</v>
+        <v>874230.2</v>
       </c>
       <c r="H108" t="n">
-        <v>2630.43</v>
+        <v>863096.3</v>
       </c>
       <c r="I108" t="n">
-        <v>372.83</v>
+        <v>601870.2</v>
       </c>
       <c r="J108" t="n">
-        <v>142.87</v>
+        <v>177343.8</v>
       </c>
       <c r="K108" t="n">
-        <v>1556.03</v>
+        <v>971583.3</v>
       </c>
       <c r="L108" t="n">
-        <v>1539.71</v>
+        <v>213794.2</v>
       </c>
       <c r="M108" t="n">
-        <v>272.64</v>
+        <v>949372</v>
       </c>
       <c r="N108" t="n">
-        <v>403.07</v>
+        <v>505311.9</v>
+      </c>
+      <c r="O108" t="n">
+        <v>591108.9</v>
+      </c>
+      <c r="P108" t="n">
+        <v>672401.4</v>
       </c>
     </row>
     <row r="109">
@@ -6293,28 +6943,34 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>945.42</v>
+        <v>720725.2</v>
       </c>
       <c r="H109" t="n">
-        <v>216.83</v>
+        <v>288774.3</v>
       </c>
       <c r="I109" t="n">
-        <v>391.61</v>
+        <v>70572.10000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>260.09</v>
+        <v>566790</v>
       </c>
       <c r="K109" t="n">
-        <v>1042.9</v>
+        <v>784904.9</v>
       </c>
       <c r="L109" t="n">
-        <v>1374.13</v>
+        <v>519834.9</v>
       </c>
       <c r="M109" t="n">
-        <v>2410.07</v>
+        <v>1767.2</v>
       </c>
       <c r="N109" t="n">
-        <v>48.66</v>
+        <v>14012.7</v>
+      </c>
+      <c r="O109" t="n">
+        <v>262498.3</v>
+      </c>
+      <c r="P109" t="n">
+        <v>160603.4</v>
       </c>
     </row>
     <row r="110">
@@ -6347,28 +7003,34 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>478.98</v>
+        <v>218604</v>
       </c>
       <c r="H110" t="n">
-        <v>2008.09</v>
+        <v>399543.9</v>
       </c>
       <c r="I110" t="n">
-        <v>343.05</v>
+        <v>555785.5</v>
       </c>
       <c r="J110" t="n">
-        <v>147.08</v>
+        <v>690741.2</v>
       </c>
       <c r="K110" t="n">
-        <v>1819.4</v>
+        <v>205225.2</v>
       </c>
       <c r="L110" t="n">
-        <v>220.47</v>
+        <v>534106.4</v>
       </c>
       <c r="M110" t="n">
-        <v>201.98</v>
+        <v>82036.60000000001</v>
       </c>
       <c r="N110" t="n">
-        <v>486.64</v>
+        <v>558768.1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>829608.4</v>
+      </c>
+      <c r="P110" t="n">
+        <v>787262.5</v>
       </c>
     </row>
     <row r="111">
@@ -6401,28 +7063,34 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>65.68000000000001</v>
+        <v>809273.9</v>
       </c>
       <c r="H111" t="n">
-        <v>1375.08</v>
+        <v>512272.3</v>
       </c>
       <c r="I111" t="n">
-        <v>316.54</v>
+        <v>781355.6</v>
       </c>
       <c r="J111" t="n">
-        <v>164.51</v>
+        <v>48253.5</v>
       </c>
       <c r="K111" t="n">
-        <v>650.37</v>
+        <v>553705.2</v>
       </c>
       <c r="L111" t="n">
-        <v>2983.88</v>
+        <v>442253</v>
       </c>
       <c r="M111" t="n">
-        <v>1326.39</v>
+        <v>608948.6</v>
       </c>
       <c r="N111" t="n">
-        <v>362.97</v>
+        <v>414138.4</v>
+      </c>
+      <c r="O111" t="n">
+        <v>942634.1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>948789.1</v>
       </c>
     </row>
     <row r="112">
@@ -6455,28 +7123,34 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>605.4299999999999</v>
+        <v>674296.8</v>
       </c>
       <c r="H112" t="n">
-        <v>495.89</v>
+        <v>901241.7</v>
       </c>
       <c r="I112" t="n">
-        <v>350.89</v>
+        <v>572911.8</v>
       </c>
       <c r="J112" t="n">
-        <v>255.84</v>
+        <v>398941.8</v>
       </c>
       <c r="K112" t="n">
-        <v>1301.83</v>
+        <v>717720</v>
       </c>
       <c r="L112" t="n">
-        <v>2306.89</v>
+        <v>876989.2</v>
       </c>
       <c r="M112" t="n">
-        <v>1802.1</v>
+        <v>605878.7</v>
       </c>
       <c r="N112" t="n">
-        <v>172.02</v>
+        <v>706237.4</v>
+      </c>
+      <c r="O112" t="n">
+        <v>31097.2</v>
+      </c>
+      <c r="P112" t="n">
+        <v>459062.8</v>
       </c>
     </row>
     <row r="113">
@@ -6509,28 +7183,34 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>451.55</v>
+        <v>249720.6</v>
       </c>
       <c r="H113" t="n">
-        <v>1142.47</v>
+        <v>227829.4</v>
       </c>
       <c r="I113" t="n">
-        <v>169.47</v>
+        <v>337759.5</v>
       </c>
       <c r="J113" t="n">
-        <v>136.05</v>
+        <v>668103.3</v>
       </c>
       <c r="K113" t="n">
-        <v>831.98</v>
+        <v>174737.9</v>
       </c>
       <c r="L113" t="n">
-        <v>285.26</v>
+        <v>531471.7</v>
       </c>
       <c r="M113" t="n">
-        <v>1066.91</v>
+        <v>917096.3</v>
       </c>
       <c r="N113" t="n">
-        <v>532.09</v>
+        <v>26747.6</v>
+      </c>
+      <c r="O113" t="n">
+        <v>805093.5</v>
+      </c>
+      <c r="P113" t="n">
+        <v>688044.4</v>
       </c>
     </row>
     <row r="114">
@@ -6563,28 +7243,34 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>374.3</v>
+        <v>296376.7</v>
       </c>
       <c r="H114" t="n">
-        <v>763.1900000000001</v>
+        <v>524119.5</v>
       </c>
       <c r="I114" t="n">
-        <v>461.49</v>
+        <v>785405.5</v>
       </c>
       <c r="J114" t="n">
-        <v>20.14</v>
+        <v>153348.4</v>
       </c>
       <c r="K114" t="n">
-        <v>1663.54</v>
+        <v>989181.8</v>
       </c>
       <c r="L114" t="n">
-        <v>279.69</v>
+        <v>674482.8</v>
       </c>
       <c r="M114" t="n">
-        <v>241.41</v>
+        <v>662784.7</v>
       </c>
       <c r="N114" t="n">
-        <v>591.04</v>
+        <v>558561.3</v>
+      </c>
+      <c r="O114" t="n">
+        <v>781576</v>
+      </c>
+      <c r="P114" t="n">
+        <v>546420.1</v>
       </c>
     </row>
     <row r="115">
@@ -6617,28 +7303,34 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>811.77</v>
+        <v>751506.3</v>
       </c>
       <c r="H115" t="n">
-        <v>2781.85</v>
+        <v>991640.9</v>
       </c>
       <c r="I115" t="n">
-        <v>293.23</v>
+        <v>399549.8</v>
       </c>
       <c r="J115" t="n">
-        <v>168.48</v>
+        <v>957090.6</v>
       </c>
       <c r="K115" t="n">
-        <v>659.29</v>
+        <v>272051.4</v>
       </c>
       <c r="L115" t="n">
-        <v>366.69</v>
+        <v>936031.1</v>
       </c>
       <c r="M115" t="n">
-        <v>884</v>
+        <v>182259.7</v>
       </c>
       <c r="N115" t="n">
-        <v>532.27</v>
+        <v>916126.1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>801861.1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>796188.9</v>
       </c>
     </row>
     <row r="116">
@@ -6671,28 +7363,34 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>750.28</v>
+        <v>80127.10000000001</v>
       </c>
       <c r="H116" t="n">
-        <v>4340.46</v>
+        <v>212162.9</v>
       </c>
       <c r="I116" t="n">
-        <v>360.53</v>
+        <v>793431.4</v>
       </c>
       <c r="J116" t="n">
-        <v>290.52</v>
+        <v>211996.3</v>
       </c>
       <c r="K116" t="n">
-        <v>1200.82</v>
+        <v>848400.5</v>
       </c>
       <c r="L116" t="n">
-        <v>1054.94</v>
+        <v>441653.8</v>
       </c>
       <c r="M116" t="n">
-        <v>1444.8</v>
+        <v>540460.9</v>
       </c>
       <c r="N116" t="n">
-        <v>170.19</v>
+        <v>536055.6</v>
+      </c>
+      <c r="O116" t="n">
+        <v>526395.6</v>
+      </c>
+      <c r="P116" t="n">
+        <v>916220.1</v>
       </c>
     </row>
     <row r="117">
@@ -6725,28 +7423,34 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>656.74</v>
+        <v>437815.8</v>
       </c>
       <c r="H117" t="n">
-        <v>1121.22</v>
+        <v>647806</v>
       </c>
       <c r="I117" t="n">
-        <v>54.11</v>
+        <v>10543.8</v>
       </c>
       <c r="J117" t="n">
-        <v>253.61</v>
+        <v>117715.3</v>
       </c>
       <c r="K117" t="n">
-        <v>735.12</v>
+        <v>14766</v>
       </c>
       <c r="L117" t="n">
-        <v>2287.82</v>
+        <v>863401.2</v>
       </c>
       <c r="M117" t="n">
-        <v>1435.25</v>
+        <v>967316.9</v>
       </c>
       <c r="N117" t="n">
-        <v>645.78</v>
+        <v>394655.3</v>
+      </c>
+      <c r="O117" t="n">
+        <v>146995.8</v>
+      </c>
+      <c r="P117" t="n">
+        <v>35712.1</v>
       </c>
     </row>
     <row r="118">
@@ -6779,28 +7483,34 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>845.16</v>
+        <v>963806.7</v>
       </c>
       <c r="H118" t="n">
-        <v>4872.73</v>
+        <v>163835.4</v>
       </c>
       <c r="I118" t="n">
-        <v>409.21</v>
+        <v>88423.10000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>184.07</v>
+        <v>687645.1</v>
       </c>
       <c r="K118" t="n">
-        <v>1285.4</v>
+        <v>87078.5</v>
       </c>
       <c r="L118" t="n">
-        <v>78.76000000000001</v>
+        <v>410353.8</v>
       </c>
       <c r="M118" t="n">
-        <v>2322.71</v>
+        <v>821626.3</v>
       </c>
       <c r="N118" t="n">
-        <v>663.5700000000001</v>
+        <v>188902.9</v>
+      </c>
+      <c r="O118" t="n">
+        <v>360788.9</v>
+      </c>
+      <c r="P118" t="n">
+        <v>207417.2</v>
       </c>
     </row>
     <row r="119">
@@ -6833,28 +7543,34 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>267.45</v>
+        <v>256212.5</v>
       </c>
       <c r="H119" t="n">
-        <v>902.08</v>
+        <v>567181.4</v>
       </c>
       <c r="I119" t="n">
-        <v>351.35</v>
+        <v>457899</v>
       </c>
       <c r="J119" t="n">
-        <v>92.7</v>
+        <v>985376.5</v>
       </c>
       <c r="K119" t="n">
-        <v>679.65</v>
+        <v>15708.3</v>
       </c>
       <c r="L119" t="n">
-        <v>18.32</v>
+        <v>18473.6</v>
       </c>
       <c r="M119" t="n">
-        <v>2174.66</v>
+        <v>714663.9</v>
       </c>
       <c r="N119" t="n">
-        <v>453.06</v>
+        <v>133599</v>
+      </c>
+      <c r="O119" t="n">
+        <v>688026.4</v>
+      </c>
+      <c r="P119" t="n">
+        <v>92145.7</v>
       </c>
     </row>
     <row r="120">
@@ -6887,28 +7603,34 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>400.78</v>
+        <v>503150.7</v>
       </c>
       <c r="H120" t="n">
-        <v>709.37</v>
+        <v>434711.4</v>
       </c>
       <c r="I120" t="n">
-        <v>316.59</v>
+        <v>83659.10000000001</v>
       </c>
       <c r="J120" t="n">
-        <v>9.199999999999999</v>
+        <v>773148.4</v>
       </c>
       <c r="K120" t="n">
-        <v>1492.22</v>
+        <v>87610.60000000001</v>
       </c>
       <c r="L120" t="n">
-        <v>645.4</v>
+        <v>224997.2</v>
       </c>
       <c r="M120" t="n">
-        <v>1049.58</v>
+        <v>249815.9</v>
       </c>
       <c r="N120" t="n">
-        <v>272.72</v>
+        <v>434531.3</v>
+      </c>
+      <c r="O120" t="n">
+        <v>669561.2</v>
+      </c>
+      <c r="P120" t="n">
+        <v>141531.4</v>
       </c>
     </row>
     <row r="121">
@@ -6941,28 +7663,34 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>370.05</v>
+        <v>907205.7</v>
       </c>
       <c r="H121" t="n">
-        <v>3607.98</v>
+        <v>565561.6</v>
       </c>
       <c r="I121" t="n">
-        <v>388.42</v>
+        <v>195102.6</v>
       </c>
       <c r="J121" t="n">
-        <v>170.28</v>
+        <v>531970.1</v>
       </c>
       <c r="K121" t="n">
-        <v>169.91</v>
+        <v>74517.2</v>
       </c>
       <c r="L121" t="n">
-        <v>157.83</v>
+        <v>248168.8</v>
       </c>
       <c r="M121" t="n">
-        <v>393.52</v>
+        <v>441580.8</v>
       </c>
       <c r="N121" t="n">
-        <v>494.27</v>
+        <v>412509.6</v>
+      </c>
+      <c r="O121" t="n">
+        <v>92964.8</v>
+      </c>
+      <c r="P121" t="n">
+        <v>116301.1</v>
       </c>
     </row>
     <row r="122">
@@ -6995,28 +7723,34 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>673.97</v>
+        <v>874593.1</v>
       </c>
       <c r="H122" t="n">
-        <v>1360.51</v>
+        <v>28715</v>
       </c>
       <c r="I122" t="n">
-        <v>330.97</v>
+        <v>933219</v>
       </c>
       <c r="J122" t="n">
-        <v>145.7</v>
+        <v>328497.3</v>
       </c>
       <c r="K122" t="n">
-        <v>884.09</v>
+        <v>78971.2</v>
       </c>
       <c r="L122" t="n">
-        <v>819.5</v>
+        <v>648096</v>
       </c>
       <c r="M122" t="n">
-        <v>1887.36</v>
+        <v>581017</v>
       </c>
       <c r="N122" t="n">
-        <v>91.05</v>
+        <v>572156.5</v>
+      </c>
+      <c r="O122" t="n">
+        <v>29007.8</v>
+      </c>
+      <c r="P122" t="n">
+        <v>594465.9</v>
       </c>
     </row>
     <row r="123">
@@ -7049,28 +7783,34 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>429.91</v>
+        <v>788204.2</v>
       </c>
       <c r="H123" t="n">
-        <v>1416.23</v>
+        <v>202036.1</v>
       </c>
       <c r="I123" t="n">
-        <v>339.24</v>
+        <v>776684</v>
       </c>
       <c r="J123" t="n">
-        <v>145.99</v>
+        <v>215534.9</v>
       </c>
       <c r="K123" t="n">
-        <v>1334.27</v>
+        <v>723258.7</v>
       </c>
       <c r="L123" t="n">
-        <v>136.25</v>
+        <v>171401.9</v>
       </c>
       <c r="M123" t="n">
-        <v>988.16</v>
+        <v>125211.6</v>
       </c>
       <c r="N123" t="n">
-        <v>479.46</v>
+        <v>95685.60000000001</v>
+      </c>
+      <c r="O123" t="n">
+        <v>115616.8</v>
+      </c>
+      <c r="P123" t="n">
+        <v>128606.3</v>
       </c>
     </row>
     <row r="124">
@@ -7103,28 +7843,34 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>7.69</v>
+        <v>533244.1</v>
       </c>
       <c r="H124" t="n">
-        <v>1507.1</v>
+        <v>900570.4</v>
       </c>
       <c r="I124" t="n">
-        <v>105.62</v>
+        <v>298718.9</v>
       </c>
       <c r="J124" t="n">
-        <v>41.17</v>
+        <v>64379.4</v>
       </c>
       <c r="K124" t="n">
-        <v>511.04</v>
+        <v>920534.8</v>
       </c>
       <c r="L124" t="n">
-        <v>984.37</v>
+        <v>648701.7</v>
       </c>
       <c r="M124" t="n">
-        <v>19.32</v>
+        <v>402417.7</v>
       </c>
       <c r="N124" t="n">
-        <v>597.61</v>
+        <v>350132.2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>783772.7</v>
+      </c>
+      <c r="P124" t="n">
+        <v>946046</v>
       </c>
     </row>
     <row r="125">
@@ -7157,28 +7903,34 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>175.69</v>
+        <v>929830.8</v>
       </c>
       <c r="H125" t="n">
-        <v>1901.04</v>
+        <v>179747.6</v>
       </c>
       <c r="I125" t="n">
-        <v>351.84</v>
+        <v>114532.3</v>
       </c>
       <c r="J125" t="n">
-        <v>150.08</v>
+        <v>223841.4</v>
       </c>
       <c r="K125" t="n">
-        <v>1666.71</v>
+        <v>797190.2</v>
       </c>
       <c r="L125" t="n">
-        <v>2418.6</v>
+        <v>313115.7</v>
       </c>
       <c r="M125" t="n">
-        <v>180.19</v>
+        <v>448198.8</v>
       </c>
       <c r="N125" t="n">
-        <v>689.41</v>
+        <v>838577.8</v>
+      </c>
+      <c r="O125" t="n">
+        <v>25286.1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>302739.5</v>
       </c>
     </row>
     <row r="126">
@@ -7211,28 +7963,34 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>42.3</v>
+        <v>256835.8</v>
       </c>
       <c r="H126" t="n">
-        <v>93.70999999999999</v>
+        <v>300471.4</v>
       </c>
       <c r="I126" t="n">
-        <v>460.58</v>
+        <v>731395.5</v>
       </c>
       <c r="J126" t="n">
-        <v>258.63</v>
+        <v>628687.1</v>
       </c>
       <c r="K126" t="n">
-        <v>1151.52</v>
+        <v>818286.2</v>
       </c>
       <c r="L126" t="n">
-        <v>1720.2</v>
+        <v>650191.4</v>
       </c>
       <c r="M126" t="n">
-        <v>1773.75</v>
+        <v>382953.9</v>
       </c>
       <c r="N126" t="n">
-        <v>334.16</v>
+        <v>109021.6</v>
+      </c>
+      <c r="O126" t="n">
+        <v>83981.3</v>
+      </c>
+      <c r="P126" t="n">
+        <v>619884.3</v>
       </c>
     </row>
     <row r="127">
@@ -7265,28 +8023,34 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>115.17</v>
+        <v>881578.9</v>
       </c>
       <c r="H127" t="n">
-        <v>104.28</v>
+        <v>989201.8</v>
       </c>
       <c r="I127" t="n">
-        <v>162.38</v>
+        <v>708073.9</v>
       </c>
       <c r="J127" t="n">
-        <v>240.4</v>
+        <v>247366.7</v>
       </c>
       <c r="K127" t="n">
-        <v>1236.25</v>
+        <v>779244.9</v>
       </c>
       <c r="L127" t="n">
-        <v>2496.08</v>
+        <v>906976.7</v>
       </c>
       <c r="M127" t="n">
-        <v>2299.42</v>
+        <v>772864.3</v>
       </c>
       <c r="N127" t="n">
-        <v>70.5</v>
+        <v>227845.4</v>
+      </c>
+      <c r="O127" t="n">
+        <v>95399.89999999999</v>
+      </c>
+      <c r="P127" t="n">
+        <v>51918.2</v>
       </c>
     </row>
     <row r="128">
@@ -7319,28 +8083,34 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>844.48</v>
+        <v>409332.5</v>
       </c>
       <c r="H128" t="n">
-        <v>1216.58</v>
+        <v>254598.9</v>
       </c>
       <c r="I128" t="n">
-        <v>294.44</v>
+        <v>173232.9</v>
       </c>
       <c r="J128" t="n">
-        <v>157.19</v>
+        <v>988479.7</v>
       </c>
       <c r="K128" t="n">
-        <v>791.53</v>
+        <v>174123.5</v>
       </c>
       <c r="L128" t="n">
-        <v>930.8200000000001</v>
+        <v>658375.5</v>
       </c>
       <c r="M128" t="n">
-        <v>848.78</v>
+        <v>260860.1</v>
       </c>
       <c r="N128" t="n">
-        <v>266.45</v>
+        <v>838647.1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>49221.2</v>
+      </c>
+      <c r="P128" t="n">
+        <v>557829.9</v>
       </c>
     </row>
     <row r="129">
@@ -7373,28 +8143,34 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>168.13</v>
+        <v>658217.4</v>
       </c>
       <c r="H129" t="n">
-        <v>2552.42</v>
+        <v>579754.2</v>
       </c>
       <c r="I129" t="n">
-        <v>57.01</v>
+        <v>554971.5</v>
       </c>
       <c r="J129" t="n">
-        <v>152.99</v>
+        <v>156703.6</v>
       </c>
       <c r="K129" t="n">
-        <v>1811.85</v>
+        <v>385407.4</v>
       </c>
       <c r="L129" t="n">
-        <v>1048.13</v>
+        <v>696818</v>
       </c>
       <c r="M129" t="n">
-        <v>1818.45</v>
+        <v>490714.4</v>
       </c>
       <c r="N129" t="n">
-        <v>655.16</v>
+        <v>238451.3</v>
+      </c>
+      <c r="O129" t="n">
+        <v>103523.2</v>
+      </c>
+      <c r="P129" t="n">
+        <v>328109.3</v>
       </c>
     </row>
     <row r="130">
@@ -7427,28 +8203,34 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>815.04</v>
+        <v>611003.6</v>
       </c>
       <c r="H130" t="n">
-        <v>1181.34</v>
+        <v>430628.8</v>
       </c>
       <c r="I130" t="n">
-        <v>73.22</v>
+        <v>641152.6</v>
       </c>
       <c r="J130" t="n">
-        <v>59.18</v>
+        <v>244476.2</v>
       </c>
       <c r="K130" t="n">
-        <v>1204.8</v>
+        <v>46906.9</v>
       </c>
       <c r="L130" t="n">
-        <v>2280.65</v>
+        <v>584870.4</v>
       </c>
       <c r="M130" t="n">
-        <v>1638.77</v>
+        <v>945636.8</v>
       </c>
       <c r="N130" t="n">
-        <v>141.72</v>
+        <v>393567.4</v>
+      </c>
+      <c r="O130" t="n">
+        <v>803920</v>
+      </c>
+      <c r="P130" t="n">
+        <v>966207.7</v>
       </c>
     </row>
     <row r="131">
@@ -7481,28 +8263,34 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>772.85</v>
+        <v>282290.9</v>
       </c>
       <c r="H131" t="n">
-        <v>2470.59</v>
+        <v>3219.6</v>
       </c>
       <c r="I131" t="n">
-        <v>377.22</v>
+        <v>88997.5</v>
       </c>
       <c r="J131" t="n">
-        <v>227.96</v>
+        <v>407569.2</v>
       </c>
       <c r="K131" t="n">
-        <v>897.8099999999999</v>
+        <v>179698.1</v>
       </c>
       <c r="L131" t="n">
-        <v>2772.46</v>
+        <v>572467.6</v>
       </c>
       <c r="M131" t="n">
-        <v>1411.23</v>
+        <v>601940.3</v>
       </c>
       <c r="N131" t="n">
-        <v>508.24</v>
+        <v>610152.4</v>
+      </c>
+      <c r="O131" t="n">
+        <v>982363.1</v>
+      </c>
+      <c r="P131" t="n">
+        <v>652578.9</v>
       </c>
     </row>
     <row r="132">
@@ -7535,28 +8323,34 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>624.52</v>
+        <v>678242.4</v>
       </c>
       <c r="H132" t="n">
-        <v>4321.23</v>
+        <v>643571.2</v>
       </c>
       <c r="I132" t="n">
-        <v>313.61</v>
+        <v>111559.5</v>
       </c>
       <c r="J132" t="n">
-        <v>45.29</v>
+        <v>953856.8</v>
       </c>
       <c r="K132" t="n">
-        <v>136.57</v>
+        <v>195941.3</v>
       </c>
       <c r="L132" t="n">
-        <v>1326.62</v>
+        <v>479249.8</v>
       </c>
       <c r="M132" t="n">
-        <v>757.05</v>
+        <v>520076</v>
       </c>
       <c r="N132" t="n">
-        <v>219.74</v>
+        <v>924288</v>
+      </c>
+      <c r="O132" t="n">
+        <v>814525.7</v>
+      </c>
+      <c r="P132" t="n">
+        <v>652392.2</v>
       </c>
     </row>
     <row r="133">
@@ -7589,28 +8383,34 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>56.17</v>
+        <v>604276.5</v>
       </c>
       <c r="H133" t="n">
-        <v>2536.68</v>
+        <v>502978.1</v>
       </c>
       <c r="I133" t="n">
-        <v>155.2</v>
+        <v>25142.1</v>
       </c>
       <c r="J133" t="n">
-        <v>135.57</v>
+        <v>341127.8</v>
       </c>
       <c r="K133" t="n">
-        <v>113.78</v>
+        <v>463119.3</v>
       </c>
       <c r="L133" t="n">
-        <v>2495.09</v>
+        <v>754611.1</v>
       </c>
       <c r="M133" t="n">
-        <v>191.83</v>
+        <v>731124.3</v>
       </c>
       <c r="N133" t="n">
-        <v>691.4</v>
+        <v>906367.8</v>
+      </c>
+      <c r="O133" t="n">
+        <v>220861.2</v>
+      </c>
+      <c r="P133" t="n">
+        <v>148987</v>
       </c>
     </row>
     <row r="134">
@@ -7643,28 +8443,34 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>855.29</v>
+        <v>987292.5</v>
       </c>
       <c r="H134" t="n">
-        <v>3075.04</v>
+        <v>936944.1</v>
       </c>
       <c r="I134" t="n">
-        <v>253.53</v>
+        <v>837515.7</v>
       </c>
       <c r="J134" t="n">
-        <v>138.81</v>
+        <v>184549.2</v>
       </c>
       <c r="K134" t="n">
-        <v>1108.63</v>
+        <v>923350.9</v>
       </c>
       <c r="L134" t="n">
-        <v>2375.45</v>
+        <v>412817.1</v>
       </c>
       <c r="M134" t="n">
-        <v>2239.69</v>
+        <v>698459.5</v>
       </c>
       <c r="N134" t="n">
-        <v>359.79</v>
+        <v>419139.9</v>
+      </c>
+      <c r="O134" t="n">
+        <v>347282.1</v>
+      </c>
+      <c r="P134" t="n">
+        <v>179570.7</v>
       </c>
     </row>
     <row r="135">
@@ -7697,28 +8503,34 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>809.8200000000001</v>
+        <v>666781.7</v>
       </c>
       <c r="H135" t="n">
-        <v>3259.19</v>
+        <v>976659.2</v>
       </c>
       <c r="I135" t="n">
-        <v>160.76</v>
+        <v>297771.3</v>
       </c>
       <c r="J135" t="n">
-        <v>142.69</v>
+        <v>724755.3</v>
       </c>
       <c r="K135" t="n">
-        <v>301.72</v>
+        <v>354473.4</v>
       </c>
       <c r="L135" t="n">
-        <v>185.62</v>
+        <v>403850.6</v>
       </c>
       <c r="M135" t="n">
-        <v>258.75</v>
+        <v>551175.2</v>
       </c>
       <c r="N135" t="n">
-        <v>719.3</v>
+        <v>504755.4</v>
+      </c>
+      <c r="O135" t="n">
+        <v>153331.5</v>
+      </c>
+      <c r="P135" t="n">
+        <v>791221.7</v>
       </c>
     </row>
     <row r="136">
@@ -7751,28 +8563,34 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>343.44</v>
+        <v>440053.5</v>
       </c>
       <c r="H136" t="n">
-        <v>3571.58</v>
+        <v>74022.3</v>
       </c>
       <c r="I136" t="n">
-        <v>252.27</v>
+        <v>334778.1</v>
       </c>
       <c r="J136" t="n">
-        <v>51.77</v>
+        <v>86157</v>
       </c>
       <c r="K136" t="n">
-        <v>495.49</v>
+        <v>688994.2</v>
       </c>
       <c r="L136" t="n">
-        <v>1313.27</v>
+        <v>807286.9</v>
       </c>
       <c r="M136" t="n">
-        <v>1098.55</v>
+        <v>373046.3</v>
       </c>
       <c r="N136" t="n">
-        <v>418.2</v>
+        <v>524449.1</v>
+      </c>
+      <c r="O136" t="n">
+        <v>888943.9</v>
+      </c>
+      <c r="P136" t="n">
+        <v>567016.6</v>
       </c>
     </row>
     <row r="137">
@@ -7805,28 +8623,34 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>158.75</v>
+        <v>379824.5</v>
       </c>
       <c r="H137" t="n">
-        <v>1864.26</v>
+        <v>588227.9</v>
       </c>
       <c r="I137" t="n">
-        <v>141.45</v>
+        <v>42820</v>
       </c>
       <c r="J137" t="n">
-        <v>122.63</v>
+        <v>470723.1</v>
       </c>
       <c r="K137" t="n">
-        <v>676.73</v>
+        <v>659367.3</v>
       </c>
       <c r="L137" t="n">
-        <v>1793.66</v>
+        <v>746468.4</v>
       </c>
       <c r="M137" t="n">
-        <v>1973.07</v>
+        <v>578958.1</v>
       </c>
       <c r="N137" t="n">
-        <v>517.84</v>
+        <v>307225.1</v>
+      </c>
+      <c r="O137" t="n">
+        <v>295667.8</v>
+      </c>
+      <c r="P137" t="n">
+        <v>760134.3</v>
       </c>
     </row>
     <row r="138">
@@ -7859,28 +8683,34 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>65.91</v>
+        <v>887480.8</v>
       </c>
       <c r="H138" t="n">
-        <v>472.53</v>
+        <v>341318.2</v>
       </c>
       <c r="I138" t="n">
-        <v>339.19</v>
+        <v>648721</v>
       </c>
       <c r="J138" t="n">
-        <v>85.23999999999999</v>
+        <v>215273.1</v>
       </c>
       <c r="K138" t="n">
-        <v>1447.47</v>
+        <v>307259.3</v>
       </c>
       <c r="L138" t="n">
-        <v>1969.69</v>
+        <v>10122.9</v>
       </c>
       <c r="M138" t="n">
-        <v>2265.86</v>
+        <v>925067.2</v>
       </c>
       <c r="N138" t="n">
-        <v>698.62</v>
+        <v>702496.6</v>
+      </c>
+      <c r="O138" t="n">
+        <v>225518.7</v>
+      </c>
+      <c r="P138" t="n">
+        <v>87439.2</v>
       </c>
     </row>
     <row r="139">
@@ -7913,28 +8743,34 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>333.36</v>
+        <v>345382.6</v>
       </c>
       <c r="H139" t="n">
-        <v>2913.7</v>
+        <v>132088.2</v>
       </c>
       <c r="I139" t="n">
-        <v>70.70999999999999</v>
+        <v>250108.8</v>
       </c>
       <c r="J139" t="n">
-        <v>104.95</v>
+        <v>975921.8</v>
       </c>
       <c r="K139" t="n">
-        <v>1935.39</v>
+        <v>42709.8</v>
       </c>
       <c r="L139" t="n">
-        <v>2095.44</v>
+        <v>315291.8</v>
       </c>
       <c r="M139" t="n">
-        <v>979.89</v>
+        <v>418131.9</v>
       </c>
       <c r="N139" t="n">
-        <v>476.03</v>
+        <v>40813.7</v>
+      </c>
+      <c r="O139" t="n">
+        <v>176361.2</v>
+      </c>
+      <c r="P139" t="n">
+        <v>666170.8</v>
       </c>
     </row>
     <row r="140">
@@ -7967,28 +8803,34 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>938</v>
+        <v>667061.3</v>
       </c>
       <c r="H140" t="n">
-        <v>1547.91</v>
+        <v>916927.7</v>
       </c>
       <c r="I140" t="n">
-        <v>188.34</v>
+        <v>542261.4</v>
       </c>
       <c r="J140" t="n">
-        <v>237.5</v>
+        <v>437707.2</v>
       </c>
       <c r="K140" t="n">
-        <v>1626.37</v>
+        <v>216420</v>
       </c>
       <c r="L140" t="n">
-        <v>2010.35</v>
+        <v>321041.1</v>
       </c>
       <c r="M140" t="n">
-        <v>2072.4</v>
+        <v>663675.7</v>
       </c>
       <c r="N140" t="n">
-        <v>591.02</v>
+        <v>654105.6</v>
+      </c>
+      <c r="O140" t="n">
+        <v>703017.2</v>
+      </c>
+      <c r="P140" t="n">
+        <v>630680.6</v>
       </c>
     </row>
     <row r="141">
@@ -8021,28 +8863,34 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>685.41</v>
+        <v>694337.5</v>
       </c>
       <c r="H141" t="n">
-        <v>2631.97</v>
+        <v>90994</v>
       </c>
       <c r="I141" t="n">
-        <v>323.01</v>
+        <v>349443.5</v>
       </c>
       <c r="J141" t="n">
-        <v>127.02</v>
+        <v>505646.2</v>
       </c>
       <c r="K141" t="n">
-        <v>723.66</v>
+        <v>200520.9</v>
       </c>
       <c r="L141" t="n">
-        <v>1087.79</v>
+        <v>269566.1</v>
       </c>
       <c r="M141" t="n">
-        <v>450.66</v>
+        <v>264365.6</v>
       </c>
       <c r="N141" t="n">
-        <v>171.35</v>
+        <v>34295.7</v>
+      </c>
+      <c r="O141" t="n">
+        <v>635515.4</v>
+      </c>
+      <c r="P141" t="n">
+        <v>788022.6</v>
       </c>
     </row>
     <row r="142">
@@ -8075,28 +8923,34 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>947.67</v>
+        <v>964647.5</v>
       </c>
       <c r="H142" t="n">
-        <v>2431.35</v>
+        <v>501962.3</v>
       </c>
       <c r="I142" t="n">
-        <v>113.27</v>
+        <v>348107.2</v>
       </c>
       <c r="J142" t="n">
-        <v>41.27</v>
+        <v>956090.3</v>
       </c>
       <c r="K142" t="n">
-        <v>154.33</v>
+        <v>515226.1</v>
       </c>
       <c r="L142" t="n">
-        <v>2533.29</v>
+        <v>122105.4</v>
       </c>
       <c r="M142" t="n">
-        <v>252.85</v>
+        <v>521833.1</v>
       </c>
       <c r="N142" t="n">
-        <v>616.7</v>
+        <v>318124.6</v>
+      </c>
+      <c r="O142" t="n">
+        <v>967081</v>
+      </c>
+      <c r="P142" t="n">
+        <v>680932.7</v>
       </c>
     </row>
     <row r="143">
@@ -8129,28 +8983,34 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>835.12</v>
+        <v>193276.9</v>
       </c>
       <c r="H143" t="n">
-        <v>4418.41</v>
+        <v>232620.9</v>
       </c>
       <c r="I143" t="n">
-        <v>18.87</v>
+        <v>43016.6</v>
       </c>
       <c r="J143" t="n">
-        <v>101.03</v>
+        <v>652410.5</v>
       </c>
       <c r="K143" t="n">
-        <v>1532.62</v>
+        <v>316187.5</v>
       </c>
       <c r="L143" t="n">
-        <v>393.15</v>
+        <v>472574.1</v>
       </c>
       <c r="M143" t="n">
-        <v>941.8</v>
+        <v>300525.2</v>
       </c>
       <c r="N143" t="n">
-        <v>129.8</v>
+        <v>317046.6</v>
+      </c>
+      <c r="O143" t="n">
+        <v>855478.8</v>
+      </c>
+      <c r="P143" t="n">
+        <v>236851</v>
       </c>
     </row>
     <row r="144">
@@ -8183,28 +9043,34 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>831.35</v>
+        <v>665011.4</v>
       </c>
       <c r="H144" t="n">
-        <v>3855.49</v>
+        <v>572881.9</v>
       </c>
       <c r="I144" t="n">
-        <v>404.52</v>
+        <v>325087.4</v>
       </c>
       <c r="J144" t="n">
-        <v>49.66</v>
+        <v>992494.1</v>
       </c>
       <c r="K144" t="n">
-        <v>875.35</v>
+        <v>651840.3</v>
       </c>
       <c r="L144" t="n">
-        <v>1232.58</v>
+        <v>459833.5</v>
       </c>
       <c r="M144" t="n">
-        <v>1690.91</v>
+        <v>304881.7</v>
       </c>
       <c r="N144" t="n">
-        <v>190.02</v>
+        <v>767802.8</v>
+      </c>
+      <c r="O144" t="n">
+        <v>471360.6</v>
+      </c>
+      <c r="P144" t="n">
+        <v>294449.4</v>
       </c>
     </row>
     <row r="145">
@@ -8237,28 +9103,34 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>444.2</v>
+        <v>171658.8</v>
       </c>
       <c r="H145" t="n">
-        <v>1424.64</v>
+        <v>208398.6</v>
       </c>
       <c r="I145" t="n">
-        <v>374.27</v>
+        <v>912667.6</v>
       </c>
       <c r="J145" t="n">
-        <v>134.68</v>
+        <v>428657.1</v>
       </c>
       <c r="K145" t="n">
-        <v>1068.02</v>
+        <v>612227</v>
       </c>
       <c r="L145" t="n">
-        <v>928.4</v>
+        <v>624240.6</v>
       </c>
       <c r="M145" t="n">
-        <v>2021.56</v>
+        <v>203115.6</v>
       </c>
       <c r="N145" t="n">
-        <v>375.21</v>
+        <v>206304.9</v>
+      </c>
+      <c r="O145" t="n">
+        <v>662097.6</v>
+      </c>
+      <c r="P145" t="n">
+        <v>523948</v>
       </c>
     </row>
     <row r="146">
@@ -8291,28 +9163,34 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>835.11</v>
+        <v>640064.4</v>
       </c>
       <c r="H146" t="n">
-        <v>1839.2</v>
+        <v>854735.2</v>
       </c>
       <c r="I146" t="n">
-        <v>473.57</v>
+        <v>943222.9</v>
       </c>
       <c r="J146" t="n">
-        <v>295.33</v>
+        <v>872205.3</v>
       </c>
       <c r="K146" t="n">
-        <v>923.36</v>
+        <v>110716.3</v>
       </c>
       <c r="L146" t="n">
-        <v>845.3200000000001</v>
+        <v>390741.3</v>
       </c>
       <c r="M146" t="n">
-        <v>954.6799999999999</v>
+        <v>174232</v>
       </c>
       <c r="N146" t="n">
-        <v>421.97</v>
+        <v>408124.3</v>
+      </c>
+      <c r="O146" t="n">
+        <v>26385.4</v>
+      </c>
+      <c r="P146" t="n">
+        <v>928345.1</v>
       </c>
     </row>
     <row r="147">
@@ -8345,28 +9223,34 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>966.27</v>
+        <v>657166.6</v>
       </c>
       <c r="H147" t="n">
-        <v>4084.46</v>
+        <v>436336.6</v>
       </c>
       <c r="I147" t="n">
-        <v>400.63</v>
+        <v>913932.8</v>
       </c>
       <c r="J147" t="n">
-        <v>41.52</v>
+        <v>434556.2</v>
       </c>
       <c r="K147" t="n">
-        <v>500.01</v>
+        <v>859965.8</v>
       </c>
       <c r="L147" t="n">
-        <v>1923.54</v>
+        <v>786486.5</v>
       </c>
       <c r="M147" t="n">
-        <v>2185.29</v>
+        <v>96628.60000000001</v>
       </c>
       <c r="N147" t="n">
-        <v>443.63</v>
+        <v>456515.9</v>
+      </c>
+      <c r="O147" t="n">
+        <v>814824.7</v>
+      </c>
+      <c r="P147" t="n">
+        <v>552706.4</v>
       </c>
     </row>
     <row r="148">
@@ -8399,28 +9283,34 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>102.59</v>
+        <v>743016.1</v>
       </c>
       <c r="H148" t="n">
-        <v>4229.46</v>
+        <v>201676.1</v>
       </c>
       <c r="I148" t="n">
-        <v>425.58</v>
+        <v>850820.8</v>
       </c>
       <c r="J148" t="n">
-        <v>85.52</v>
+        <v>277010.8</v>
       </c>
       <c r="K148" t="n">
-        <v>1526.23</v>
+        <v>416323.5</v>
       </c>
       <c r="L148" t="n">
-        <v>818.37</v>
+        <v>740746.3</v>
       </c>
       <c r="M148" t="n">
-        <v>2263.27</v>
+        <v>50087.1</v>
       </c>
       <c r="N148" t="n">
-        <v>117.88</v>
+        <v>55063.1</v>
+      </c>
+      <c r="O148" t="n">
+        <v>120536.5</v>
+      </c>
+      <c r="P148" t="n">
+        <v>241708.1</v>
       </c>
     </row>
     <row r="149">
@@ -8453,28 +9343,34 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>437.47</v>
+        <v>866275.9</v>
       </c>
       <c r="H149" t="n">
-        <v>4732.07</v>
+        <v>800645.7</v>
       </c>
       <c r="I149" t="n">
-        <v>111.02</v>
+        <v>810966.1</v>
       </c>
       <c r="J149" t="n">
-        <v>135.34</v>
+        <v>960808.7</v>
       </c>
       <c r="K149" t="n">
-        <v>699.17</v>
+        <v>211369.4</v>
       </c>
       <c r="L149" t="n">
-        <v>80.01000000000001</v>
+        <v>933059.4</v>
       </c>
       <c r="M149" t="n">
-        <v>133.14</v>
+        <v>955944</v>
       </c>
       <c r="N149" t="n">
-        <v>401.61</v>
+        <v>648838.7</v>
+      </c>
+      <c r="O149" t="n">
+        <v>818956.7</v>
+      </c>
+      <c r="P149" t="n">
+        <v>942804.9</v>
       </c>
     </row>
     <row r="150">
@@ -8507,28 +9403,34 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>235.78</v>
+        <v>231236.6</v>
       </c>
       <c r="H150" t="n">
-        <v>4972.63</v>
+        <v>134613.8</v>
       </c>
       <c r="I150" t="n">
-        <v>187.46</v>
+        <v>628062.6</v>
       </c>
       <c r="J150" t="n">
-        <v>8.460000000000001</v>
+        <v>622975.4</v>
       </c>
       <c r="K150" t="n">
-        <v>1861.65</v>
+        <v>33696.3</v>
       </c>
       <c r="L150" t="n">
-        <v>2517.53</v>
+        <v>27913.8</v>
       </c>
       <c r="M150" t="n">
-        <v>1624.9</v>
+        <v>673138.4</v>
       </c>
       <c r="N150" t="n">
-        <v>633.1</v>
+        <v>183394.4</v>
+      </c>
+      <c r="O150" t="n">
+        <v>557625.6</v>
+      </c>
+      <c r="P150" t="n">
+        <v>45724.5</v>
       </c>
     </row>
     <row r="151">
@@ -8561,28 +9463,34 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>137.6</v>
+        <v>860505.4</v>
       </c>
       <c r="H151" t="n">
-        <v>1434.4</v>
+        <v>738152.1</v>
       </c>
       <c r="I151" t="n">
-        <v>414.88</v>
+        <v>604860.8</v>
       </c>
       <c r="J151" t="n">
-        <v>208.82</v>
+        <v>143381</v>
       </c>
       <c r="K151" t="n">
-        <v>277.59</v>
+        <v>480479.9</v>
       </c>
       <c r="L151" t="n">
-        <v>2116.61</v>
+        <v>823770.1</v>
       </c>
       <c r="M151" t="n">
-        <v>1121.5</v>
+        <v>193556</v>
       </c>
       <c r="N151" t="n">
-        <v>4.2</v>
+        <v>94238.7</v>
+      </c>
+      <c r="O151" t="n">
+        <v>891357.3</v>
+      </c>
+      <c r="P151" t="n">
+        <v>691856.1</v>
       </c>
     </row>
     <row r="152">
@@ -8615,28 +9523,34 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>79.23</v>
+        <v>345536.4</v>
       </c>
       <c r="H152" t="n">
-        <v>1279.62</v>
+        <v>248420</v>
       </c>
       <c r="I152" t="n">
-        <v>417.48</v>
+        <v>718357.4</v>
       </c>
       <c r="J152" t="n">
-        <v>164.64</v>
+        <v>568710</v>
       </c>
       <c r="K152" t="n">
-        <v>1454.47</v>
+        <v>119183.1</v>
       </c>
       <c r="L152" t="n">
-        <v>1583.31</v>
+        <v>967800.9</v>
       </c>
       <c r="M152" t="n">
-        <v>277.97</v>
+        <v>448702.4</v>
       </c>
       <c r="N152" t="n">
-        <v>230.48</v>
+        <v>964486.4</v>
+      </c>
+      <c r="O152" t="n">
+        <v>756757.9</v>
+      </c>
+      <c r="P152" t="n">
+        <v>762257.4</v>
       </c>
     </row>
     <row r="153">
@@ -8669,28 +9583,34 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>301.15</v>
+        <v>399900.6</v>
       </c>
       <c r="H153" t="n">
-        <v>238.75</v>
+        <v>840901.1</v>
       </c>
       <c r="I153" t="n">
-        <v>209.91</v>
+        <v>960531.8</v>
       </c>
       <c r="J153" t="n">
-        <v>238.17</v>
+        <v>691101.2</v>
       </c>
       <c r="K153" t="n">
-        <v>914.23</v>
+        <v>752999.5</v>
       </c>
       <c r="L153" t="n">
-        <v>332.57</v>
+        <v>512765.5</v>
       </c>
       <c r="M153" t="n">
-        <v>2262.87</v>
+        <v>841847.5</v>
       </c>
       <c r="N153" t="n">
-        <v>477.39</v>
+        <v>927030.9</v>
+      </c>
+      <c r="O153" t="n">
+        <v>345295.6</v>
+      </c>
+      <c r="P153" t="n">
+        <v>29034.6</v>
       </c>
     </row>
     <row r="154">
@@ -8723,28 +9643,34 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>16.44</v>
+        <v>112332.2</v>
       </c>
       <c r="H154" t="n">
-        <v>2576.88</v>
+        <v>256528.7</v>
       </c>
       <c r="I154" t="n">
-        <v>120.97</v>
+        <v>603736.4</v>
       </c>
       <c r="J154" t="n">
-        <v>43.07</v>
+        <v>135810.5</v>
       </c>
       <c r="K154" t="n">
-        <v>858.48</v>
+        <v>201753.8</v>
       </c>
       <c r="L154" t="n">
-        <v>1844.43</v>
+        <v>522940.4</v>
       </c>
       <c r="M154" t="n">
-        <v>601.41</v>
+        <v>122435.5</v>
       </c>
       <c r="N154" t="n">
-        <v>333.25</v>
+        <v>485313.1</v>
+      </c>
+      <c r="O154" t="n">
+        <v>431984</v>
+      </c>
+      <c r="P154" t="n">
+        <v>248657.7</v>
       </c>
     </row>
     <row r="155">
@@ -8777,28 +9703,34 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>664.37</v>
+        <v>531748.4</v>
       </c>
       <c r="H155" t="n">
-        <v>428.07</v>
+        <v>651473</v>
       </c>
       <c r="I155" t="n">
-        <v>487.33</v>
+        <v>557383</v>
       </c>
       <c r="J155" t="n">
-        <v>20.3</v>
+        <v>483481.5</v>
       </c>
       <c r="K155" t="n">
-        <v>1052.12</v>
+        <v>171252.6</v>
       </c>
       <c r="L155" t="n">
-        <v>1521.98</v>
+        <v>907084.4</v>
       </c>
       <c r="M155" t="n">
-        <v>2470.83</v>
+        <v>176116.9</v>
       </c>
       <c r="N155" t="n">
-        <v>443.32</v>
+        <v>243754.5</v>
+      </c>
+      <c r="O155" t="n">
+        <v>713483.1</v>
+      </c>
+      <c r="P155" t="n">
+        <v>830617.1</v>
       </c>
     </row>
     <row r="156">
@@ -8831,28 +9763,34 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>390.45</v>
+        <v>1292.5</v>
       </c>
       <c r="H156" t="n">
-        <v>2350.68</v>
+        <v>672252.1</v>
       </c>
       <c r="I156" t="n">
-        <v>317.84</v>
+        <v>728488.6</v>
       </c>
       <c r="J156" t="n">
-        <v>294.31</v>
+        <v>443986.1</v>
       </c>
       <c r="K156" t="n">
-        <v>507.3</v>
+        <v>426127.6</v>
       </c>
       <c r="L156" t="n">
-        <v>48.73</v>
+        <v>317461.2</v>
       </c>
       <c r="M156" t="n">
-        <v>1971.3</v>
+        <v>96490.2</v>
       </c>
       <c r="N156" t="n">
-        <v>275.84</v>
+        <v>431760.6</v>
+      </c>
+      <c r="O156" t="n">
+        <v>188455.9</v>
+      </c>
+      <c r="P156" t="n">
+        <v>834211.4</v>
       </c>
     </row>
     <row r="157">
@@ -8885,28 +9823,34 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>732.9400000000001</v>
+        <v>310534.8</v>
       </c>
       <c r="H157" t="n">
-        <v>3141.28</v>
+        <v>504501.2</v>
       </c>
       <c r="I157" t="n">
-        <v>385.75</v>
+        <v>844946.3</v>
       </c>
       <c r="J157" t="n">
-        <v>220.56</v>
+        <v>183288.3</v>
       </c>
       <c r="K157" t="n">
-        <v>665.04</v>
+        <v>77415.89999999999</v>
       </c>
       <c r="L157" t="n">
-        <v>133.01</v>
+        <v>820205.1</v>
       </c>
       <c r="M157" t="n">
-        <v>1365.03</v>
+        <v>461656.2</v>
       </c>
       <c r="N157" t="n">
-        <v>650.8099999999999</v>
+        <v>501613.5</v>
+      </c>
+      <c r="O157" t="n">
+        <v>3732.6</v>
+      </c>
+      <c r="P157" t="n">
+        <v>827751</v>
       </c>
     </row>
     <row r="158">
@@ -8939,28 +9883,34 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>175.09</v>
+        <v>672300.5</v>
       </c>
       <c r="H158" t="n">
-        <v>3895.71</v>
+        <v>870667.5</v>
       </c>
       <c r="I158" t="n">
-        <v>232.31</v>
+        <v>533900.5</v>
       </c>
       <c r="J158" t="n">
-        <v>208.62</v>
+        <v>686629.9</v>
       </c>
       <c r="K158" t="n">
-        <v>1263.47</v>
+        <v>909797.9</v>
       </c>
       <c r="L158" t="n">
-        <v>2434.49</v>
+        <v>463178</v>
       </c>
       <c r="M158" t="n">
-        <v>157.75</v>
+        <v>460700.1</v>
       </c>
       <c r="N158" t="n">
-        <v>620.95</v>
+        <v>791499.8</v>
+      </c>
+      <c r="O158" t="n">
+        <v>955551.4</v>
+      </c>
+      <c r="P158" t="n">
+        <v>452667</v>
       </c>
     </row>
     <row r="159">
@@ -8993,28 +9943,34 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>457.68</v>
+        <v>747544.8</v>
       </c>
       <c r="H159" t="n">
-        <v>1467.21</v>
+        <v>543221.4</v>
       </c>
       <c r="I159" t="n">
-        <v>21.9</v>
+        <v>20544.1</v>
       </c>
       <c r="J159" t="n">
-        <v>59.84</v>
+        <v>487189.8</v>
       </c>
       <c r="K159" t="n">
-        <v>83.81</v>
+        <v>855769.9</v>
       </c>
       <c r="L159" t="n">
-        <v>2800.11</v>
+        <v>852882.6</v>
       </c>
       <c r="M159" t="n">
-        <v>1288.46</v>
+        <v>53540.2</v>
       </c>
       <c r="N159" t="n">
-        <v>791.3</v>
+        <v>237800.1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>90501.7</v>
+      </c>
+      <c r="P159" t="n">
+        <v>201760.2</v>
       </c>
     </row>
     <row r="160">
@@ -9047,28 +10003,34 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>543.03</v>
+        <v>167359.7</v>
       </c>
       <c r="H160" t="n">
-        <v>1266.57</v>
+        <v>234740</v>
       </c>
       <c r="I160" t="n">
-        <v>376.65</v>
+        <v>605891.6</v>
       </c>
       <c r="J160" t="n">
-        <v>57.33</v>
+        <v>595787.3</v>
       </c>
       <c r="K160" t="n">
-        <v>713.95</v>
+        <v>80337.2</v>
       </c>
       <c r="L160" t="n">
-        <v>2342.52</v>
+        <v>738201.8</v>
       </c>
       <c r="M160" t="n">
-        <v>2164.5</v>
+        <v>562221</v>
       </c>
       <c r="N160" t="n">
-        <v>265.54</v>
+        <v>150880.7</v>
+      </c>
+      <c r="O160" t="n">
+        <v>825380.2</v>
+      </c>
+      <c r="P160" t="n">
+        <v>869843</v>
       </c>
     </row>
     <row r="161">
@@ -9101,28 +10063,34 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>124.48</v>
+        <v>784871.6</v>
       </c>
       <c r="H161" t="n">
-        <v>1840.1</v>
+        <v>524490.2</v>
       </c>
       <c r="I161" t="n">
-        <v>444.74</v>
+        <v>344040.3</v>
       </c>
       <c r="J161" t="n">
-        <v>222.99</v>
+        <v>535752</v>
       </c>
       <c r="K161" t="n">
-        <v>1789.27</v>
+        <v>242132.3</v>
       </c>
       <c r="L161" t="n">
-        <v>1159.93</v>
+        <v>472618.1</v>
       </c>
       <c r="M161" t="n">
-        <v>2434.31</v>
+        <v>583690.9</v>
       </c>
       <c r="N161" t="n">
-        <v>396.96</v>
+        <v>905834.4</v>
+      </c>
+      <c r="O161" t="n">
+        <v>178436.9</v>
+      </c>
+      <c r="P161" t="n">
+        <v>446466.7</v>
       </c>
     </row>
     <row r="162">
@@ -9155,28 +10123,34 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>497.52</v>
+        <v>444116.8</v>
       </c>
       <c r="H162" t="n">
-        <v>4621.55</v>
+        <v>687097.6</v>
       </c>
       <c r="I162" t="n">
-        <v>259.64</v>
+        <v>128312.4</v>
       </c>
       <c r="J162" t="n">
-        <v>240.34</v>
+        <v>614650.6</v>
       </c>
       <c r="K162" t="n">
-        <v>1454.16</v>
+        <v>833137.4</v>
       </c>
       <c r="L162" t="n">
-        <v>236.78</v>
+        <v>156682.5</v>
       </c>
       <c r="M162" t="n">
-        <v>1506.13</v>
+        <v>684608.2</v>
       </c>
       <c r="N162" t="n">
-        <v>657.87</v>
+        <v>870441.7</v>
+      </c>
+      <c r="O162" t="n">
+        <v>523343.3</v>
+      </c>
+      <c r="P162" t="n">
+        <v>982100.2</v>
       </c>
     </row>
     <row r="163">
@@ -9209,28 +10183,34 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>545.47</v>
+        <v>205296.6</v>
       </c>
       <c r="H163" t="n">
-        <v>1606.06</v>
+        <v>420997.2</v>
       </c>
       <c r="I163" t="n">
-        <v>40.03</v>
+        <v>45792.1</v>
       </c>
       <c r="J163" t="n">
-        <v>198.28</v>
+        <v>779003.8</v>
       </c>
       <c r="K163" t="n">
-        <v>612.99</v>
+        <v>767877.9</v>
       </c>
       <c r="L163" t="n">
-        <v>1807.86</v>
+        <v>287859.5</v>
       </c>
       <c r="M163" t="n">
-        <v>1065.29</v>
+        <v>606902.5</v>
       </c>
       <c r="N163" t="n">
-        <v>551.8099999999999</v>
+        <v>791024.8</v>
+      </c>
+      <c r="O163" t="n">
+        <v>661062.5</v>
+      </c>
+      <c r="P163" t="n">
+        <v>63172.7</v>
       </c>
     </row>
     <row r="164">
@@ -9263,28 +10243,34 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>351.55</v>
+        <v>748576.9</v>
       </c>
       <c r="H164" t="n">
-        <v>211.78</v>
+        <v>524372.9</v>
       </c>
       <c r="I164" t="n">
-        <v>435.02</v>
+        <v>533934.8</v>
       </c>
       <c r="J164" t="n">
-        <v>105.77</v>
+        <v>483895</v>
       </c>
       <c r="K164" t="n">
-        <v>1996.3</v>
+        <v>535731.4</v>
       </c>
       <c r="L164" t="n">
-        <v>823.67</v>
+        <v>633767.2</v>
       </c>
       <c r="M164" t="n">
-        <v>2450.07</v>
+        <v>34483.9</v>
       </c>
       <c r="N164" t="n">
-        <v>758.3200000000001</v>
+        <v>689168.1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>366936.8</v>
+      </c>
+      <c r="P164" t="n">
+        <v>105326.9</v>
       </c>
     </row>
     <row r="165">
@@ -9317,28 +10303,34 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>75.04000000000001</v>
+        <v>738925.5</v>
       </c>
       <c r="H165" t="n">
-        <v>3187.56</v>
+        <v>72482.3</v>
       </c>
       <c r="I165" t="n">
-        <v>181.66</v>
+        <v>955036</v>
       </c>
       <c r="J165" t="n">
-        <v>240.33</v>
+        <v>964966.9</v>
       </c>
       <c r="K165" t="n">
-        <v>1358.82</v>
+        <v>676958.5</v>
       </c>
       <c r="L165" t="n">
-        <v>2858.37</v>
+        <v>328551.9</v>
       </c>
       <c r="M165" t="n">
-        <v>356.95</v>
+        <v>58577.7</v>
       </c>
       <c r="N165" t="n">
-        <v>486.06</v>
+        <v>489558.5</v>
+      </c>
+      <c r="O165" t="n">
+        <v>299871.7</v>
+      </c>
+      <c r="P165" t="n">
+        <v>444998</v>
       </c>
     </row>
     <row r="166">
@@ -9371,28 +10363,34 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>781.3099999999999</v>
+        <v>468024.5</v>
       </c>
       <c r="H166" t="n">
-        <v>173.99</v>
+        <v>250497.4</v>
       </c>
       <c r="I166" t="n">
-        <v>33.62</v>
+        <v>558065.8</v>
       </c>
       <c r="J166" t="n">
-        <v>233.55</v>
+        <v>902319.7</v>
       </c>
       <c r="K166" t="n">
-        <v>732.66</v>
+        <v>440680.9</v>
       </c>
       <c r="L166" t="n">
-        <v>1148.56</v>
+        <v>193203.7</v>
       </c>
       <c r="M166" t="n">
-        <v>1418.11</v>
+        <v>492014</v>
       </c>
       <c r="N166" t="n">
-        <v>484.08</v>
+        <v>781367.1</v>
+      </c>
+      <c r="O166" t="n">
+        <v>579380.9</v>
+      </c>
+      <c r="P166" t="n">
+        <v>836672.6</v>
       </c>
     </row>
     <row r="167">
@@ -9425,28 +10423,34 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>679.0599999999999</v>
+        <v>531031.1</v>
       </c>
       <c r="H167" t="n">
-        <v>4744.12</v>
+        <v>767118.7</v>
       </c>
       <c r="I167" t="n">
-        <v>186.01</v>
+        <v>834007.2</v>
       </c>
       <c r="J167" t="n">
-        <v>228.93</v>
+        <v>454518.2</v>
       </c>
       <c r="K167" t="n">
-        <v>1147.84</v>
+        <v>608263.9</v>
       </c>
       <c r="L167" t="n">
-        <v>1588.38</v>
+        <v>269240.7</v>
       </c>
       <c r="M167" t="n">
-        <v>995.09</v>
+        <v>231585.3</v>
       </c>
       <c r="N167" t="n">
-        <v>519.65</v>
+        <v>876471.2</v>
+      </c>
+      <c r="O167" t="n">
+        <v>665483</v>
+      </c>
+      <c r="P167" t="n">
+        <v>539773.9</v>
       </c>
     </row>
     <row r="168">
@@ -9479,28 +10483,34 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>249.61</v>
+        <v>619803.8</v>
       </c>
       <c r="H168" t="n">
-        <v>567.24</v>
+        <v>334189.1</v>
       </c>
       <c r="I168" t="n">
-        <v>367.84</v>
+        <v>172988</v>
       </c>
       <c r="J168" t="n">
-        <v>149.71</v>
+        <v>121304.7</v>
       </c>
       <c r="K168" t="n">
-        <v>773.97</v>
+        <v>619432.7</v>
       </c>
       <c r="L168" t="n">
-        <v>1685.02</v>
+        <v>479385</v>
       </c>
       <c r="M168" t="n">
-        <v>654.4400000000001</v>
+        <v>307348.2</v>
       </c>
       <c r="N168" t="n">
-        <v>208.23</v>
+        <v>871356.6</v>
+      </c>
+      <c r="O168" t="n">
+        <v>5642.5</v>
+      </c>
+      <c r="P168" t="n">
+        <v>273015.7</v>
       </c>
     </row>
     <row r="169">
@@ -9533,28 +10543,34 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>446.27</v>
+        <v>631695.2</v>
       </c>
       <c r="H169" t="n">
-        <v>4981.83</v>
+        <v>189088.7</v>
       </c>
       <c r="I169" t="n">
-        <v>142.79</v>
+        <v>328904.6</v>
       </c>
       <c r="J169" t="n">
-        <v>274.94</v>
+        <v>489827.2</v>
       </c>
       <c r="K169" t="n">
-        <v>982.4</v>
+        <v>744082.6</v>
       </c>
       <c r="L169" t="n">
-        <v>367.91</v>
+        <v>579941.3</v>
       </c>
       <c r="M169" t="n">
-        <v>2132.07</v>
+        <v>685769</v>
       </c>
       <c r="N169" t="n">
-        <v>361.63</v>
+        <v>96883.60000000001</v>
+      </c>
+      <c r="O169" t="n">
+        <v>221534.6</v>
+      </c>
+      <c r="P169" t="n">
+        <v>487635.6</v>
       </c>
     </row>
     <row r="170">
@@ -9587,28 +10603,34 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>898.6799999999999</v>
+        <v>765041.6</v>
       </c>
       <c r="H170" t="n">
-        <v>2225.56</v>
+        <v>793461.8</v>
       </c>
       <c r="I170" t="n">
-        <v>43.9</v>
+        <v>955250.5</v>
       </c>
       <c r="J170" t="n">
-        <v>204.58</v>
+        <v>380996.4</v>
       </c>
       <c r="K170" t="n">
-        <v>1691.04</v>
+        <v>971831.5</v>
       </c>
       <c r="L170" t="n">
-        <v>958.76</v>
+        <v>730328.5</v>
       </c>
       <c r="M170" t="n">
-        <v>868.5599999999999</v>
+        <v>702540.9</v>
       </c>
       <c r="N170" t="n">
-        <v>51.95</v>
+        <v>241223</v>
+      </c>
+      <c r="O170" t="n">
+        <v>651581</v>
+      </c>
+      <c r="P170" t="n">
+        <v>306263</v>
       </c>
     </row>
     <row r="171">
@@ -9641,28 +10663,34 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>542.17</v>
+        <v>768936.2</v>
       </c>
       <c r="H171" t="n">
-        <v>4456.66</v>
+        <v>29600.2</v>
       </c>
       <c r="I171" t="n">
-        <v>425.68</v>
+        <v>688736.6</v>
       </c>
       <c r="J171" t="n">
-        <v>213.54</v>
+        <v>888696.4</v>
       </c>
       <c r="K171" t="n">
-        <v>1854.65</v>
+        <v>519020.7</v>
       </c>
       <c r="L171" t="n">
-        <v>1913.1</v>
+        <v>33907.4</v>
       </c>
       <c r="M171" t="n">
-        <v>1984.24</v>
+        <v>331840.2</v>
       </c>
       <c r="N171" t="n">
-        <v>407</v>
+        <v>262374.2</v>
+      </c>
+      <c r="O171" t="n">
+        <v>592594.5</v>
+      </c>
+      <c r="P171" t="n">
+        <v>947568.6</v>
       </c>
     </row>
     <row r="172">
@@ -9695,28 +10723,34 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>121.36</v>
+        <v>200284.6</v>
       </c>
       <c r="H172" t="n">
-        <v>1004.9</v>
+        <v>38240</v>
       </c>
       <c r="I172" t="n">
-        <v>69.44</v>
+        <v>726704.3</v>
       </c>
       <c r="J172" t="n">
-        <v>237.11</v>
+        <v>314368</v>
       </c>
       <c r="K172" t="n">
-        <v>52.57</v>
+        <v>129909.2</v>
       </c>
       <c r="L172" t="n">
-        <v>1662.06</v>
+        <v>597917.7</v>
       </c>
       <c r="M172" t="n">
-        <v>922.28</v>
+        <v>824227.6</v>
       </c>
       <c r="N172" t="n">
-        <v>642.9299999999999</v>
+        <v>644276.4</v>
+      </c>
+      <c r="O172" t="n">
+        <v>675635.4</v>
+      </c>
+      <c r="P172" t="n">
+        <v>390600.8</v>
       </c>
     </row>
     <row r="173">
@@ -9749,28 +10783,34 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>551.65</v>
+        <v>20617.8</v>
       </c>
       <c r="H173" t="n">
-        <v>3059.74</v>
+        <v>62153.4</v>
       </c>
       <c r="I173" t="n">
-        <v>43.11</v>
+        <v>295584.9</v>
       </c>
       <c r="J173" t="n">
-        <v>92.79000000000001</v>
+        <v>59832.2</v>
       </c>
       <c r="K173" t="n">
-        <v>1999.19</v>
+        <v>770519.8</v>
       </c>
       <c r="L173" t="n">
-        <v>2156.61</v>
+        <v>87281.60000000001</v>
       </c>
       <c r="M173" t="n">
-        <v>1314.24</v>
+        <v>119900.4</v>
       </c>
       <c r="N173" t="n">
-        <v>615.33</v>
+        <v>21650.7</v>
+      </c>
+      <c r="O173" t="n">
+        <v>234860.3</v>
+      </c>
+      <c r="P173" t="n">
+        <v>254792.7</v>
       </c>
     </row>
     <row r="174">
@@ -9803,28 +10843,34 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>823.34</v>
+        <v>105151.5</v>
       </c>
       <c r="H174" t="n">
-        <v>368.75</v>
+        <v>189623.4</v>
       </c>
       <c r="I174" t="n">
-        <v>486.19</v>
+        <v>667956.1</v>
       </c>
       <c r="J174" t="n">
-        <v>192.7</v>
+        <v>195325.5</v>
       </c>
       <c r="K174" t="n">
-        <v>899.95</v>
+        <v>974125.5</v>
       </c>
       <c r="L174" t="n">
-        <v>2040.33</v>
+        <v>530078.2</v>
       </c>
       <c r="M174" t="n">
-        <v>861.29</v>
+        <v>120714.5</v>
       </c>
       <c r="N174" t="n">
-        <v>702.37</v>
+        <v>821204.9</v>
+      </c>
+      <c r="O174" t="n">
+        <v>932748.9</v>
+      </c>
+      <c r="P174" t="n">
+        <v>612585.6</v>
       </c>
     </row>
     <row r="175">
@@ -9857,28 +10903,34 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>780.26</v>
+        <v>307501.1</v>
       </c>
       <c r="H175" t="n">
-        <v>3198.97</v>
+        <v>49972.5</v>
       </c>
       <c r="I175" t="n">
-        <v>90.98</v>
+        <v>343163.2</v>
       </c>
       <c r="J175" t="n">
-        <v>289.88</v>
+        <v>877852</v>
       </c>
       <c r="K175" t="n">
-        <v>865.24</v>
+        <v>537274.6</v>
       </c>
       <c r="L175" t="n">
-        <v>2732.14</v>
+        <v>216619.6</v>
       </c>
       <c r="M175" t="n">
-        <v>138.53</v>
+        <v>172406.3</v>
       </c>
       <c r="N175" t="n">
-        <v>99.33</v>
+        <v>874397.6</v>
+      </c>
+      <c r="O175" t="n">
+        <v>602128.8</v>
+      </c>
+      <c r="P175" t="n">
+        <v>442725.6</v>
       </c>
     </row>
     <row r="176">
@@ -9911,28 +10963,34 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>153.02</v>
+        <v>580511</v>
       </c>
       <c r="H176" t="n">
-        <v>823.29</v>
+        <v>292853.4</v>
       </c>
       <c r="I176" t="n">
-        <v>161.33</v>
+        <v>198663</v>
       </c>
       <c r="J176" t="n">
-        <v>212.8</v>
+        <v>121733</v>
       </c>
       <c r="K176" t="n">
-        <v>692.05</v>
+        <v>933827.9</v>
       </c>
       <c r="L176" t="n">
-        <v>2822.71</v>
+        <v>715570.6</v>
       </c>
       <c r="M176" t="n">
-        <v>2237.31</v>
+        <v>889593.6</v>
       </c>
       <c r="N176" t="n">
-        <v>676.75</v>
+        <v>238844.4</v>
+      </c>
+      <c r="O176" t="n">
+        <v>100689.3</v>
+      </c>
+      <c r="P176" t="n">
+        <v>858870.2</v>
       </c>
     </row>
     <row r="177">
@@ -9965,28 +11023,34 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>250.61</v>
+        <v>961137.9</v>
       </c>
       <c r="H177" t="n">
-        <v>3175.29</v>
+        <v>268226.5</v>
       </c>
       <c r="I177" t="n">
-        <v>275.42</v>
+        <v>157574.4</v>
       </c>
       <c r="J177" t="n">
-        <v>37.55</v>
+        <v>909654.3</v>
       </c>
       <c r="K177" t="n">
-        <v>605.65</v>
+        <v>751978.1</v>
       </c>
       <c r="L177" t="n">
-        <v>1600.43</v>
+        <v>475170.9</v>
       </c>
       <c r="M177" t="n">
-        <v>1256.43</v>
+        <v>554297.4</v>
       </c>
       <c r="N177" t="n">
-        <v>134.91</v>
+        <v>246112.1</v>
+      </c>
+      <c r="O177" t="n">
+        <v>195045.1</v>
+      </c>
+      <c r="P177" t="n">
+        <v>60571.1</v>
       </c>
     </row>
     <row r="178">
@@ -10019,28 +11083,34 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>941.61</v>
+        <v>416772.9</v>
       </c>
       <c r="H178" t="n">
-        <v>770.97</v>
+        <v>923127</v>
       </c>
       <c r="I178" t="n">
-        <v>329.37</v>
+        <v>175537.5</v>
       </c>
       <c r="J178" t="n">
-        <v>216.19</v>
+        <v>429648.2</v>
       </c>
       <c r="K178" t="n">
-        <v>1210.28</v>
+        <v>750698.9</v>
       </c>
       <c r="L178" t="n">
-        <v>2527.59</v>
+        <v>117276.8</v>
       </c>
       <c r="M178" t="n">
-        <v>1409.05</v>
+        <v>657232.1</v>
       </c>
       <c r="N178" t="n">
-        <v>660.1900000000001</v>
+        <v>816186.4</v>
+      </c>
+      <c r="O178" t="n">
+        <v>863571.7</v>
+      </c>
+      <c r="P178" t="n">
+        <v>900199</v>
       </c>
     </row>
     <row r="179">
@@ -10073,28 +11143,34 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>28.37</v>
+        <v>369226.5</v>
       </c>
       <c r="H179" t="n">
-        <v>227.31</v>
+        <v>254916.3</v>
       </c>
       <c r="I179" t="n">
-        <v>320.73</v>
+        <v>92473.10000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>173.03</v>
+        <v>540995.1</v>
       </c>
       <c r="K179" t="n">
-        <v>1302.26</v>
+        <v>792905.8</v>
       </c>
       <c r="L179" t="n">
-        <v>2300.88</v>
+        <v>500083.8</v>
       </c>
       <c r="M179" t="n">
-        <v>1041.47</v>
+        <v>5733.1</v>
       </c>
       <c r="N179" t="n">
-        <v>511.19</v>
+        <v>459057.7</v>
+      </c>
+      <c r="O179" t="n">
+        <v>476038.7</v>
+      </c>
+      <c r="P179" t="n">
+        <v>284336</v>
       </c>
     </row>
     <row r="180">
@@ -10127,28 +11203,34 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>498.04</v>
+        <v>557228.7</v>
       </c>
       <c r="H180" t="n">
-        <v>3135.82</v>
+        <v>577254.2</v>
       </c>
       <c r="I180" t="n">
-        <v>144.84</v>
+        <v>391007.2</v>
       </c>
       <c r="J180" t="n">
-        <v>287</v>
+        <v>754615.2</v>
       </c>
       <c r="K180" t="n">
-        <v>965.89</v>
+        <v>607890.3</v>
       </c>
       <c r="L180" t="n">
-        <v>2414.06</v>
+        <v>451834.7</v>
       </c>
       <c r="M180" t="n">
-        <v>1712.48</v>
+        <v>554336.4</v>
       </c>
       <c r="N180" t="n">
-        <v>237.95</v>
+        <v>199880.4</v>
+      </c>
+      <c r="O180" t="n">
+        <v>505001.3</v>
+      </c>
+      <c r="P180" t="n">
+        <v>406578.4</v>
       </c>
     </row>
     <row r="181">
@@ -10181,28 +11263,34 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>72.97</v>
+        <v>948312.8</v>
       </c>
       <c r="H181" t="n">
-        <v>299.57</v>
+        <v>295332.4</v>
       </c>
       <c r="I181" t="n">
-        <v>219.8</v>
+        <v>867522.9</v>
       </c>
       <c r="J181" t="n">
-        <v>145.28</v>
+        <v>867497.9</v>
       </c>
       <c r="K181" t="n">
-        <v>408.05</v>
+        <v>108714.2</v>
       </c>
       <c r="L181" t="n">
-        <v>1819.98</v>
+        <v>712103.9</v>
       </c>
       <c r="M181" t="n">
-        <v>781.46</v>
+        <v>861150.6</v>
       </c>
       <c r="N181" t="n">
-        <v>574.6900000000001</v>
+        <v>464802.5</v>
+      </c>
+      <c r="O181" t="n">
+        <v>333421.2</v>
+      </c>
+      <c r="P181" t="n">
+        <v>839712.4</v>
       </c>
     </row>
     <row r="182">
@@ -10235,28 +11323,34 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>734.2</v>
+        <v>588011.4</v>
       </c>
       <c r="H182" t="n">
-        <v>4303.89</v>
+        <v>725691.1</v>
       </c>
       <c r="I182" t="n">
-        <v>487.69</v>
+        <v>544795.9</v>
       </c>
       <c r="J182" t="n">
-        <v>39.23</v>
+        <v>112979.9</v>
       </c>
       <c r="K182" t="n">
-        <v>741.08</v>
+        <v>135151.8</v>
       </c>
       <c r="L182" t="n">
-        <v>1684.95</v>
+        <v>899484.6</v>
       </c>
       <c r="M182" t="n">
-        <v>797.79</v>
+        <v>507804.3</v>
       </c>
       <c r="N182" t="n">
-        <v>373.18</v>
+        <v>110331.9</v>
+      </c>
+      <c r="O182" t="n">
+        <v>494709.9</v>
+      </c>
+      <c r="P182" t="n">
+        <v>89577.89999999999</v>
       </c>
     </row>
     <row r="183">
@@ -10289,28 +11383,34 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>267.47</v>
+        <v>295172.5</v>
       </c>
       <c r="H183" t="n">
-        <v>1239.59</v>
+        <v>114076.2</v>
       </c>
       <c r="I183" t="n">
-        <v>48.41</v>
+        <v>372625.8</v>
       </c>
       <c r="J183" t="n">
-        <v>87.06</v>
+        <v>588740.7</v>
       </c>
       <c r="K183" t="n">
-        <v>768.3</v>
+        <v>868333.2</v>
       </c>
       <c r="L183" t="n">
-        <v>1846.13</v>
+        <v>998821.2</v>
       </c>
       <c r="M183" t="n">
-        <v>620.6799999999999</v>
+        <v>712561.2</v>
       </c>
       <c r="N183" t="n">
-        <v>692.25</v>
+        <v>713993.2</v>
+      </c>
+      <c r="O183" t="n">
+        <v>258853.2</v>
+      </c>
+      <c r="P183" t="n">
+        <v>468747.2</v>
       </c>
     </row>
     <row r="184">
@@ -10343,28 +11443,34 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>159.7</v>
+        <v>756663.4</v>
       </c>
       <c r="H184" t="n">
-        <v>1637.18</v>
+        <v>344569</v>
       </c>
       <c r="I184" t="n">
-        <v>288.84</v>
+        <v>641529.5</v>
       </c>
       <c r="J184" t="n">
-        <v>93.81</v>
+        <v>188805.1</v>
       </c>
       <c r="K184" t="n">
-        <v>1526.24</v>
+        <v>642413.7</v>
       </c>
       <c r="L184" t="n">
-        <v>1494.8</v>
+        <v>969729.9</v>
       </c>
       <c r="M184" t="n">
-        <v>1286.81</v>
+        <v>344842</v>
       </c>
       <c r="N184" t="n">
-        <v>399.01</v>
+        <v>536250.1</v>
+      </c>
+      <c r="O184" t="n">
+        <v>989455.9</v>
+      </c>
+      <c r="P184" t="n">
+        <v>581319.5</v>
       </c>
     </row>
     <row r="185">
@@ -10397,28 +11503,34 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>308.54</v>
+        <v>991820.9</v>
       </c>
       <c r="H185" t="n">
-        <v>115.88</v>
+        <v>142292.5</v>
       </c>
       <c r="I185" t="n">
-        <v>472.62</v>
+        <v>922215.2</v>
       </c>
       <c r="J185" t="n">
-        <v>151.63</v>
+        <v>954667.1</v>
       </c>
       <c r="K185" t="n">
-        <v>1933.37</v>
+        <v>171382.2</v>
       </c>
       <c r="L185" t="n">
-        <v>645.4299999999999</v>
+        <v>58466.2</v>
       </c>
       <c r="M185" t="n">
-        <v>882.24</v>
+        <v>295984.6</v>
       </c>
       <c r="N185" t="n">
-        <v>40.43</v>
+        <v>440238.7</v>
+      </c>
+      <c r="O185" t="n">
+        <v>546606.3</v>
+      </c>
+      <c r="P185" t="n">
+        <v>544754.9</v>
       </c>
     </row>
     <row r="186">
@@ -10451,28 +11563,34 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>494.89</v>
+        <v>793619.3</v>
       </c>
       <c r="H186" t="n">
-        <v>4411.7</v>
+        <v>305059.7</v>
       </c>
       <c r="I186" t="n">
-        <v>327.13</v>
+        <v>258964.3</v>
       </c>
       <c r="J186" t="n">
-        <v>141.18</v>
+        <v>771398.4</v>
       </c>
       <c r="K186" t="n">
-        <v>1073.38</v>
+        <v>235503.9</v>
       </c>
       <c r="L186" t="n">
-        <v>2541.52</v>
+        <v>528346</v>
       </c>
       <c r="M186" t="n">
-        <v>1077.32</v>
+        <v>827182.3</v>
       </c>
       <c r="N186" t="n">
-        <v>705.96</v>
+        <v>925210.9</v>
+      </c>
+      <c r="O186" t="n">
+        <v>676797.8</v>
+      </c>
+      <c r="P186" t="n">
+        <v>134418.3</v>
       </c>
     </row>
     <row r="187">
@@ -10505,28 +11623,34 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>727.51</v>
+        <v>398446.5</v>
       </c>
       <c r="H187" t="n">
-        <v>3819.28</v>
+        <v>260378.1</v>
       </c>
       <c r="I187" t="n">
-        <v>182.97</v>
+        <v>918485.5</v>
       </c>
       <c r="J187" t="n">
-        <v>120.17</v>
+        <v>253845.1</v>
       </c>
       <c r="K187" t="n">
-        <v>1140.56</v>
+        <v>874665.2</v>
       </c>
       <c r="L187" t="n">
-        <v>583.97</v>
+        <v>392434.9</v>
       </c>
       <c r="M187" t="n">
-        <v>1383.06</v>
+        <v>764941.4</v>
       </c>
       <c r="N187" t="n">
-        <v>58.83</v>
+        <v>844415.4</v>
+      </c>
+      <c r="O187" t="n">
+        <v>255259.1</v>
+      </c>
+      <c r="P187" t="n">
+        <v>713100.2</v>
       </c>
     </row>
     <row r="188">
@@ -10559,28 +11683,34 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>504.26</v>
+        <v>172252.9</v>
       </c>
       <c r="H188" t="n">
-        <v>3822.02</v>
+        <v>452393.9</v>
       </c>
       <c r="I188" t="n">
-        <v>139.86</v>
+        <v>981780.9</v>
       </c>
       <c r="J188" t="n">
-        <v>296.73</v>
+        <v>345921.3</v>
       </c>
       <c r="K188" t="n">
-        <v>1360.8</v>
+        <v>125358</v>
       </c>
       <c r="L188" t="n">
-        <v>356.43</v>
+        <v>814835.4</v>
       </c>
       <c r="M188" t="n">
-        <v>2437.71</v>
+        <v>25787.2</v>
       </c>
       <c r="N188" t="n">
-        <v>315.12</v>
+        <v>205924.9</v>
+      </c>
+      <c r="O188" t="n">
+        <v>213615.5</v>
+      </c>
+      <c r="P188" t="n">
+        <v>543602.5</v>
       </c>
     </row>
     <row r="189">
@@ -10613,28 +11743,34 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>794.9</v>
+        <v>460822.3</v>
       </c>
       <c r="H189" t="n">
-        <v>1695.43</v>
+        <v>943548.8</v>
       </c>
       <c r="I189" t="n">
-        <v>469.47</v>
+        <v>351740.8</v>
       </c>
       <c r="J189" t="n">
-        <v>226.49</v>
+        <v>975848.4</v>
       </c>
       <c r="K189" t="n">
-        <v>398.12</v>
+        <v>585567.8</v>
       </c>
       <c r="L189" t="n">
-        <v>1527.37</v>
+        <v>254009.8</v>
       </c>
       <c r="M189" t="n">
-        <v>1250.19</v>
+        <v>338856.3</v>
       </c>
       <c r="N189" t="n">
-        <v>36.24</v>
+        <v>371994.9</v>
+      </c>
+      <c r="O189" t="n">
+        <v>875387.4</v>
+      </c>
+      <c r="P189" t="n">
+        <v>692511.7</v>
       </c>
     </row>
     <row r="190">
@@ -10667,28 +11803,34 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>137.04</v>
+        <v>128468.7</v>
       </c>
       <c r="H190" t="n">
-        <v>1665.2</v>
+        <v>27217.8</v>
       </c>
       <c r="I190" t="n">
-        <v>236.87</v>
+        <v>63114.8</v>
       </c>
       <c r="J190" t="n">
-        <v>137.1</v>
+        <v>958176.9</v>
       </c>
       <c r="K190" t="n">
-        <v>1212.52</v>
+        <v>760458.4</v>
       </c>
       <c r="L190" t="n">
-        <v>1546.52</v>
+        <v>917117.3</v>
       </c>
       <c r="M190" t="n">
-        <v>819.91</v>
+        <v>114875.8</v>
       </c>
       <c r="N190" t="n">
-        <v>490.45</v>
+        <v>454811.2</v>
+      </c>
+      <c r="O190" t="n">
+        <v>253900</v>
+      </c>
+      <c r="P190" t="n">
+        <v>71657.10000000001</v>
       </c>
     </row>
     <row r="191">
@@ -10721,28 +11863,34 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>162.5</v>
+        <v>130663.6</v>
       </c>
       <c r="H191" t="n">
-        <v>4953.08</v>
+        <v>231599.8</v>
       </c>
       <c r="I191" t="n">
-        <v>369.66</v>
+        <v>681032.5</v>
       </c>
       <c r="J191" t="n">
-        <v>89.77</v>
+        <v>766998</v>
       </c>
       <c r="K191" t="n">
-        <v>672.75</v>
+        <v>291085.8</v>
       </c>
       <c r="L191" t="n">
-        <v>2484.87</v>
+        <v>136405.9</v>
       </c>
       <c r="M191" t="n">
-        <v>1330.85</v>
+        <v>194173.4</v>
       </c>
       <c r="N191" t="n">
-        <v>566.99</v>
+        <v>87054.8</v>
+      </c>
+      <c r="O191" t="n">
+        <v>610029.3</v>
+      </c>
+      <c r="P191" t="n">
+        <v>973236</v>
       </c>
     </row>
     <row r="192">
@@ -10775,28 +11923,34 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>299.79</v>
+        <v>446548.5</v>
       </c>
       <c r="H192" t="n">
-        <v>4078.74</v>
+        <v>608266.6</v>
       </c>
       <c r="I192" t="n">
-        <v>184.18</v>
+        <v>919060.8</v>
       </c>
       <c r="J192" t="n">
-        <v>202.14</v>
+        <v>38978</v>
       </c>
       <c r="K192" t="n">
-        <v>1959.8</v>
+        <v>16401.6</v>
       </c>
       <c r="L192" t="n">
-        <v>1751.11</v>
+        <v>142822.8</v>
       </c>
       <c r="M192" t="n">
-        <v>1991.89</v>
+        <v>364105</v>
       </c>
       <c r="N192" t="n">
-        <v>580.26</v>
+        <v>171474.3</v>
+      </c>
+      <c r="O192" t="n">
+        <v>431087.2</v>
+      </c>
+      <c r="P192" t="n">
+        <v>696318.6</v>
       </c>
     </row>
     <row r="193">
@@ -10829,28 +11983,34 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>688.04</v>
+        <v>850222.4</v>
       </c>
       <c r="H193" t="n">
-        <v>133.24</v>
+        <v>834823.4</v>
       </c>
       <c r="I193" t="n">
-        <v>237.3</v>
+        <v>367726.9</v>
       </c>
       <c r="J193" t="n">
-        <v>290.12</v>
+        <v>219717.9</v>
       </c>
       <c r="K193" t="n">
-        <v>1565.81</v>
+        <v>385156.2</v>
       </c>
       <c r="L193" t="n">
-        <v>2328.49</v>
+        <v>257421.9</v>
       </c>
       <c r="M193" t="n">
-        <v>1444.09</v>
+        <v>293815.5</v>
       </c>
       <c r="N193" t="n">
-        <v>577.12</v>
+        <v>323545.2</v>
+      </c>
+      <c r="O193" t="n">
+        <v>490103</v>
+      </c>
+      <c r="P193" t="n">
+        <v>531676.9</v>
       </c>
     </row>
     <row r="194">
@@ -10883,28 +12043,34 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>583.52</v>
+        <v>701840.7</v>
       </c>
       <c r="H194" t="n">
-        <v>852.5599999999999</v>
+        <v>379589.3</v>
       </c>
       <c r="I194" t="n">
-        <v>314.51</v>
+        <v>313412.9</v>
       </c>
       <c r="J194" t="n">
-        <v>185.92</v>
+        <v>603343.6</v>
       </c>
       <c r="K194" t="n">
-        <v>1682.33</v>
+        <v>671079.2</v>
       </c>
       <c r="L194" t="n">
-        <v>443.33</v>
+        <v>347283.2</v>
       </c>
       <c r="M194" t="n">
-        <v>1701.82</v>
+        <v>912836.8</v>
       </c>
       <c r="N194" t="n">
-        <v>25.26</v>
+        <v>745223.3</v>
+      </c>
+      <c r="O194" t="n">
+        <v>402008.2</v>
+      </c>
+      <c r="P194" t="n">
+        <v>563968.7</v>
       </c>
     </row>
     <row r="195">
@@ -10937,28 +12103,34 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>948.21</v>
+        <v>418163</v>
       </c>
       <c r="H195" t="n">
-        <v>549.48</v>
+        <v>358837</v>
       </c>
       <c r="I195" t="n">
-        <v>9.470000000000001</v>
+        <v>236893.1</v>
       </c>
       <c r="J195" t="n">
-        <v>94.11</v>
+        <v>206650</v>
       </c>
       <c r="K195" t="n">
-        <v>302.86</v>
+        <v>878230.1</v>
       </c>
       <c r="L195" t="n">
-        <v>2071.5</v>
+        <v>808265.5</v>
       </c>
       <c r="M195" t="n">
-        <v>1025.94</v>
+        <v>889332.8</v>
       </c>
       <c r="N195" t="n">
-        <v>619.98</v>
+        <v>446916.9</v>
+      </c>
+      <c r="O195" t="n">
+        <v>967024.5</v>
+      </c>
+      <c r="P195" t="n">
+        <v>328993.6</v>
       </c>
     </row>
     <row r="196">
@@ -10991,28 +12163,34 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>920.52</v>
+        <v>954331.5</v>
       </c>
       <c r="H196" t="n">
-        <v>4364.09</v>
+        <v>317975.7</v>
       </c>
       <c r="I196" t="n">
-        <v>367.92</v>
+        <v>124224.7</v>
       </c>
       <c r="J196" t="n">
-        <v>18.68</v>
+        <v>517066.4</v>
       </c>
       <c r="K196" t="n">
-        <v>276.16</v>
+        <v>598383.8</v>
       </c>
       <c r="L196" t="n">
-        <v>622.03</v>
+        <v>382332.2</v>
       </c>
       <c r="M196" t="n">
-        <v>812.62</v>
+        <v>625321.7</v>
       </c>
       <c r="N196" t="n">
-        <v>529.78</v>
+        <v>232095.2</v>
+      </c>
+      <c r="O196" t="n">
+        <v>8634.4</v>
+      </c>
+      <c r="P196" t="n">
+        <v>357860.6</v>
       </c>
     </row>
     <row r="197">
@@ -11045,28 +12223,34 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>525.48</v>
+        <v>178834.1</v>
       </c>
       <c r="H197" t="n">
-        <v>1568.76</v>
+        <v>375266.3</v>
       </c>
       <c r="I197" t="n">
-        <v>86.59</v>
+        <v>664117.9</v>
       </c>
       <c r="J197" t="n">
-        <v>273.64</v>
+        <v>6453.2</v>
       </c>
       <c r="K197" t="n">
-        <v>684.65</v>
+        <v>72143.2</v>
       </c>
       <c r="L197" t="n">
-        <v>1062.86</v>
+        <v>566413.1</v>
       </c>
       <c r="M197" t="n">
-        <v>1929.97</v>
+        <v>324212.6</v>
       </c>
       <c r="N197" t="n">
-        <v>576.74</v>
+        <v>685378.5</v>
+      </c>
+      <c r="O197" t="n">
+        <v>126350.8</v>
+      </c>
+      <c r="P197" t="n">
+        <v>476534.1</v>
       </c>
     </row>
     <row r="198">
@@ -11099,28 +12283,34 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>643.3099999999999</v>
+        <v>250167.7</v>
       </c>
       <c r="H198" t="n">
-        <v>3466.57</v>
+        <v>538314.9</v>
       </c>
       <c r="I198" t="n">
-        <v>305.04</v>
+        <v>289308.7</v>
       </c>
       <c r="J198" t="n">
-        <v>57.68</v>
+        <v>461279.9</v>
       </c>
       <c r="K198" t="n">
-        <v>493.04</v>
+        <v>197784.7</v>
       </c>
       <c r="L198" t="n">
-        <v>1674.26</v>
+        <v>855165.5</v>
       </c>
       <c r="M198" t="n">
-        <v>562.17</v>
+        <v>383816.8</v>
       </c>
       <c r="N198" t="n">
-        <v>778.33</v>
+        <v>857534.8</v>
+      </c>
+      <c r="O198" t="n">
+        <v>230678.6</v>
+      </c>
+      <c r="P198" t="n">
+        <v>752002.7</v>
       </c>
     </row>
     <row r="199">
@@ -11153,28 +12343,34 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>297.61</v>
+        <v>273578</v>
       </c>
       <c r="H199" t="n">
-        <v>1445.02</v>
+        <v>779797.3</v>
       </c>
       <c r="I199" t="n">
-        <v>103.64</v>
+        <v>933239.9</v>
       </c>
       <c r="J199" t="n">
-        <v>211.5</v>
+        <v>476268.5</v>
       </c>
       <c r="K199" t="n">
-        <v>634.08</v>
+        <v>509122.1</v>
       </c>
       <c r="L199" t="n">
-        <v>1046.41</v>
+        <v>96265.60000000001</v>
       </c>
       <c r="M199" t="n">
-        <v>2334.25</v>
+        <v>885003.9</v>
       </c>
       <c r="N199" t="n">
-        <v>636.3200000000001</v>
+        <v>439928.3</v>
+      </c>
+      <c r="O199" t="n">
+        <v>553905.3</v>
+      </c>
+      <c r="P199" t="n">
+        <v>136055.4</v>
       </c>
     </row>
     <row r="200">
@@ -11207,28 +12403,34 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>273.46</v>
+        <v>572663.7</v>
       </c>
       <c r="H200" t="n">
-        <v>609.37</v>
+        <v>21536.5</v>
       </c>
       <c r="I200" t="n">
-        <v>338.31</v>
+        <v>407825.4</v>
       </c>
       <c r="J200" t="n">
-        <v>113.91</v>
+        <v>828667.1</v>
       </c>
       <c r="K200" t="n">
-        <v>1960.32</v>
+        <v>252063.2</v>
       </c>
       <c r="L200" t="n">
-        <v>2455.13</v>
+        <v>499637.8</v>
       </c>
       <c r="M200" t="n">
-        <v>2386.52</v>
+        <v>86479.60000000001</v>
       </c>
       <c r="N200" t="n">
-        <v>643.6900000000001</v>
+        <v>382975.2</v>
+      </c>
+      <c r="O200" t="n">
+        <v>682329.4</v>
+      </c>
+      <c r="P200" t="n">
+        <v>9918.9</v>
       </c>
     </row>
     <row r="201">
@@ -11261,28 +12463,34 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>290.45</v>
+        <v>889763.7</v>
       </c>
       <c r="H201" t="n">
-        <v>1438.15</v>
+        <v>175942.4</v>
       </c>
       <c r="I201" t="n">
-        <v>357.07</v>
+        <v>128934</v>
       </c>
       <c r="J201" t="n">
-        <v>103.91</v>
+        <v>346770.1</v>
       </c>
       <c r="K201" t="n">
-        <v>884.75</v>
+        <v>132687</v>
       </c>
       <c r="L201" t="n">
-        <v>769.33</v>
+        <v>637257.3</v>
       </c>
       <c r="M201" t="n">
-        <v>1197.7</v>
+        <v>403340.1</v>
       </c>
       <c r="N201" t="n">
-        <v>161.65</v>
+        <v>275242.7</v>
+      </c>
+      <c r="O201" t="n">
+        <v>510232</v>
+      </c>
+      <c r="P201" t="n">
+        <v>821861.1</v>
       </c>
     </row>
     <row r="202">
@@ -11315,28 +12523,34 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>538.58</v>
+        <v>382654.3</v>
       </c>
       <c r="H202" t="n">
-        <v>4665.12</v>
+        <v>222119.2</v>
       </c>
       <c r="I202" t="n">
-        <v>348.09</v>
+        <v>666990.9</v>
       </c>
       <c r="J202" t="n">
-        <v>41.18</v>
+        <v>900152.1</v>
       </c>
       <c r="K202" t="n">
-        <v>1231.35</v>
+        <v>154550.5</v>
       </c>
       <c r="L202" t="n">
-        <v>1760.49</v>
+        <v>721375.3</v>
       </c>
       <c r="M202" t="n">
-        <v>606.15</v>
+        <v>94381.3</v>
       </c>
       <c r="N202" t="n">
-        <v>535.87</v>
+        <v>535289.8</v>
+      </c>
+      <c r="O202" t="n">
+        <v>254602.5</v>
+      </c>
+      <c r="P202" t="n">
+        <v>819617.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dataset/RADAR_Test_CAMRI_ARG.xlsx
+++ b/docs/dataset/RADAR_Test_CAMRI_ARG.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P202"/>
+  <dimension ref="A1:P222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12553,6 +12555,1206 @@
         <v>819617.9</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240105</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>45296</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>90339.89999999999</v>
+      </c>
+      <c r="H203" t="n">
+        <v>950633.6</v>
+      </c>
+      <c r="I203" t="n">
+        <v>149971.1</v>
+      </c>
+      <c r="J203" t="n">
+        <v>739370.4</v>
+      </c>
+      <c r="K203" t="n">
+        <v>841242.4</v>
+      </c>
+      <c r="L203" t="n">
+        <v>747137</v>
+      </c>
+      <c r="M203" t="n">
+        <v>301937.6</v>
+      </c>
+      <c r="N203" t="n">
+        <v>351623.9</v>
+      </c>
+      <c r="O203" t="n">
+        <v>721862.6</v>
+      </c>
+      <c r="P203" t="n">
+        <v>965646.4</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240210</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>45332</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>662627.8</v>
+      </c>
+      <c r="H204" t="n">
+        <v>540581.2</v>
+      </c>
+      <c r="I204" t="n">
+        <v>387901.2</v>
+      </c>
+      <c r="J204" t="n">
+        <v>405739.7</v>
+      </c>
+      <c r="K204" t="n">
+        <v>719095.9</v>
+      </c>
+      <c r="L204" t="n">
+        <v>428891.2</v>
+      </c>
+      <c r="M204" t="n">
+        <v>534196.7</v>
+      </c>
+      <c r="N204" t="n">
+        <v>630948.6</v>
+      </c>
+      <c r="O204" t="n">
+        <v>632518.6</v>
+      </c>
+      <c r="P204" t="n">
+        <v>41025.8</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240317</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>45368</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>230611.6</v>
+      </c>
+      <c r="H205" t="n">
+        <v>705759.3</v>
+      </c>
+      <c r="I205" t="n">
+        <v>570348.3</v>
+      </c>
+      <c r="J205" t="n">
+        <v>837906.6</v>
+      </c>
+      <c r="K205" t="n">
+        <v>52486.3</v>
+      </c>
+      <c r="L205" t="n">
+        <v>231729.9</v>
+      </c>
+      <c r="M205" t="n">
+        <v>501970.6</v>
+      </c>
+      <c r="N205" t="n">
+        <v>746993.3</v>
+      </c>
+      <c r="O205" t="n">
+        <v>195089.1</v>
+      </c>
+      <c r="P205" t="n">
+        <v>764622.1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240422</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>410400.3</v>
+      </c>
+      <c r="H206" t="n">
+        <v>305663.7</v>
+      </c>
+      <c r="I206" t="n">
+        <v>829454.1</v>
+      </c>
+      <c r="J206" t="n">
+        <v>107128.4</v>
+      </c>
+      <c r="K206" t="n">
+        <v>933785.7</v>
+      </c>
+      <c r="L206" t="n">
+        <v>310524.5</v>
+      </c>
+      <c r="M206" t="n">
+        <v>362293.3</v>
+      </c>
+      <c r="N206" t="n">
+        <v>203077.5</v>
+      </c>
+      <c r="O206" t="n">
+        <v>467986.3</v>
+      </c>
+      <c r="P206" t="n">
+        <v>842275.2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240528</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>45440</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>221066.8</v>
+      </c>
+      <c r="H207" t="n">
+        <v>554024.4</v>
+      </c>
+      <c r="I207" t="n">
+        <v>440223.9</v>
+      </c>
+      <c r="J207" t="n">
+        <v>301739.1</v>
+      </c>
+      <c r="K207" t="n">
+        <v>130187.5</v>
+      </c>
+      <c r="L207" t="n">
+        <v>697886</v>
+      </c>
+      <c r="M207" t="n">
+        <v>415113.9</v>
+      </c>
+      <c r="N207" t="n">
+        <v>469680.6</v>
+      </c>
+      <c r="O207" t="n">
+        <v>602678.7</v>
+      </c>
+      <c r="P207" t="n">
+        <v>106964.3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240703</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>817723.1</v>
+      </c>
+      <c r="H208" t="n">
+        <v>890827.8</v>
+      </c>
+      <c r="I208" t="n">
+        <v>254308.3</v>
+      </c>
+      <c r="J208" t="n">
+        <v>816040.8</v>
+      </c>
+      <c r="K208" t="n">
+        <v>698841.6</v>
+      </c>
+      <c r="L208" t="n">
+        <v>298250.8</v>
+      </c>
+      <c r="M208" t="n">
+        <v>269845.5</v>
+      </c>
+      <c r="N208" t="n">
+        <v>83908.8</v>
+      </c>
+      <c r="O208" t="n">
+        <v>414151.7</v>
+      </c>
+      <c r="P208" t="n">
+        <v>451193.4</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240808</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>45512</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>486837</v>
+      </c>
+      <c r="H209" t="n">
+        <v>481530.4</v>
+      </c>
+      <c r="I209" t="n">
+        <v>548661.8</v>
+      </c>
+      <c r="J209" t="n">
+        <v>124791.8</v>
+      </c>
+      <c r="K209" t="n">
+        <v>224576.3</v>
+      </c>
+      <c r="L209" t="n">
+        <v>559146.4</v>
+      </c>
+      <c r="M209" t="n">
+        <v>472393.4</v>
+      </c>
+      <c r="N209" t="n">
+        <v>174386.8</v>
+      </c>
+      <c r="O209" t="n">
+        <v>276791.6</v>
+      </c>
+      <c r="P209" t="n">
+        <v>979108.3</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20240913</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>45548</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>799013.9</v>
+      </c>
+      <c r="H210" t="n">
+        <v>726924.6</v>
+      </c>
+      <c r="I210" t="n">
+        <v>355285.8</v>
+      </c>
+      <c r="J210" t="n">
+        <v>418596.4</v>
+      </c>
+      <c r="K210" t="n">
+        <v>704907.2</v>
+      </c>
+      <c r="L210" t="n">
+        <v>561796.8</v>
+      </c>
+      <c r="M210" t="n">
+        <v>640474.6</v>
+      </c>
+      <c r="N210" t="n">
+        <v>35548.5</v>
+      </c>
+      <c r="O210" t="n">
+        <v>712577.4</v>
+      </c>
+      <c r="P210" t="n">
+        <v>200048</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20241019</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>327461.1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>530820.6</v>
+      </c>
+      <c r="I211" t="n">
+        <v>949190.1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>405574.6</v>
+      </c>
+      <c r="K211" t="n">
+        <v>646121.4</v>
+      </c>
+      <c r="L211" t="n">
+        <v>208606.7</v>
+      </c>
+      <c r="M211" t="n">
+        <v>939503.5</v>
+      </c>
+      <c r="N211" t="n">
+        <v>247726.5</v>
+      </c>
+      <c r="O211" t="n">
+        <v>540846.2</v>
+      </c>
+      <c r="P211" t="n">
+        <v>680739.4</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ARG-Site1-20241124</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>45620</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>699081.6</v>
+      </c>
+      <c r="H212" t="n">
+        <v>445444.2</v>
+      </c>
+      <c r="I212" t="n">
+        <v>647113.9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>10242.6</v>
+      </c>
+      <c r="K212" t="n">
+        <v>985231.8</v>
+      </c>
+      <c r="L212" t="n">
+        <v>558351.7</v>
+      </c>
+      <c r="M212" t="n">
+        <v>595108.2</v>
+      </c>
+      <c r="N212" t="n">
+        <v>254383.2</v>
+      </c>
+      <c r="O212" t="n">
+        <v>480092.8</v>
+      </c>
+      <c r="P212" t="n">
+        <v>642499.2</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20240123</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>45314</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>412454.9</v>
+      </c>
+      <c r="H213" t="n">
+        <v>121504.4</v>
+      </c>
+      <c r="I213" t="n">
+        <v>196400.9</v>
+      </c>
+      <c r="J213" t="n">
+        <v>873736.6</v>
+      </c>
+      <c r="K213" t="n">
+        <v>205660.8</v>
+      </c>
+      <c r="L213" t="n">
+        <v>514240.8</v>
+      </c>
+      <c r="M213" t="n">
+        <v>711082.6</v>
+      </c>
+      <c r="N213" t="n">
+        <v>221253.8</v>
+      </c>
+      <c r="O213" t="n">
+        <v>807758.2</v>
+      </c>
+      <c r="P213" t="n">
+        <v>475861.1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20240228</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>45350</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>947073.3</v>
+      </c>
+      <c r="H214" t="n">
+        <v>204814</v>
+      </c>
+      <c r="I214" t="n">
+        <v>425344.6</v>
+      </c>
+      <c r="J214" t="n">
+        <v>362557.1</v>
+      </c>
+      <c r="K214" t="n">
+        <v>273086.4</v>
+      </c>
+      <c r="L214" t="n">
+        <v>426236.9</v>
+      </c>
+      <c r="M214" t="n">
+        <v>427086.5</v>
+      </c>
+      <c r="N214" t="n">
+        <v>394314.5</v>
+      </c>
+      <c r="O214" t="n">
+        <v>868121.7</v>
+      </c>
+      <c r="P214" t="n">
+        <v>325385.1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20240404</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>56232.3</v>
+      </c>
+      <c r="H215" t="n">
+        <v>750133.7</v>
+      </c>
+      <c r="I215" t="n">
+        <v>434555.4</v>
+      </c>
+      <c r="J215" t="n">
+        <v>25075.7</v>
+      </c>
+      <c r="K215" t="n">
+        <v>754633.7</v>
+      </c>
+      <c r="L215" t="n">
+        <v>725979</v>
+      </c>
+      <c r="M215" t="n">
+        <v>654963.5</v>
+      </c>
+      <c r="N215" t="n">
+        <v>819742</v>
+      </c>
+      <c r="O215" t="n">
+        <v>269575.4</v>
+      </c>
+      <c r="P215" t="n">
+        <v>840454.8</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20240510</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>45422</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>363789.2</v>
+      </c>
+      <c r="H216" t="n">
+        <v>859009.4</v>
+      </c>
+      <c r="I216" t="n">
+        <v>998563.1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>554212.9</v>
+      </c>
+      <c r="K216" t="n">
+        <v>421798.6</v>
+      </c>
+      <c r="L216" t="n">
+        <v>734883.6</v>
+      </c>
+      <c r="M216" t="n">
+        <v>719454.2</v>
+      </c>
+      <c r="N216" t="n">
+        <v>505352.5</v>
+      </c>
+      <c r="O216" t="n">
+        <v>81358.39999999999</v>
+      </c>
+      <c r="P216" t="n">
+        <v>355683.7</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20240615</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>45458</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>680481.6</v>
+      </c>
+      <c r="H217" t="n">
+        <v>13910.7</v>
+      </c>
+      <c r="I217" t="n">
+        <v>408962.9</v>
+      </c>
+      <c r="J217" t="n">
+        <v>916438.9</v>
+      </c>
+      <c r="K217" t="n">
+        <v>715072.2</v>
+      </c>
+      <c r="L217" t="n">
+        <v>260434.5</v>
+      </c>
+      <c r="M217" t="n">
+        <v>135826.6</v>
+      </c>
+      <c r="N217" t="n">
+        <v>571453.8</v>
+      </c>
+      <c r="O217" t="n">
+        <v>615149.8</v>
+      </c>
+      <c r="P217" t="n">
+        <v>286346.1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20240721</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>45494</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>515835.5</v>
+      </c>
+      <c r="H218" t="n">
+        <v>991762.6</v>
+      </c>
+      <c r="I218" t="n">
+        <v>650113.3</v>
+      </c>
+      <c r="J218" t="n">
+        <v>542389.4</v>
+      </c>
+      <c r="K218" t="n">
+        <v>62536.3</v>
+      </c>
+      <c r="L218" t="n">
+        <v>474343.2</v>
+      </c>
+      <c r="M218" t="n">
+        <v>22487</v>
+      </c>
+      <c r="N218" t="n">
+        <v>963797.2</v>
+      </c>
+      <c r="O218" t="n">
+        <v>517056</v>
+      </c>
+      <c r="P218" t="n">
+        <v>600977.9</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20240826</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>45530</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>680683.4</v>
+      </c>
+      <c r="H219" t="n">
+        <v>40288.7</v>
+      </c>
+      <c r="I219" t="n">
+        <v>821415.4</v>
+      </c>
+      <c r="J219" t="n">
+        <v>698851.8</v>
+      </c>
+      <c r="K219" t="n">
+        <v>71943.7</v>
+      </c>
+      <c r="L219" t="n">
+        <v>914685.6</v>
+      </c>
+      <c r="M219" t="n">
+        <v>866031.9</v>
+      </c>
+      <c r="N219" t="n">
+        <v>990145.6</v>
+      </c>
+      <c r="O219" t="n">
+        <v>92570.10000000001</v>
+      </c>
+      <c r="P219" t="n">
+        <v>915692.2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20241001</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>779424.3</v>
+      </c>
+      <c r="H220" t="n">
+        <v>254241.3</v>
+      </c>
+      <c r="I220" t="n">
+        <v>79519.8</v>
+      </c>
+      <c r="J220" t="n">
+        <v>676551.2</v>
+      </c>
+      <c r="K220" t="n">
+        <v>62677.9</v>
+      </c>
+      <c r="L220" t="n">
+        <v>547651.2</v>
+      </c>
+      <c r="M220" t="n">
+        <v>805614.1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>396437.3</v>
+      </c>
+      <c r="O220" t="n">
+        <v>332659</v>
+      </c>
+      <c r="P220" t="n">
+        <v>417091.7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20241106</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>45602</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>114072.9</v>
+      </c>
+      <c r="H221" t="n">
+        <v>62317.6</v>
+      </c>
+      <c r="I221" t="n">
+        <v>564372.2</v>
+      </c>
+      <c r="J221" t="n">
+        <v>818568.8</v>
+      </c>
+      <c r="K221" t="n">
+        <v>991682.6</v>
+      </c>
+      <c r="L221" t="n">
+        <v>104095.9</v>
+      </c>
+      <c r="M221" t="n">
+        <v>303061</v>
+      </c>
+      <c r="N221" t="n">
+        <v>817119.4</v>
+      </c>
+      <c r="O221" t="n">
+        <v>291789.4</v>
+      </c>
+      <c r="P221" t="n">
+        <v>768144.6</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ARG-Site2-20241212</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>940852.6</v>
+      </c>
+      <c r="H222" t="n">
+        <v>859090.9</v>
+      </c>
+      <c r="I222" t="n">
+        <v>624310.5</v>
+      </c>
+      <c r="J222" t="n">
+        <v>728439.7</v>
+      </c>
+      <c r="K222" t="n">
+        <v>857265.9</v>
+      </c>
+      <c r="L222" t="n">
+        <v>140951.5</v>
+      </c>
+      <c r="M222" t="n">
+        <v>336653.7</v>
+      </c>
+      <c r="N222" t="n">
+        <v>733919.9</v>
+      </c>
+      <c r="O222" t="n">
+        <v>477996.2</v>
+      </c>
+      <c r="P222" t="n">
+        <v>769338.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
